--- a/Treet/RealMaxxin_Agricrafture_Treet.xlsx
+++ b/Treet/RealMaxxin_Agricrafture_Treet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GoldenGriffinGames\Projects\GoldenGriffinModding\Minecraft\Realmaxxin\Treet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51D85CF-0A37-4D5E-8E1F-CFEE5EF800DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F81FA40-2A08-4BC6-898C-0015F2C4E1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Processing Tree NEW" sheetId="9" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6640" uniqueCount="2751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6659" uniqueCount="2758">
   <si>
     <t>Minecraft</t>
   </si>
@@ -8278,9 +8278,6 @@
     <t>origin_oak_sapling</t>
   </si>
   <si>
-    <t>origin_oak_#</t>
-  </si>
-  <si>
     <t>Wooden Bench</t>
   </si>
   <si>
@@ -8297,6 +8294,30 @@
   </si>
   <si>
     <t>picnic_table</t>
+  </si>
+  <si>
+    <t>Planks texture used for Picnic Tables, Benches, Slabs, Stairs, Fences, Gates, Pressure Plates, Buttons</t>
+  </si>
+  <si>
+    <t>jurupa_oak_#</t>
+  </si>
+  <si>
+    <t>Jurupa Oak Acorn</t>
+  </si>
+  <si>
+    <t>Jurupa Oak Seedling</t>
+  </si>
+  <si>
+    <t>Jurupa Oak Bark</t>
+  </si>
+  <si>
+    <t>jurupa_oak_acorn</t>
+  </si>
+  <si>
+    <t>jurupa_oak_seedling</t>
+  </si>
+  <si>
+    <t>jurupa_oak_bark</t>
   </si>
 </sst>
 </file>
@@ -9287,23 +9308,29 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9311,13 +9338,31 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -9329,47 +9374,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="4" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9379,12 +9406,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9401,12 +9422,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="4" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9416,8 +9431,11 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9427,6 +9445,9 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -9461,27 +9482,27 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9860,288 +9881,288 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.4">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="125" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
     </row>
     <row r="2" spans="1:10" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="102" t="s">
+      <c r="A2" s="126" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="126"/>
     </row>
     <row r="3" spans="1:10" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="103" t="s">
+      <c r="A3" s="127" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
     </row>
     <row r="4" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="104" t="s">
+      <c r="A4" s="123" t="s">
         <v>938</v>
       </c>
-      <c r="B4" s="104"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="104"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="123"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="105" t="s">
+      <c r="A5" s="107" t="s">
         <v>939</v>
       </c>
-      <c r="B5" s="106"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="105"/>
-      <c r="J5" s="105"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="116"/>
-      <c r="B6" s="116"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="116"/>
-      <c r="G6" s="116"/>
-      <c r="H6" s="116"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="116"/>
+      <c r="A6" s="119"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="119"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+      <c r="J6" s="119"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="107" t="s">
+      <c r="A7" s="109" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="33"/>
-      <c r="C7" s="109" t="s">
+      <c r="C7" s="104" t="s">
         <v>837</v>
       </c>
       <c r="D7" s="33"/>
-      <c r="E7" s="109" t="s">
+      <c r="E7" s="104" t="s">
         <v>846</v>
       </c>
       <c r="F7" s="33"/>
-      <c r="G7" s="109" t="s">
+      <c r="G7" s="104" t="s">
         <v>847</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="108"/>
+      <c r="A8" s="110"/>
       <c r="B8" s="34"/>
-      <c r="C8" s="110"/>
+      <c r="C8" s="105"/>
       <c r="D8" s="34"/>
-      <c r="E8" s="110"/>
+      <c r="E8" s="105"/>
       <c r="F8" s="34"/>
-      <c r="G8" s="110"/>
+      <c r="G8" s="105"/>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="112" t="s">
+      <c r="A9" s="120" t="s">
         <v>839</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="113" t="s">
+      <c r="C9" s="121" t="s">
         <v>840</v>
       </c>
       <c r="D9" s="7"/>
-      <c r="E9" s="113" t="s">
+      <c r="E9" s="121" t="s">
         <v>842</v>
       </c>
       <c r="F9" s="7"/>
-      <c r="G9" s="113" t="s">
+      <c r="G9" s="121" t="s">
         <v>841</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="112"/>
+      <c r="A10" s="120"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="113"/>
+      <c r="C10" s="121"/>
       <c r="D10" s="7"/>
-      <c r="E10" s="113"/>
+      <c r="E10" s="121"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="113"/>
+      <c r="G10" s="121"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="112"/>
+      <c r="A11" s="120"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="113"/>
+      <c r="C11" s="121"/>
       <c r="D11" s="7"/>
-      <c r="E11" s="113"/>
+      <c r="E11" s="121"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="113"/>
+      <c r="G11" s="121"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="114"/>
-      <c r="B12" s="114"/>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="114"/>
-      <c r="F12" s="114"/>
-      <c r="G12" s="114"/>
-      <c r="H12" s="114"/>
-      <c r="I12" s="114"/>
-      <c r="J12" s="114"/>
+      <c r="A12" s="122"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="107" t="s">
+      <c r="A13" s="109" t="s">
         <v>851</v>
       </c>
       <c r="B13" s="33"/>
-      <c r="C13" s="109" t="s">
+      <c r="C13" s="104" t="s">
         <v>852</v>
       </c>
       <c r="D13" s="33"/>
-      <c r="E13" s="109" t="s">
+      <c r="E13" s="104" t="s">
         <v>853</v>
       </c>
       <c r="F13" s="33"/>
-      <c r="G13" s="109" t="s">
+      <c r="G13" s="104" t="s">
         <v>854</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="108"/>
+      <c r="A14" s="110"/>
       <c r="B14" s="34"/>
-      <c r="C14" s="110"/>
+      <c r="C14" s="105"/>
       <c r="D14" s="34"/>
-      <c r="E14" s="110"/>
+      <c r="E14" s="105"/>
       <c r="F14" s="34"/>
-      <c r="G14" s="110"/>
+      <c r="G14" s="105"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="113" t="s">
+      <c r="A15" s="121" t="s">
         <v>855</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="113" t="s">
+      <c r="C15" s="121" t="s">
         <v>840</v>
       </c>
       <c r="D15" s="7"/>
-      <c r="E15" s="113" t="s">
+      <c r="E15" s="121" t="s">
         <v>842</v>
       </c>
       <c r="F15" s="7"/>
-      <c r="G15" s="113" t="s">
+      <c r="G15" s="121" t="s">
         <v>841</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="113"/>
+      <c r="A16" s="121"/>
       <c r="B16" s="7"/>
-      <c r="C16" s="113"/>
+      <c r="C16" s="121"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="113"/>
+      <c r="E16" s="121"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="113"/>
+      <c r="G16" s="121"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="113"/>
+      <c r="A17" s="121"/>
       <c r="B17" s="7"/>
-      <c r="C17" s="113"/>
+      <c r="C17" s="121"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="113"/>
+      <c r="E17" s="121"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="113"/>
+      <c r="G17" s="121"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="115"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="115"/>
-      <c r="G18" s="115"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="115"/>
+      <c r="A18" s="124"/>
+      <c r="B18" s="124"/>
+      <c r="C18" s="124"/>
+      <c r="D18" s="124"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="124"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="124"/>
+      <c r="J18" s="124"/>
     </row>
     <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="104" t="s">
+      <c r="A19" s="123" t="s">
         <v>843</v>
       </c>
-      <c r="B19" s="104"/>
-      <c r="C19" s="104"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="104"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="104"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="123"/>
+      <c r="F19" s="123"/>
+      <c r="G19" s="123"/>
+      <c r="H19" s="123"/>
+      <c r="I19" s="123"/>
+      <c r="J19" s="123"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="105" t="s">
+      <c r="A20" s="107" t="s">
         <v>845</v>
       </c>
-      <c r="B20" s="105"/>
-      <c r="C20" s="105"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
+      <c r="B20" s="107"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="107"/>
+      <c r="J20" s="107"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="114"/>
-      <c r="B21" s="114"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="114"/>
-      <c r="E21" s="114"/>
-      <c r="F21" s="114"/>
-      <c r="G21" s="114"/>
-      <c r="H21" s="114"/>
-      <c r="I21" s="114"/>
-      <c r="J21" s="114"/>
+      <c r="A21" s="122"/>
+      <c r="B21" s="122"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="122"/>
+      <c r="G21" s="122"/>
+      <c r="H21" s="122"/>
+      <c r="I21" s="122"/>
+      <c r="J21" s="122"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="109" t="s">
+      <c r="D22" s="104" t="s">
         <v>844</v>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="40"/>
-      <c r="G22" s="109" t="s">
+      <c r="G22" s="104" t="s">
         <v>848</v>
       </c>
       <c r="H22" s="41"/>
       <c r="I22" s="42"/>
-      <c r="J22" s="109" t="s">
+      <c r="J22" s="104" t="s">
         <v>849</v>
       </c>
     </row>
@@ -10149,13 +10170,13 @@
       <c r="A23" s="7"/>
       <c r="B23" s="43"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="110"/>
+      <c r="D23" s="105"/>
       <c r="E23" s="43"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="110"/>
+      <c r="G23" s="105"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
-      <c r="J23" s="110"/>
+      <c r="J23" s="105"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
@@ -10170,36 +10191,36 @@
       <c r="J24" s="7"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="107" t="s">
+      <c r="A25" s="109" t="s">
         <v>3</v>
       </c>
       <c r="B25" s="41"/>
       <c r="C25" s="44"/>
-      <c r="D25" s="109" t="s">
+      <c r="D25" s="104" t="s">
         <v>837</v>
       </c>
       <c r="E25" s="44"/>
       <c r="F25" s="42"/>
-      <c r="G25" s="109" t="s">
+      <c r="G25" s="104" t="s">
         <v>846</v>
       </c>
       <c r="H25" s="41"/>
       <c r="I25" s="42"/>
-      <c r="J25" s="109" t="s">
+      <c r="J25" s="104" t="s">
         <v>847</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="108"/>
+      <c r="A26" s="110"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="110"/>
+      <c r="D26" s="105"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="110"/>
+      <c r="G26" s="105"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
-      <c r="J26" s="110"/>
+      <c r="J26" s="105"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
@@ -10226,36 +10247,36 @@
       <c r="J28" s="46"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="107" t="s">
+      <c r="A29" s="109" t="s">
         <v>851</v>
       </c>
       <c r="B29" s="47"/>
       <c r="C29" s="50"/>
-      <c r="D29" s="109" t="s">
+      <c r="D29" s="104" t="s">
         <v>852</v>
       </c>
       <c r="E29" s="47"/>
       <c r="F29" s="52"/>
-      <c r="G29" s="109" t="s">
+      <c r="G29" s="104" t="s">
         <v>846</v>
       </c>
       <c r="H29" s="47"/>
       <c r="I29" s="50"/>
-      <c r="J29" s="109" t="s">
+      <c r="J29" s="104" t="s">
         <v>847</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="108"/>
+      <c r="A30" s="110"/>
       <c r="B30" s="48"/>
       <c r="C30" s="46"/>
-      <c r="D30" s="110"/>
+      <c r="D30" s="105"/>
       <c r="E30" s="48"/>
       <c r="F30" s="46"/>
-      <c r="G30" s="110"/>
+      <c r="G30" s="105"/>
       <c r="H30" s="48"/>
       <c r="I30" s="46"/>
-      <c r="J30" s="110"/>
+      <c r="J30" s="105"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="46"/>
@@ -10273,17 +10294,17 @@
       <c r="A32" s="46"/>
       <c r="B32" s="49"/>
       <c r="C32" s="51"/>
-      <c r="D32" s="109" t="s">
+      <c r="D32" s="104" t="s">
         <v>844</v>
       </c>
       <c r="E32" s="49"/>
       <c r="F32" s="51"/>
-      <c r="G32" s="109" t="s">
+      <c r="G32" s="104" t="s">
         <v>856</v>
       </c>
       <c r="H32" s="49"/>
       <c r="I32" s="47"/>
-      <c r="J32" s="109" t="s">
+      <c r="J32" s="104" t="s">
         <v>857</v>
       </c>
     </row>
@@ -10291,13 +10312,13 @@
       <c r="A33" s="46"/>
       <c r="B33" s="46"/>
       <c r="C33" s="46"/>
-      <c r="D33" s="110"/>
+      <c r="D33" s="105"/>
       <c r="E33" s="46"/>
       <c r="F33" s="46"/>
-      <c r="G33" s="110"/>
+      <c r="G33" s="105"/>
       <c r="H33" s="46"/>
       <c r="I33" s="46"/>
-      <c r="J33" s="110"/>
+      <c r="J33" s="105"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="42"/>
@@ -10312,54 +10333,54 @@
       <c r="J34" s="42"/>
     </row>
     <row r="35" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="104" t="s">
+      <c r="A35" s="123" t="s">
         <v>850</v>
       </c>
-      <c r="B35" s="104"/>
-      <c r="C35" s="104"/>
-      <c r="D35" s="104"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="104"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="104"/>
-      <c r="I35" s="104"/>
-      <c r="J35" s="104"/>
+      <c r="B35" s="123"/>
+      <c r="C35" s="123"/>
+      <c r="D35" s="123"/>
+      <c r="E35" s="123"/>
+      <c r="F35" s="123"/>
+      <c r="G35" s="123"/>
+      <c r="H35" s="123"/>
+      <c r="I35" s="123"/>
+      <c r="J35" s="123"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="105" t="s">
+      <c r="A36" s="107" t="s">
         <v>886</v>
       </c>
-      <c r="B36" s="111"/>
-      <c r="C36" s="111"/>
-      <c r="D36" s="111"/>
-      <c r="E36" s="111"/>
-      <c r="F36" s="111"/>
-      <c r="G36" s="111"/>
-      <c r="H36" s="111"/>
-      <c r="I36" s="111"/>
-      <c r="J36" s="111"/>
+      <c r="B36" s="117"/>
+      <c r="C36" s="117"/>
+      <c r="D36" s="117"/>
+      <c r="E36" s="117"/>
+      <c r="F36" s="117"/>
+      <c r="G36" s="117"/>
+      <c r="H36" s="117"/>
+      <c r="I36" s="117"/>
+      <c r="J36" s="117"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C38" s="37"/>
-      <c r="D38" s="109" t="s">
+      <c r="D38" s="104" t="s">
         <v>869</v>
       </c>
       <c r="F38" s="37"/>
-      <c r="G38" s="109" t="s">
+      <c r="G38" s="104" t="s">
         <v>877</v>
       </c>
       <c r="I38" s="37"/>
-      <c r="J38" s="109" t="s">
+      <c r="J38" s="104" t="s">
         <v>876</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C39" s="55"/>
-      <c r="D39" s="110"/>
+      <c r="D39" s="105"/>
       <c r="F39" s="55"/>
-      <c r="G39" s="110"/>
+      <c r="G39" s="105"/>
       <c r="I39" s="55"/>
-      <c r="J39" s="110"/>
+      <c r="J39" s="105"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C40" s="55"/>
@@ -10368,25 +10389,25 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C41" s="38"/>
-      <c r="D41" s="109" t="s">
+      <c r="D41" s="104" t="s">
         <v>868</v>
       </c>
       <c r="F41" s="38"/>
-      <c r="G41" s="109" t="s">
+      <c r="G41" s="104" t="s">
         <v>878</v>
       </c>
       <c r="I41" s="38"/>
-      <c r="J41" s="109" t="s">
+      <c r="J41" s="104" t="s">
         <v>888</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C42" s="55"/>
-      <c r="D42" s="110"/>
+      <c r="D42" s="105"/>
       <c r="F42" s="55"/>
-      <c r="G42" s="110"/>
+      <c r="G42" s="105"/>
       <c r="I42" s="55"/>
-      <c r="J42" s="110"/>
+      <c r="J42" s="105"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C43" s="55"/>
@@ -10395,25 +10416,25 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C44" s="38"/>
-      <c r="D44" s="109" t="s">
+      <c r="D44" s="104" t="s">
         <v>867</v>
       </c>
       <c r="E44" s="39"/>
       <c r="F44" s="38"/>
-      <c r="G44" s="109" t="s">
+      <c r="G44" s="104" t="s">
         <v>879</v>
       </c>
       <c r="I44" s="38"/>
-      <c r="J44" s="109" t="s">
+      <c r="J44" s="104" t="s">
         <v>889</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B45" s="39"/>
-      <c r="D45" s="110"/>
+      <c r="D45" s="105"/>
       <c r="E45" s="39"/>
-      <c r="G45" s="110"/>
-      <c r="J45" s="110"/>
+      <c r="G45" s="105"/>
+      <c r="J45" s="105"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B46" s="39"/>
@@ -10422,12 +10443,12 @@
       <c r="I46" s="55"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="107" t="s">
+      <c r="A47" s="109" t="s">
         <v>3</v>
       </c>
       <c r="B47" s="38"/>
       <c r="C47" s="36"/>
-      <c r="D47" s="109" t="s">
+      <c r="D47" s="104" t="s">
         <v>873</v>
       </c>
       <c r="E47" s="38"/>
@@ -10437,15 +10458,15 @@
       </c>
       <c r="H47" s="38"/>
       <c r="I47" s="37"/>
-      <c r="J47" s="109" t="s">
+      <c r="J47" s="104" t="s">
         <v>838</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="108"/>
-      <c r="D48" s="110"/>
-      <c r="G48" s="110"/>
-      <c r="J48" s="110"/>
+      <c r="A48" s="110"/>
+      <c r="D48" s="105"/>
+      <c r="G48" s="105"/>
+      <c r="J48" s="105"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="45"/>
@@ -10454,35 +10475,35 @@
       <c r="A50" s="45"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="107" t="s">
+      <c r="A51" s="109" t="s">
         <v>9</v>
       </c>
       <c r="B51" s="36"/>
       <c r="C51" s="32"/>
-      <c r="D51" s="109" t="s">
+      <c r="D51" s="104" t="s">
         <v>874</v>
       </c>
       <c r="E51" s="36"/>
       <c r="F51" s="32"/>
-      <c r="G51" s="109" t="s">
+      <c r="G51" s="104" t="s">
         <v>875</v>
       </c>
       <c r="H51" s="36"/>
       <c r="I51" s="32"/>
-      <c r="J51" s="109" t="s">
+      <c r="J51" s="104" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="108"/>
+      <c r="A52" s="110"/>
       <c r="B52" s="54"/>
-      <c r="D52" s="110"/>
+      <c r="D52" s="105"/>
       <c r="E52" s="54"/>
       <c r="F52" s="54"/>
-      <c r="G52" s="110"/>
+      <c r="G52" s="105"/>
       <c r="H52" s="54"/>
       <c r="I52" s="54"/>
-      <c r="J52" s="110"/>
+      <c r="J52" s="105"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="45"/>
@@ -10494,28 +10515,28 @@
       <c r="A54" s="45"/>
       <c r="B54" s="39"/>
       <c r="C54" s="38"/>
-      <c r="D54" s="109" t="s">
+      <c r="D54" s="104" t="s">
         <v>871</v>
       </c>
       <c r="E54" s="39"/>
       <c r="F54" s="38"/>
-      <c r="G54" s="109" t="s">
+      <c r="G54" s="104" t="s">
         <v>883</v>
       </c>
       <c r="H54" s="39"/>
       <c r="I54" s="38"/>
-      <c r="J54" s="109" t="s">
+      <c r="J54" s="104" t="s">
         <v>880</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="45"/>
       <c r="B55" s="39"/>
-      <c r="D55" s="110"/>
+      <c r="D55" s="105"/>
       <c r="E55" s="39"/>
-      <c r="G55" s="110"/>
+      <c r="G55" s="105"/>
       <c r="H55" s="39"/>
-      <c r="J55" s="110"/>
+      <c r="J55" s="105"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="45"/>
@@ -10527,26 +10548,26 @@
       <c r="A57" s="45"/>
       <c r="B57" s="39"/>
       <c r="C57" s="38"/>
-      <c r="D57" s="109" t="s">
+      <c r="D57" s="104" t="s">
         <v>870</v>
       </c>
       <c r="F57" s="38"/>
-      <c r="G57" s="109" t="s">
+      <c r="G57" s="104" t="s">
         <v>884</v>
       </c>
       <c r="I57" s="38"/>
-      <c r="J57" s="109" t="s">
+      <c r="J57" s="104" t="s">
         <v>881</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="45"/>
       <c r="B58" s="39"/>
-      <c r="D58" s="110"/>
+      <c r="D58" s="105"/>
       <c r="F58" s="56"/>
-      <c r="G58" s="110"/>
+      <c r="G58" s="105"/>
       <c r="I58" s="56"/>
-      <c r="J58" s="110"/>
+      <c r="J58" s="105"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="45"/>
@@ -10558,54 +10579,54 @@
       <c r="A60" s="45"/>
       <c r="B60" s="39"/>
       <c r="C60" s="38"/>
-      <c r="D60" s="109" t="s">
+      <c r="D60" s="104" t="s">
         <v>872</v>
       </c>
       <c r="F60" s="38"/>
-      <c r="G60" s="109" t="s">
+      <c r="G60" s="104" t="s">
         <v>885</v>
       </c>
       <c r="I60" s="38"/>
-      <c r="J60" s="109" t="s">
+      <c r="J60" s="104" t="s">
         <v>882</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="45"/>
-      <c r="D61" s="110"/>
-      <c r="G61" s="110"/>
-      <c r="J61" s="110"/>
+      <c r="D61" s="105"/>
+      <c r="G61" s="105"/>
+      <c r="J61" s="105"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="45"/>
     </row>
     <row r="63" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="117" t="s">
+      <c r="A63" s="106" t="s">
         <v>890</v>
       </c>
-      <c r="B63" s="117"/>
-      <c r="C63" s="117"/>
-      <c r="D63" s="117"/>
-      <c r="E63" s="117"/>
-      <c r="F63" s="117"/>
-      <c r="G63" s="117"/>
-      <c r="H63" s="117"/>
-      <c r="I63" s="117"/>
-      <c r="J63" s="117"/>
+      <c r="B63" s="106"/>
+      <c r="C63" s="106"/>
+      <c r="D63" s="106"/>
+      <c r="E63" s="106"/>
+      <c r="F63" s="106"/>
+      <c r="G63" s="106"/>
+      <c r="H63" s="106"/>
+      <c r="I63" s="106"/>
+      <c r="J63" s="106"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="105" t="s">
+      <c r="A64" s="107" t="s">
         <v>940</v>
       </c>
-      <c r="B64" s="111"/>
-      <c r="C64" s="111"/>
-      <c r="D64" s="111"/>
-      <c r="E64" s="111"/>
-      <c r="F64" s="111"/>
-      <c r="G64" s="111"/>
-      <c r="H64" s="111"/>
-      <c r="I64" s="111"/>
-      <c r="J64" s="111"/>
+      <c r="B64" s="117"/>
+      <c r="C64" s="117"/>
+      <c r="D64" s="117"/>
+      <c r="E64" s="117"/>
+      <c r="F64" s="117"/>
+      <c r="G64" s="117"/>
+      <c r="H64" s="117"/>
+      <c r="I64" s="117"/>
+      <c r="J64" s="117"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="45"/>
@@ -10613,26 +10634,26 @@
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="45"/>
       <c r="C66" s="37"/>
-      <c r="D66" s="109" t="s">
+      <c r="D66" s="104" t="s">
         <v>891</v>
       </c>
       <c r="F66" s="32"/>
-      <c r="G66" s="109" t="s">
+      <c r="G66" s="104" t="s">
         <v>894</v>
       </c>
       <c r="I66" s="32"/>
-      <c r="J66" s="109" t="s">
+      <c r="J66" s="104" t="s">
         <v>896</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="45"/>
       <c r="B67" s="39"/>
-      <c r="D67" s="110"/>
+      <c r="D67" s="105"/>
       <c r="F67" s="55"/>
-      <c r="G67" s="110"/>
+      <c r="G67" s="105"/>
       <c r="I67" s="55"/>
-      <c r="J67" s="110"/>
+      <c r="J67" s="105"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="45"/>
@@ -10650,69 +10671,69 @@
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="107" t="s">
+      <c r="A69" s="109" t="s">
         <v>3</v>
       </c>
       <c r="B69" s="38"/>
       <c r="C69" s="32"/>
-      <c r="D69" s="109" t="s">
+      <c r="D69" s="104" t="s">
         <v>873</v>
       </c>
       <c r="E69" s="36"/>
       <c r="F69" s="36"/>
-      <c r="G69" s="109" t="s">
+      <c r="G69" s="104" t="s">
         <v>1</v>
       </c>
       <c r="H69" s="36"/>
       <c r="I69" s="38"/>
-      <c r="J69" s="109" t="s">
+      <c r="J69" s="104" t="s">
         <v>838</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="108"/>
-      <c r="D70" s="110"/>
-      <c r="G70" s="110"/>
-      <c r="J70" s="110"/>
+      <c r="A70" s="110"/>
+      <c r="D70" s="105"/>
+      <c r="G70" s="105"/>
+      <c r="J70" s="105"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="45"/>
-      <c r="J71" s="121" t="s">
+      <c r="J71" s="112" t="s">
         <v>898</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="45"/>
-      <c r="J72" s="122"/>
+      <c r="J72" s="113"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="107" t="s">
+      <c r="A73" s="109" t="s">
         <v>9</v>
       </c>
       <c r="B73" s="36"/>
       <c r="C73" s="32"/>
-      <c r="D73" s="109" t="s">
+      <c r="D73" s="104" t="s">
         <v>874</v>
       </c>
       <c r="E73" s="36"/>
       <c r="F73" s="37"/>
-      <c r="G73" s="109" t="s">
+      <c r="G73" s="104" t="s">
         <v>875</v>
       </c>
       <c r="H73" s="36"/>
       <c r="I73" s="32"/>
-      <c r="J73" s="109" t="s">
+      <c r="J73" s="104" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="108"/>
+      <c r="A74" s="110"/>
       <c r="C74" s="56"/>
-      <c r="D74" s="110"/>
+      <c r="D74" s="105"/>
       <c r="F74" s="56"/>
-      <c r="G74" s="110"/>
+      <c r="G74" s="105"/>
       <c r="I74" s="56"/>
-      <c r="J74" s="110"/>
+      <c r="J74" s="105"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="45"/>
@@ -10724,86 +10745,86 @@
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="45"/>
       <c r="C76" s="38"/>
-      <c r="D76" s="109" t="s">
+      <c r="D76" s="104" t="s">
         <v>892</v>
       </c>
       <c r="F76" s="36"/>
-      <c r="G76" s="123" t="s">
+      <c r="G76" s="116" t="s">
         <v>893</v>
       </c>
       <c r="H76" s="55"/>
       <c r="I76" s="36"/>
-      <c r="J76" s="109" t="s">
+      <c r="J76" s="104" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="45"/>
-      <c r="D77" s="110"/>
-      <c r="G77" s="110"/>
-      <c r="J77" s="110"/>
+      <c r="D77" s="105"/>
+      <c r="G77" s="105"/>
+      <c r="J77" s="105"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="45"/>
-      <c r="D78" s="119" t="s">
+      <c r="D78" s="114" t="s">
         <v>895</v>
       </c>
-      <c r="G78" s="119" t="s">
+      <c r="G78" s="114" t="s">
         <v>895</v>
       </c>
-      <c r="J78" s="119" t="s">
+      <c r="J78" s="114" t="s">
         <v>895</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="45"/>
-      <c r="D79" s="120"/>
-      <c r="G79" s="120"/>
-      <c r="J79" s="120"/>
+      <c r="D79" s="115"/>
+      <c r="G79" s="115"/>
+      <c r="J79" s="115"/>
     </row>
     <row r="81" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="117" t="s">
+      <c r="A81" s="106" t="s">
         <v>899</v>
       </c>
-      <c r="B81" s="117"/>
-      <c r="C81" s="117"/>
-      <c r="D81" s="117"/>
-      <c r="E81" s="117"/>
-      <c r="F81" s="117"/>
-      <c r="G81" s="117"/>
-      <c r="H81" s="117"/>
-      <c r="I81" s="117"/>
-      <c r="J81" s="117"/>
+      <c r="B81" s="106"/>
+      <c r="C81" s="106"/>
+      <c r="D81" s="106"/>
+      <c r="E81" s="106"/>
+      <c r="F81" s="106"/>
+      <c r="G81" s="106"/>
+      <c r="H81" s="106"/>
+      <c r="I81" s="106"/>
+      <c r="J81" s="106"/>
     </row>
     <row r="82" spans="1:119" x14ac:dyDescent="0.25">
-      <c r="A82" s="105" t="s">
+      <c r="A82" s="107" t="s">
         <v>909</v>
       </c>
-      <c r="B82" s="105"/>
-      <c r="C82" s="105"/>
-      <c r="D82" s="105"/>
-      <c r="E82" s="105"/>
-      <c r="F82" s="105"/>
-      <c r="G82" s="105"/>
-      <c r="H82" s="105"/>
-      <c r="I82" s="105"/>
-      <c r="J82" s="105"/>
+      <c r="B82" s="107"/>
+      <c r="C82" s="107"/>
+      <c r="D82" s="107"/>
+      <c r="E82" s="107"/>
+      <c r="F82" s="107"/>
+      <c r="G82" s="107"/>
+      <c r="H82" s="107"/>
+      <c r="I82" s="107"/>
+      <c r="J82" s="107"/>
     </row>
     <row r="84" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="40"/>
-      <c r="D84" s="109" t="s">
+      <c r="D84" s="104" t="s">
         <v>907</v>
       </c>
       <c r="E84" s="7"/>
       <c r="F84" s="40"/>
-      <c r="G84" s="109" t="s">
+      <c r="G84" s="104" t="s">
         <v>910</v>
       </c>
       <c r="H84" s="41"/>
       <c r="I84" s="42"/>
-      <c r="J84" s="109" t="s">
+      <c r="J84" s="104" t="s">
         <v>912</v>
       </c>
     </row>
@@ -10811,13 +10832,13 @@
       <c r="A85" s="7"/>
       <c r="B85" s="43"/>
       <c r="C85" s="7"/>
-      <c r="D85" s="110"/>
+      <c r="D85" s="105"/>
       <c r="E85" s="43"/>
       <c r="F85" s="7"/>
-      <c r="G85" s="110"/>
+      <c r="G85" s="105"/>
       <c r="H85" s="7"/>
       <c r="I85" s="7"/>
-      <c r="J85" s="110"/>
+      <c r="J85" s="105"/>
     </row>
     <row r="86" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A86" s="7"/>
@@ -10832,22 +10853,22 @@
       <c r="J86" s="7"/>
     </row>
     <row r="87" spans="1:119" x14ac:dyDescent="0.25">
-      <c r="A87" s="107" t="s">
+      <c r="A87" s="109" t="s">
         <v>908</v>
       </c>
       <c r="B87" s="41"/>
       <c r="C87" s="44"/>
-      <c r="D87" s="109" t="s">
+      <c r="D87" s="104" t="s">
         <v>906</v>
       </c>
       <c r="E87" s="44"/>
       <c r="F87" s="42"/>
-      <c r="G87" s="109" t="s">
+      <c r="G87" s="104" t="s">
         <v>911</v>
       </c>
       <c r="H87" s="41"/>
       <c r="I87" s="42"/>
-      <c r="J87" s="109" t="s">
+      <c r="J87" s="104" t="s">
         <v>913</v>
       </c>
       <c r="K87" s="1"/>
@@ -10858,16 +10879,16 @@
       <c r="P87" s="1"/>
     </row>
     <row r="88" spans="1:119" x14ac:dyDescent="0.25">
-      <c r="A88" s="108"/>
+      <c r="A88" s="110"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
-      <c r="D88" s="110"/>
+      <c r="D88" s="105"/>
       <c r="E88" s="7"/>
       <c r="F88" s="7"/>
-      <c r="G88" s="110"/>
+      <c r="G88" s="105"/>
       <c r="H88" s="7"/>
       <c r="I88" s="7"/>
-      <c r="J88" s="110"/>
+      <c r="J88" s="105"/>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
@@ -10885,7 +10906,7 @@
       <c r="G89" s="13"/>
       <c r="H89" s="13"/>
       <c r="I89" s="13"/>
-      <c r="J89" s="121" t="s">
+      <c r="J89" s="112" t="s">
         <v>898</v>
       </c>
       <c r="K89" s="1"/>
@@ -10905,7 +10926,7 @@
       <c r="G90" s="46"/>
       <c r="H90" s="46"/>
       <c r="I90" s="46"/>
-      <c r="J90" s="122"/>
+      <c r="J90" s="113"/>
       <c r="K90" s="46"/>
       <c r="L90" s="46"/>
       <c r="M90" s="46"/>
@@ -11017,22 +11038,22 @@
       <c r="DO90" s="46"/>
     </row>
     <row r="91" spans="1:119" s="48" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="107" t="s">
+      <c r="A91" s="109" t="s">
         <v>892</v>
       </c>
       <c r="B91" s="47"/>
       <c r="C91" s="50"/>
-      <c r="D91" s="109" t="s">
+      <c r="D91" s="104" t="s">
         <v>905</v>
       </c>
       <c r="E91" s="47"/>
       <c r="F91" s="50"/>
-      <c r="G91" s="109" t="s">
+      <c r="G91" s="104" t="s">
         <v>900</v>
       </c>
       <c r="H91" s="47"/>
       <c r="I91" s="50"/>
-      <c r="J91" s="109" t="s">
+      <c r="J91" s="104" t="s">
         <v>901</v>
       </c>
       <c r="K91" s="46"/>
@@ -11146,16 +11167,16 @@
       <c r="DO91" s="46"/>
     </row>
     <row r="92" spans="1:119" s="48" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="108"/>
+      <c r="A92" s="110"/>
       <c r="B92" s="46"/>
       <c r="C92" s="60"/>
-      <c r="D92" s="110"/>
+      <c r="D92" s="105"/>
       <c r="E92" s="46"/>
       <c r="F92" s="60"/>
-      <c r="G92" s="110"/>
+      <c r="G92" s="105"/>
       <c r="H92" s="46"/>
       <c r="I92" s="60"/>
-      <c r="J92" s="110"/>
+      <c r="J92" s="105"/>
       <c r="K92" s="46"/>
       <c r="L92" s="46"/>
       <c r="M92" s="46"/>
@@ -11391,17 +11412,17 @@
       <c r="A94" s="46"/>
       <c r="B94" s="46"/>
       <c r="C94" s="51"/>
-      <c r="D94" s="109" t="s">
+      <c r="D94" s="104" t="s">
         <v>904</v>
       </c>
       <c r="E94" s="46"/>
       <c r="F94" s="47"/>
-      <c r="G94" s="109" t="s">
+      <c r="G94" s="104" t="s">
         <v>903</v>
       </c>
       <c r="H94" s="46"/>
       <c r="I94" s="47"/>
-      <c r="J94" s="109" t="s">
+      <c r="J94" s="104" t="s">
         <v>902</v>
       </c>
       <c r="K94" s="46"/>
@@ -11518,13 +11539,13 @@
       <c r="A95" s="46"/>
       <c r="B95" s="46"/>
       <c r="C95" s="46"/>
-      <c r="D95" s="110"/>
+      <c r="D95" s="105"/>
       <c r="E95" s="46"/>
       <c r="F95" s="46"/>
-      <c r="G95" s="110"/>
+      <c r="G95" s="105"/>
       <c r="H95" s="46"/>
       <c r="I95" s="46"/>
-      <c r="J95" s="110"/>
+      <c r="J95" s="105"/>
       <c r="K95" s="46"/>
       <c r="L95" s="46"/>
       <c r="M95" s="46"/>
@@ -11654,18 +11675,18 @@
       <c r="P96" s="1"/>
     </row>
     <row r="97" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="117" t="s">
+      <c r="A97" s="106" t="s">
         <v>914</v>
       </c>
-      <c r="B97" s="117"/>
-      <c r="C97" s="117"/>
-      <c r="D97" s="117"/>
-      <c r="E97" s="117"/>
-      <c r="F97" s="117"/>
-      <c r="G97" s="117"/>
-      <c r="H97" s="117"/>
-      <c r="I97" s="117"/>
-      <c r="J97" s="117"/>
+      <c r="B97" s="106"/>
+      <c r="C97" s="106"/>
+      <c r="D97" s="106"/>
+      <c r="E97" s="106"/>
+      <c r="F97" s="106"/>
+      <c r="G97" s="106"/>
+      <c r="H97" s="106"/>
+      <c r="I97" s="106"/>
+      <c r="J97" s="106"/>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="1"/>
@@ -11674,18 +11695,18 @@
       <c r="P97" s="1"/>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A98" s="105" t="s">
+      <c r="A98" s="107" t="s">
         <v>915</v>
       </c>
-      <c r="B98" s="105"/>
-      <c r="C98" s="105"/>
-      <c r="D98" s="105"/>
-      <c r="E98" s="105"/>
-      <c r="F98" s="105"/>
-      <c r="G98" s="105"/>
-      <c r="H98" s="105"/>
-      <c r="I98" s="105"/>
-      <c r="J98" s="105"/>
+      <c r="B98" s="107"/>
+      <c r="C98" s="107"/>
+      <c r="D98" s="107"/>
+      <c r="E98" s="107"/>
+      <c r="F98" s="107"/>
+      <c r="G98" s="107"/>
+      <c r="H98" s="107"/>
+      <c r="I98" s="107"/>
+      <c r="J98" s="107"/>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
       <c r="M98" s="1"/>
@@ -11706,15 +11727,15 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C100" s="37"/>
-      <c r="D100" s="109" t="s">
+      <c r="D100" s="104" t="s">
         <v>916</v>
       </c>
       <c r="F100" s="37"/>
-      <c r="G100" s="109" t="s">
+      <c r="G100" s="104" t="s">
         <v>922</v>
       </c>
       <c r="I100" s="37"/>
-      <c r="J100" s="109" t="s">
+      <c r="J100" s="104" t="s">
         <v>933</v>
       </c>
       <c r="K100" s="1"/>
@@ -11726,11 +11747,11 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C101" s="55"/>
-      <c r="D101" s="110"/>
+      <c r="D101" s="105"/>
       <c r="F101" s="55"/>
-      <c r="G101" s="110"/>
+      <c r="G101" s="105"/>
       <c r="I101" s="55"/>
-      <c r="J101" s="110"/>
+      <c r="J101" s="105"/>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
@@ -11745,25 +11766,25 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C103" s="38"/>
-      <c r="D103" s="109" t="s">
+      <c r="D103" s="104" t="s">
         <v>917</v>
       </c>
       <c r="F103" s="38"/>
-      <c r="G103" s="109" t="s">
+      <c r="G103" s="104" t="s">
         <v>923</v>
       </c>
       <c r="I103" s="38"/>
-      <c r="J103" s="109" t="s">
+      <c r="J103" s="104" t="s">
         <v>932</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C104" s="55"/>
-      <c r="D104" s="110"/>
+      <c r="D104" s="105"/>
       <c r="F104" s="55"/>
-      <c r="G104" s="110"/>
+      <c r="G104" s="105"/>
       <c r="I104" s="55"/>
-      <c r="J104" s="110"/>
+      <c r="J104" s="105"/>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C105" s="55"/>
@@ -11772,25 +11793,25 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C106" s="38"/>
-      <c r="D106" s="109" t="s">
+      <c r="D106" s="104" t="s">
         <v>918</v>
       </c>
       <c r="F106" s="38"/>
-      <c r="G106" s="109" t="s">
+      <c r="G106" s="104" t="s">
         <v>924</v>
       </c>
       <c r="I106" s="38"/>
-      <c r="J106" s="109" t="s">
+      <c r="J106" s="104" t="s">
         <v>931</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B107" s="39"/>
-      <c r="D107" s="110"/>
+      <c r="D107" s="105"/>
       <c r="E107" s="39"/>
-      <c r="G107" s="110"/>
+      <c r="G107" s="105"/>
       <c r="H107" s="39"/>
-      <c r="J107" s="110"/>
+      <c r="J107" s="105"/>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B108" s="39"/>
@@ -11798,69 +11819,69 @@
       <c r="H108" s="39"/>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A109" s="107" t="s">
+      <c r="A109" s="109" t="s">
         <v>891</v>
       </c>
       <c r="B109" s="38"/>
       <c r="C109" s="36"/>
-      <c r="D109" s="109" t="s">
+      <c r="D109" s="104" t="s">
         <v>906</v>
       </c>
       <c r="E109" s="38"/>
       <c r="F109" s="36"/>
-      <c r="G109" s="109" t="s">
+      <c r="G109" s="104" t="s">
         <v>911</v>
       </c>
       <c r="H109" s="38"/>
       <c r="I109" s="36"/>
-      <c r="J109" s="109" t="s">
+      <c r="J109" s="104" t="s">
         <v>913</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A110" s="108"/>
-      <c r="D110" s="110"/>
-      <c r="G110" s="110"/>
-      <c r="J110" s="110"/>
+      <c r="A110" s="110"/>
+      <c r="D110" s="105"/>
+      <c r="G110" s="105"/>
+      <c r="J110" s="105"/>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="45"/>
-      <c r="J111" s="121" t="s">
+      <c r="J111" s="112" t="s">
         <v>898</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="45"/>
-      <c r="J112" s="122"/>
+      <c r="J112" s="113"/>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A113" s="107" t="s">
+      <c r="A113" s="109" t="s">
         <v>892</v>
       </c>
       <c r="B113" s="36"/>
       <c r="C113" s="32"/>
-      <c r="D113" s="109" t="s">
+      <c r="D113" s="104" t="s">
         <v>905</v>
       </c>
       <c r="E113" s="36"/>
       <c r="F113" s="32"/>
-      <c r="G113" s="109" t="s">
+      <c r="G113" s="104" t="s">
         <v>900</v>
       </c>
       <c r="H113" s="36"/>
       <c r="I113" s="32"/>
-      <c r="J113" s="109" t="s">
+      <c r="J113" s="104" t="s">
         <v>901</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A114" s="108"/>
+      <c r="A114" s="110"/>
       <c r="B114" s="54"/>
-      <c r="D114" s="110"/>
+      <c r="D114" s="105"/>
       <c r="E114" s="54"/>
-      <c r="G114" s="110"/>
+      <c r="G114" s="105"/>
       <c r="H114" s="54"/>
-      <c r="J114" s="110"/>
+      <c r="J114" s="105"/>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B115" s="39"/>
@@ -11870,27 +11891,27 @@
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B116" s="39"/>
       <c r="C116" s="38"/>
-      <c r="D116" s="109" t="s">
+      <c r="D116" s="104" t="s">
         <v>919</v>
       </c>
       <c r="E116" s="39"/>
       <c r="F116" s="38"/>
-      <c r="G116" s="109" t="s">
+      <c r="G116" s="104" t="s">
         <v>925</v>
       </c>
       <c r="H116" s="39"/>
       <c r="I116" s="38"/>
-      <c r="J116" s="109" t="s">
+      <c r="J116" s="104" t="s">
         <v>927</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B117" s="39"/>
-      <c r="D117" s="110"/>
+      <c r="D117" s="105"/>
       <c r="E117" s="39"/>
-      <c r="G117" s="110"/>
+      <c r="G117" s="105"/>
       <c r="H117" s="39"/>
-      <c r="J117" s="110"/>
+      <c r="J117" s="105"/>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B118" s="39"/>
@@ -11900,27 +11921,27 @@
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B119" s="39"/>
       <c r="C119" s="38"/>
-      <c r="D119" s="109" t="s">
+      <c r="D119" s="104" t="s">
         <v>920</v>
       </c>
       <c r="E119" s="39"/>
       <c r="F119" s="38"/>
-      <c r="G119" s="109" t="s">
+      <c r="G119" s="104" t="s">
         <v>926</v>
       </c>
       <c r="H119" s="39"/>
       <c r="I119" s="38"/>
-      <c r="J119" s="109" t="s">
+      <c r="J119" s="104" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B120" s="39"/>
-      <c r="D120" s="110"/>
+      <c r="D120" s="105"/>
       <c r="E120" s="39"/>
-      <c r="G120" s="110"/>
+      <c r="G120" s="105"/>
       <c r="H120" s="39"/>
-      <c r="J120" s="110"/>
+      <c r="J120" s="105"/>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B121" s="39"/>
@@ -11930,93 +11951,93 @@
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B122" s="39"/>
       <c r="C122" s="38"/>
-      <c r="D122" s="109" t="s">
+      <c r="D122" s="104" t="s">
         <v>921</v>
       </c>
       <c r="E122" s="39"/>
       <c r="F122" s="38"/>
-      <c r="G122" s="109" t="s">
+      <c r="G122" s="104" t="s">
         <v>930</v>
       </c>
       <c r="H122" s="39"/>
       <c r="I122" s="38"/>
-      <c r="J122" s="109" t="s">
+      <c r="J122" s="104" t="s">
         <v>929</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D123" s="110"/>
-      <c r="G123" s="110"/>
-      <c r="J123" s="110"/>
+      <c r="D123" s="105"/>
+      <c r="G123" s="105"/>
+      <c r="J123" s="105"/>
     </row>
     <row r="125" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="117" t="s">
+      <c r="A125" s="106" t="s">
         <v>934</v>
       </c>
-      <c r="B125" s="117"/>
-      <c r="C125" s="117"/>
-      <c r="D125" s="117"/>
-      <c r="E125" s="117"/>
-      <c r="F125" s="117"/>
-      <c r="G125" s="117"/>
-      <c r="H125" s="117"/>
-      <c r="I125" s="117"/>
-      <c r="J125" s="117"/>
+      <c r="B125" s="106"/>
+      <c r="C125" s="106"/>
+      <c r="D125" s="106"/>
+      <c r="E125" s="106"/>
+      <c r="F125" s="106"/>
+      <c r="G125" s="106"/>
+      <c r="H125" s="106"/>
+      <c r="I125" s="106"/>
+      <c r="J125" s="106"/>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A126" s="105" t="s">
+      <c r="A126" s="107" t="s">
         <v>937</v>
       </c>
-      <c r="B126" s="105"/>
-      <c r="C126" s="105"/>
-      <c r="D126" s="105"/>
-      <c r="E126" s="105"/>
-      <c r="F126" s="105"/>
-      <c r="G126" s="105"/>
-      <c r="H126" s="105"/>
-      <c r="I126" s="105"/>
-      <c r="J126" s="105"/>
+      <c r="B126" s="107"/>
+      <c r="C126" s="107"/>
+      <c r="D126" s="107"/>
+      <c r="E126" s="107"/>
+      <c r="F126" s="107"/>
+      <c r="G126" s="107"/>
+      <c r="H126" s="107"/>
+      <c r="I126" s="107"/>
+      <c r="J126" s="107"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A127" s="124"/>
-      <c r="B127" s="124"/>
-      <c r="C127" s="124"/>
-      <c r="D127" s="124"/>
-      <c r="E127" s="124"/>
-      <c r="F127" s="124"/>
-      <c r="G127" s="124"/>
-      <c r="H127" s="124"/>
-      <c r="I127" s="124"/>
-      <c r="J127" s="124"/>
+      <c r="A127" s="111"/>
+      <c r="B127" s="111"/>
+      <c r="C127" s="111"/>
+      <c r="D127" s="111"/>
+      <c r="E127" s="111"/>
+      <c r="F127" s="111"/>
+      <c r="G127" s="111"/>
+      <c r="H127" s="111"/>
+      <c r="I127" s="111"/>
+      <c r="J127" s="111"/>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" s="107" t="s">
+      <c r="A128" s="109" t="s">
         <v>892</v>
       </c>
       <c r="B128" s="36"/>
       <c r="C128" s="32"/>
-      <c r="D128" s="109" t="s">
+      <c r="D128" s="104" t="s">
         <v>905</v>
       </c>
       <c r="E128" s="36"/>
       <c r="F128" s="32"/>
-      <c r="G128" s="109" t="s">
+      <c r="G128" s="104" t="s">
         <v>900</v>
       </c>
       <c r="H128" s="36"/>
       <c r="I128" s="32"/>
-      <c r="J128" s="109" t="s">
+      <c r="J128" s="104" t="s">
         <v>901</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" s="108"/>
+      <c r="A129" s="110"/>
       <c r="B129" s="54"/>
-      <c r="D129" s="110"/>
+      <c r="D129" s="105"/>
       <c r="E129" s="54"/>
-      <c r="G129" s="110"/>
+      <c r="G129" s="105"/>
       <c r="H129" s="54"/>
-      <c r="J129" s="110"/>
+      <c r="J129" s="105"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C130" s="55"/>
@@ -12028,22 +12049,22 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C131" s="36"/>
-      <c r="D131" s="109" t="s">
+      <c r="D131" s="104" t="s">
         <v>935</v>
       </c>
       <c r="F131" s="36"/>
-      <c r="G131" s="109" t="s">
+      <c r="G131" s="104" t="s">
         <v>935</v>
       </c>
       <c r="I131" s="36"/>
-      <c r="J131" s="109" t="s">
+      <c r="J131" s="104" t="s">
         <v>935</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D132" s="110"/>
-      <c r="G132" s="110"/>
-      <c r="J132" s="110"/>
+      <c r="D132" s="105"/>
+      <c r="G132" s="105"/>
+      <c r="J132" s="105"/>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="32"/>
@@ -12058,133 +12079,239 @@
       <c r="J133" s="32"/>
     </row>
     <row r="134" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="117" t="s">
+      <c r="A134" s="106" t="s">
         <v>941</v>
       </c>
-      <c r="B134" s="117"/>
-      <c r="C134" s="117"/>
-      <c r="D134" s="117"/>
-      <c r="E134" s="117"/>
-      <c r="F134" s="117"/>
-      <c r="G134" s="117"/>
-      <c r="H134" s="117"/>
-      <c r="I134" s="117"/>
-      <c r="J134" s="117"/>
+      <c r="B134" s="106"/>
+      <c r="C134" s="106"/>
+      <c r="D134" s="106"/>
+      <c r="E134" s="106"/>
+      <c r="F134" s="106"/>
+      <c r="G134" s="106"/>
+      <c r="H134" s="106"/>
+      <c r="I134" s="106"/>
+      <c r="J134" s="106"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" s="105" t="s">
+      <c r="A135" s="107" t="s">
         <v>942</v>
       </c>
-      <c r="B135" s="105"/>
-      <c r="C135" s="105"/>
-      <c r="D135" s="105"/>
-      <c r="E135" s="105"/>
-      <c r="F135" s="105"/>
-      <c r="G135" s="105"/>
-      <c r="H135" s="105"/>
-      <c r="I135" s="105"/>
-      <c r="J135" s="105"/>
+      <c r="B135" s="107"/>
+      <c r="C135" s="107"/>
+      <c r="D135" s="107"/>
+      <c r="E135" s="107"/>
+      <c r="F135" s="107"/>
+      <c r="G135" s="107"/>
+      <c r="H135" s="107"/>
+      <c r="I135" s="107"/>
+      <c r="J135" s="107"/>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A136" s="128" t="s">
+      <c r="A136" s="108" t="s">
         <v>943</v>
       </c>
-      <c r="B136" s="128"/>
-      <c r="C136" s="128"/>
-      <c r="D136" s="128"/>
-      <c r="E136" s="128"/>
-      <c r="F136" s="128"/>
-      <c r="G136" s="128"/>
-      <c r="H136" s="128"/>
-      <c r="I136" s="128"/>
-      <c r="J136" s="128"/>
+      <c r="B136" s="108"/>
+      <c r="C136" s="108"/>
+      <c r="D136" s="108"/>
+      <c r="E136" s="108"/>
+      <c r="F136" s="108"/>
+      <c r="G136" s="108"/>
+      <c r="H136" s="108"/>
+      <c r="I136" s="108"/>
+      <c r="J136" s="108"/>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A137" s="125"/>
-      <c r="B137" s="125"/>
-      <c r="C137" s="125"/>
-      <c r="D137" s="125"/>
-      <c r="E137" s="125"/>
-      <c r="F137" s="125"/>
-      <c r="G137" s="125"/>
-      <c r="H137" s="125"/>
-      <c r="I137" s="125"/>
-      <c r="J137" s="125"/>
+      <c r="A137" s="101"/>
+      <c r="B137" s="101"/>
+      <c r="C137" s="101"/>
+      <c r="D137" s="101"/>
+      <c r="E137" s="101"/>
+      <c r="F137" s="101"/>
+      <c r="G137" s="101"/>
+      <c r="H137" s="101"/>
+      <c r="I137" s="101"/>
+      <c r="J137" s="101"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A138" s="126"/>
-      <c r="B138" s="126"/>
-      <c r="C138" s="126"/>
-      <c r="D138" s="126"/>
-      <c r="E138" s="126"/>
-      <c r="F138" s="126"/>
-      <c r="G138" s="126"/>
-      <c r="H138" s="126"/>
-      <c r="I138" s="126"/>
-      <c r="J138" s="126"/>
+      <c r="A138" s="102"/>
+      <c r="B138" s="102"/>
+      <c r="C138" s="102"/>
+      <c r="D138" s="102"/>
+      <c r="E138" s="102"/>
+      <c r="F138" s="102"/>
+      <c r="G138" s="102"/>
+      <c r="H138" s="102"/>
+      <c r="I138" s="102"/>
+      <c r="J138" s="102"/>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A139" s="125"/>
-      <c r="B139" s="125"/>
-      <c r="C139" s="125"/>
-      <c r="D139" s="125"/>
-      <c r="E139" s="125"/>
-      <c r="F139" s="125"/>
-      <c r="G139" s="125"/>
-      <c r="H139" s="125"/>
-      <c r="I139" s="125"/>
-      <c r="J139" s="125"/>
+      <c r="A139" s="101"/>
+      <c r="B139" s="101"/>
+      <c r="C139" s="101"/>
+      <c r="D139" s="101"/>
+      <c r="E139" s="101"/>
+      <c r="F139" s="101"/>
+      <c r="G139" s="101"/>
+      <c r="H139" s="101"/>
+      <c r="I139" s="101"/>
+      <c r="J139" s="101"/>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A140" s="126"/>
-      <c r="B140" s="126"/>
-      <c r="C140" s="126"/>
-      <c r="D140" s="126"/>
-      <c r="E140" s="126"/>
-      <c r="F140" s="126"/>
-      <c r="G140" s="126"/>
-      <c r="H140" s="126"/>
-      <c r="I140" s="126"/>
-      <c r="J140" s="126"/>
+      <c r="A140" s="102"/>
+      <c r="B140" s="102"/>
+      <c r="C140" s="102"/>
+      <c r="D140" s="102"/>
+      <c r="E140" s="102"/>
+      <c r="F140" s="102"/>
+      <c r="G140" s="102"/>
+      <c r="H140" s="102"/>
+      <c r="I140" s="102"/>
+      <c r="J140" s="102"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" s="125"/>
-      <c r="B141" s="125"/>
-      <c r="C141" s="125"/>
-      <c r="D141" s="125"/>
-      <c r="E141" s="125"/>
-      <c r="F141" s="125"/>
-      <c r="G141" s="125"/>
-      <c r="H141" s="125"/>
-      <c r="I141" s="125"/>
-      <c r="J141" s="125"/>
+      <c r="A141" s="101"/>
+      <c r="B141" s="101"/>
+      <c r="C141" s="101"/>
+      <c r="D141" s="101"/>
+      <c r="E141" s="101"/>
+      <c r="F141" s="101"/>
+      <c r="G141" s="101"/>
+      <c r="H141" s="101"/>
+      <c r="I141" s="101"/>
+      <c r="J141" s="101"/>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A142" s="127"/>
-      <c r="B142" s="127"/>
-      <c r="C142" s="127"/>
-      <c r="D142" s="127"/>
-      <c r="E142" s="127"/>
-      <c r="F142" s="127"/>
-      <c r="G142" s="127"/>
-      <c r="H142" s="127"/>
-      <c r="I142" s="127"/>
-      <c r="J142" s="127"/>
+      <c r="A142" s="103"/>
+      <c r="B142" s="103"/>
+      <c r="C142" s="103"/>
+      <c r="D142" s="103"/>
+      <c r="E142" s="103"/>
+      <c r="F142" s="103"/>
+      <c r="G142" s="103"/>
+      <c r="H142" s="103"/>
+      <c r="I142" s="103"/>
+      <c r="J142" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="154">
-    <mergeCell ref="A139:J139"/>
-    <mergeCell ref="A140:J140"/>
-    <mergeCell ref="A141:J141"/>
-    <mergeCell ref="A142:J142"/>
-    <mergeCell ref="D131:D132"/>
-    <mergeCell ref="G131:G132"/>
-    <mergeCell ref="J131:J132"/>
-    <mergeCell ref="A134:J134"/>
-    <mergeCell ref="A135:J135"/>
-    <mergeCell ref="A136:J136"/>
-    <mergeCell ref="A137:J137"/>
-    <mergeCell ref="A138:J138"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A64:J64"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="J57:J58"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="J73:J74"/>
+    <mergeCell ref="J69:J70"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="J66:J67"/>
+    <mergeCell ref="J71:J72"/>
+    <mergeCell ref="J76:J77"/>
+    <mergeCell ref="J78:J79"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="D91:D92"/>
+    <mergeCell ref="G91:G92"/>
+    <mergeCell ref="A81:J81"/>
+    <mergeCell ref="A82:J82"/>
+    <mergeCell ref="J91:J92"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="G94:G95"/>
+    <mergeCell ref="J94:J95"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="G103:G104"/>
+    <mergeCell ref="G106:G107"/>
+    <mergeCell ref="J89:J90"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="J84:J85"/>
+    <mergeCell ref="D119:D120"/>
+    <mergeCell ref="A97:J97"/>
+    <mergeCell ref="A98:J98"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="D103:D104"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="J100:J101"/>
+    <mergeCell ref="J103:J104"/>
+    <mergeCell ref="J106:J107"/>
     <mergeCell ref="A125:J125"/>
     <mergeCell ref="A126:J126"/>
     <mergeCell ref="A128:A129"/>
@@ -12209,124 +12336,18 @@
     <mergeCell ref="A113:A114"/>
     <mergeCell ref="D113:D114"/>
     <mergeCell ref="D116:D117"/>
-    <mergeCell ref="D119:D120"/>
-    <mergeCell ref="A97:J97"/>
-    <mergeCell ref="A98:J98"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="D103:D104"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="J100:J101"/>
-    <mergeCell ref="J103:J104"/>
-    <mergeCell ref="J106:J107"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="G94:G95"/>
-    <mergeCell ref="J94:J95"/>
-    <mergeCell ref="G100:G101"/>
-    <mergeCell ref="G103:G104"/>
-    <mergeCell ref="G106:G107"/>
-    <mergeCell ref="J89:J90"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="J84:J85"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="D91:D92"/>
-    <mergeCell ref="G91:G92"/>
-    <mergeCell ref="A81:J81"/>
-    <mergeCell ref="A82:J82"/>
-    <mergeCell ref="J91:J92"/>
-    <mergeCell ref="J73:J74"/>
-    <mergeCell ref="J69:J70"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="J66:J67"/>
-    <mergeCell ref="J71:J72"/>
-    <mergeCell ref="J76:J77"/>
-    <mergeCell ref="J78:J79"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="A63:J63"/>
-    <mergeCell ref="A64:J64"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="G57:G58"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="J54:J55"/>
-    <mergeCell ref="J57:J58"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A139:J139"/>
+    <mergeCell ref="A140:J140"/>
+    <mergeCell ref="A141:J141"/>
+    <mergeCell ref="A142:J142"/>
+    <mergeCell ref="D131:D132"/>
+    <mergeCell ref="G131:G132"/>
+    <mergeCell ref="J131:J132"/>
+    <mergeCell ref="A134:J134"/>
+    <mergeCell ref="A135:J135"/>
+    <mergeCell ref="A136:J136"/>
+    <mergeCell ref="A137:J137"/>
+    <mergeCell ref="A138:J138"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12641,7 +12662,7 @@
       </c>
       <c r="F17" s="82">
         <f>COUNTIF('New Trees'!S$6:S$153,"In-Game")+COUNTIF('Updated Trees'!T$6:T$50,"In-Game")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -12681,7 +12702,7 @@
       </c>
       <c r="F19" s="82">
         <f>COUNTIF('Updated Trees'!T$6:T$50,"In-Game")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -13189,29 +13210,29 @@
       <c r="U1" s="98"/>
     </row>
     <row r="2" spans="1:21" ht="20.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="166" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="159"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="159"/>
-      <c r="P2" s="159"/>
-      <c r="Q2" s="159"/>
-      <c r="R2" s="159"/>
-      <c r="S2" s="159"/>
-      <c r="T2" s="159"/>
-      <c r="U2" s="159"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
+      <c r="L2" s="166"/>
+      <c r="M2" s="166"/>
+      <c r="N2" s="166"/>
+      <c r="O2" s="166"/>
+      <c r="P2" s="166"/>
+      <c r="Q2" s="166"/>
+      <c r="R2" s="166"/>
+      <c r="S2" s="166"/>
+      <c r="T2" s="166"/>
+      <c r="U2" s="166"/>
     </row>
     <row r="3" spans="1:21" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="153" t="s">
@@ -13613,7 +13634,7 @@
       </c>
       <c r="H17" s="82">
         <f>COUNTIF('New Trees'!S$6:S$153,"In-Game")+COUNTIF('Updated Trees'!T$6:T$50,"In-Game")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -13667,7 +13688,7 @@
       </c>
       <c r="H19" s="82">
         <f>COUNTIF('Updated Trees'!T$6:T$50,"In-Game")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -14995,52 +15016,52 @@
       <c r="H80" s="82"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="163"/>
-      <c r="B81" s="163"/>
-      <c r="C81" s="163"/>
-      <c r="D81" s="163"/>
-      <c r="E81" s="163"/>
-      <c r="F81" s="163"/>
-      <c r="G81" s="163"/>
-      <c r="H81" s="163"/>
-      <c r="I81" s="163"/>
-      <c r="J81" s="163"/>
-      <c r="K81" s="163"/>
-      <c r="L81" s="163"/>
-      <c r="M81" s="163"/>
-      <c r="N81" s="163"/>
-      <c r="O81" s="163"/>
-      <c r="P81" s="163"/>
-      <c r="Q81" s="163"/>
-      <c r="R81" s="163"/>
-      <c r="S81" s="163"/>
-      <c r="T81" s="163"/>
-      <c r="U81" s="163"/>
+      <c r="A81" s="162"/>
+      <c r="B81" s="162"/>
+      <c r="C81" s="162"/>
+      <c r="D81" s="162"/>
+      <c r="E81" s="162"/>
+      <c r="F81" s="162"/>
+      <c r="G81" s="162"/>
+      <c r="H81" s="162"/>
+      <c r="I81" s="162"/>
+      <c r="J81" s="162"/>
+      <c r="K81" s="162"/>
+      <c r="L81" s="162"/>
+      <c r="M81" s="162"/>
+      <c r="N81" s="162"/>
+      <c r="O81" s="162"/>
+      <c r="P81" s="162"/>
+      <c r="Q81" s="162"/>
+      <c r="R81" s="162"/>
+      <c r="S81" s="162"/>
+      <c r="T81" s="162"/>
+      <c r="U81" s="162"/>
     </row>
     <row r="82" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="164" t="s">
+      <c r="A82" s="165" t="s">
         <v>1822</v>
       </c>
-      <c r="B82" s="164"/>
-      <c r="C82" s="164"/>
-      <c r="D82" s="164"/>
-      <c r="E82" s="164"/>
-      <c r="F82" s="164"/>
-      <c r="G82" s="164"/>
-      <c r="H82" s="164"/>
-      <c r="I82" s="164"/>
-      <c r="J82" s="164"/>
-      <c r="K82" s="164"/>
-      <c r="L82" s="164"/>
-      <c r="M82" s="164"/>
-      <c r="N82" s="164"/>
-      <c r="O82" s="164"/>
-      <c r="P82" s="164"/>
-      <c r="Q82" s="164"/>
-      <c r="R82" s="164"/>
-      <c r="S82" s="164"/>
-      <c r="T82" s="164"/>
-      <c r="U82" s="164"/>
+      <c r="B82" s="165"/>
+      <c r="C82" s="165"/>
+      <c r="D82" s="165"/>
+      <c r="E82" s="165"/>
+      <c r="F82" s="165"/>
+      <c r="G82" s="165"/>
+      <c r="H82" s="165"/>
+      <c r="I82" s="165"/>
+      <c r="J82" s="165"/>
+      <c r="K82" s="165"/>
+      <c r="L82" s="165"/>
+      <c r="M82" s="165"/>
+      <c r="N82" s="165"/>
+      <c r="O82" s="165"/>
+      <c r="P82" s="165"/>
+      <c r="Q82" s="165"/>
+      <c r="R82" s="165"/>
+      <c r="S82" s="165"/>
+      <c r="T82" s="165"/>
+      <c r="U82" s="165"/>
     </row>
     <row r="83" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A83" s="91" t="s">
@@ -15058,24 +15079,24 @@
       <c r="E83" s="93" t="s">
         <v>1838</v>
       </c>
-      <c r="F83" s="166" t="s">
+      <c r="F83" s="161" t="s">
         <v>149</v>
       </c>
-      <c r="G83" s="166"/>
-      <c r="H83" s="166"/>
-      <c r="I83" s="166"/>
-      <c r="J83" s="166"/>
-      <c r="K83" s="166"/>
-      <c r="L83" s="166"/>
-      <c r="M83" s="166"/>
-      <c r="N83" s="166"/>
-      <c r="O83" s="166"/>
-      <c r="P83" s="166"/>
-      <c r="Q83" s="166"/>
-      <c r="R83" s="166"/>
-      <c r="S83" s="166"/>
-      <c r="T83" s="166"/>
-      <c r="U83" s="166"/>
+      <c r="G83" s="161"/>
+      <c r="H83" s="161"/>
+      <c r="I83" s="161"/>
+      <c r="J83" s="161"/>
+      <c r="K83" s="161"/>
+      <c r="L83" s="161"/>
+      <c r="M83" s="161"/>
+      <c r="N83" s="161"/>
+      <c r="O83" s="161"/>
+      <c r="P83" s="161"/>
+      <c r="Q83" s="161"/>
+      <c r="R83" s="161"/>
+      <c r="S83" s="161"/>
+      <c r="T83" s="161"/>
+      <c r="U83" s="161"/>
     </row>
     <row r="84" spans="1:21" s="19" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="76" t="s">
@@ -15093,22 +15114,22 @@
       <c r="E84" s="76" t="s">
         <v>1840</v>
       </c>
-      <c r="F84" s="165"/>
-      <c r="G84" s="165"/>
-      <c r="H84" s="165"/>
-      <c r="I84" s="165"/>
-      <c r="J84" s="165"/>
-      <c r="K84" s="165"/>
-      <c r="L84" s="165"/>
-      <c r="M84" s="165"/>
-      <c r="N84" s="165"/>
-      <c r="O84" s="165"/>
-      <c r="P84" s="165"/>
-      <c r="Q84" s="165"/>
-      <c r="R84" s="165"/>
-      <c r="S84" s="165"/>
-      <c r="T84" s="165"/>
-      <c r="U84" s="165"/>
+      <c r="F84" s="160"/>
+      <c r="G84" s="160"/>
+      <c r="H84" s="160"/>
+      <c r="I84" s="160"/>
+      <c r="J84" s="160"/>
+      <c r="K84" s="160"/>
+      <c r="L84" s="160"/>
+      <c r="M84" s="160"/>
+      <c r="N84" s="160"/>
+      <c r="O84" s="160"/>
+      <c r="P84" s="160"/>
+      <c r="Q84" s="160"/>
+      <c r="R84" s="160"/>
+      <c r="S84" s="160"/>
+      <c r="T84" s="160"/>
+      <c r="U84" s="160"/>
     </row>
     <row r="85" spans="1:21" s="19" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="76" t="s">
@@ -15126,24 +15147,24 @@
       <c r="E85" s="76" t="s">
         <v>1843</v>
       </c>
-      <c r="F85" s="160" t="s">
+      <c r="F85" s="159" t="s">
         <v>1844</v>
       </c>
-      <c r="G85" s="160"/>
-      <c r="H85" s="160"/>
-      <c r="I85" s="160"/>
-      <c r="J85" s="160"/>
-      <c r="K85" s="160"/>
-      <c r="L85" s="160"/>
-      <c r="M85" s="160"/>
-      <c r="N85" s="160"/>
-      <c r="O85" s="160"/>
-      <c r="P85" s="160"/>
-      <c r="Q85" s="160"/>
-      <c r="R85" s="160"/>
-      <c r="S85" s="160"/>
-      <c r="T85" s="160"/>
-      <c r="U85" s="160"/>
+      <c r="G85" s="159"/>
+      <c r="H85" s="159"/>
+      <c r="I85" s="159"/>
+      <c r="J85" s="159"/>
+      <c r="K85" s="159"/>
+      <c r="L85" s="159"/>
+      <c r="M85" s="159"/>
+      <c r="N85" s="159"/>
+      <c r="O85" s="159"/>
+      <c r="P85" s="159"/>
+      <c r="Q85" s="159"/>
+      <c r="R85" s="159"/>
+      <c r="S85" s="159"/>
+      <c r="T85" s="159"/>
+      <c r="U85" s="159"/>
     </row>
     <row r="86" spans="1:21" s="19" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="76" t="s">
@@ -15161,24 +15182,24 @@
       <c r="E86" s="76" t="s">
         <v>1848</v>
       </c>
-      <c r="F86" s="160" t="s">
+      <c r="F86" s="159" t="s">
         <v>1849</v>
       </c>
-      <c r="G86" s="160"/>
-      <c r="H86" s="160"/>
-      <c r="I86" s="160"/>
-      <c r="J86" s="160"/>
-      <c r="K86" s="160"/>
-      <c r="L86" s="160"/>
-      <c r="M86" s="160"/>
-      <c r="N86" s="160"/>
-      <c r="O86" s="160"/>
-      <c r="P86" s="160"/>
-      <c r="Q86" s="160"/>
-      <c r="R86" s="160"/>
-      <c r="S86" s="160"/>
-      <c r="T86" s="160"/>
-      <c r="U86" s="160"/>
+      <c r="G86" s="159"/>
+      <c r="H86" s="159"/>
+      <c r="I86" s="159"/>
+      <c r="J86" s="159"/>
+      <c r="K86" s="159"/>
+      <c r="L86" s="159"/>
+      <c r="M86" s="159"/>
+      <c r="N86" s="159"/>
+      <c r="O86" s="159"/>
+      <c r="P86" s="159"/>
+      <c r="Q86" s="159"/>
+      <c r="R86" s="159"/>
+      <c r="S86" s="159"/>
+      <c r="T86" s="159"/>
+      <c r="U86" s="159"/>
     </row>
     <row r="87" spans="1:21" s="19" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="20" t="s">
@@ -15196,24 +15217,24 @@
       <c r="E87" s="20" t="s">
         <v>1852</v>
       </c>
-      <c r="F87" s="160" t="s">
+      <c r="F87" s="159" t="s">
         <v>1853</v>
       </c>
-      <c r="G87" s="160"/>
-      <c r="H87" s="160"/>
-      <c r="I87" s="160"/>
-      <c r="J87" s="160"/>
-      <c r="K87" s="160"/>
-      <c r="L87" s="160"/>
-      <c r="M87" s="160"/>
-      <c r="N87" s="160"/>
-      <c r="O87" s="160"/>
-      <c r="P87" s="160"/>
-      <c r="Q87" s="160"/>
-      <c r="R87" s="160"/>
-      <c r="S87" s="160"/>
-      <c r="T87" s="160"/>
-      <c r="U87" s="160"/>
+      <c r="G87" s="159"/>
+      <c r="H87" s="159"/>
+      <c r="I87" s="159"/>
+      <c r="J87" s="159"/>
+      <c r="K87" s="159"/>
+      <c r="L87" s="159"/>
+      <c r="M87" s="159"/>
+      <c r="N87" s="159"/>
+      <c r="O87" s="159"/>
+      <c r="P87" s="159"/>
+      <c r="Q87" s="159"/>
+      <c r="R87" s="159"/>
+      <c r="S87" s="159"/>
+      <c r="T87" s="159"/>
+      <c r="U87" s="159"/>
     </row>
     <row r="88" spans="1:21" s="19" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="76" t="s">
@@ -15231,24 +15252,24 @@
       <c r="E88" s="76" t="s">
         <v>1855</v>
       </c>
-      <c r="F88" s="160" t="s">
+      <c r="F88" s="159" t="s">
         <v>1856</v>
       </c>
-      <c r="G88" s="160"/>
-      <c r="H88" s="160"/>
-      <c r="I88" s="160"/>
-      <c r="J88" s="160"/>
-      <c r="K88" s="160"/>
-      <c r="L88" s="160"/>
-      <c r="M88" s="160"/>
-      <c r="N88" s="160"/>
-      <c r="O88" s="160"/>
-      <c r="P88" s="160"/>
-      <c r="Q88" s="160"/>
-      <c r="R88" s="160"/>
-      <c r="S88" s="160"/>
-      <c r="T88" s="160"/>
-      <c r="U88" s="160"/>
+      <c r="G88" s="159"/>
+      <c r="H88" s="159"/>
+      <c r="I88" s="159"/>
+      <c r="J88" s="159"/>
+      <c r="K88" s="159"/>
+      <c r="L88" s="159"/>
+      <c r="M88" s="159"/>
+      <c r="N88" s="159"/>
+      <c r="O88" s="159"/>
+      <c r="P88" s="159"/>
+      <c r="Q88" s="159"/>
+      <c r="R88" s="159"/>
+      <c r="S88" s="159"/>
+      <c r="T88" s="159"/>
+      <c r="U88" s="159"/>
     </row>
     <row r="89" spans="1:21" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="76" t="s">
@@ -15266,24 +15287,24 @@
       <c r="E89" s="76" t="s">
         <v>1859</v>
       </c>
-      <c r="F89" s="160" t="s">
+      <c r="F89" s="159" t="s">
         <v>1860</v>
       </c>
-      <c r="G89" s="160"/>
-      <c r="H89" s="160"/>
-      <c r="I89" s="160"/>
-      <c r="J89" s="160"/>
-      <c r="K89" s="160"/>
-      <c r="L89" s="160"/>
-      <c r="M89" s="160"/>
-      <c r="N89" s="160"/>
-      <c r="O89" s="160"/>
-      <c r="P89" s="160"/>
-      <c r="Q89" s="160"/>
-      <c r="R89" s="160"/>
-      <c r="S89" s="160"/>
-      <c r="T89" s="160"/>
-      <c r="U89" s="160"/>
+      <c r="G89" s="159"/>
+      <c r="H89" s="159"/>
+      <c r="I89" s="159"/>
+      <c r="J89" s="159"/>
+      <c r="K89" s="159"/>
+      <c r="L89" s="159"/>
+      <c r="M89" s="159"/>
+      <c r="N89" s="159"/>
+      <c r="O89" s="159"/>
+      <c r="P89" s="159"/>
+      <c r="Q89" s="159"/>
+      <c r="R89" s="159"/>
+      <c r="S89" s="159"/>
+      <c r="T89" s="159"/>
+      <c r="U89" s="159"/>
     </row>
     <row r="90" spans="1:21" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="76" t="s">
@@ -15301,24 +15322,24 @@
       <c r="E90" s="76" t="s">
         <v>1863</v>
       </c>
-      <c r="F90" s="160" t="s">
+      <c r="F90" s="159" t="s">
         <v>1864</v>
       </c>
-      <c r="G90" s="160"/>
-      <c r="H90" s="160"/>
-      <c r="I90" s="160"/>
-      <c r="J90" s="160"/>
-      <c r="K90" s="160"/>
-      <c r="L90" s="160"/>
-      <c r="M90" s="160"/>
-      <c r="N90" s="160"/>
-      <c r="O90" s="160"/>
-      <c r="P90" s="160"/>
-      <c r="Q90" s="160"/>
-      <c r="R90" s="160"/>
-      <c r="S90" s="160"/>
-      <c r="T90" s="160"/>
-      <c r="U90" s="160"/>
+      <c r="G90" s="159"/>
+      <c r="H90" s="159"/>
+      <c r="I90" s="159"/>
+      <c r="J90" s="159"/>
+      <c r="K90" s="159"/>
+      <c r="L90" s="159"/>
+      <c r="M90" s="159"/>
+      <c r="N90" s="159"/>
+      <c r="O90" s="159"/>
+      <c r="P90" s="159"/>
+      <c r="Q90" s="159"/>
+      <c r="R90" s="159"/>
+      <c r="S90" s="159"/>
+      <c r="T90" s="159"/>
+      <c r="U90" s="159"/>
     </row>
     <row r="91" spans="1:21" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="76" t="s">
@@ -15336,24 +15357,24 @@
       <c r="E91" s="76" t="s">
         <v>1868</v>
       </c>
-      <c r="F91" s="160" t="s">
+      <c r="F91" s="159" t="s">
         <v>1869</v>
       </c>
-      <c r="G91" s="160"/>
-      <c r="H91" s="160"/>
-      <c r="I91" s="160"/>
-      <c r="J91" s="160"/>
-      <c r="K91" s="160"/>
-      <c r="L91" s="160"/>
-      <c r="M91" s="160"/>
-      <c r="N91" s="160"/>
-      <c r="O91" s="160"/>
-      <c r="P91" s="160"/>
-      <c r="Q91" s="160"/>
-      <c r="R91" s="160"/>
-      <c r="S91" s="160"/>
-      <c r="T91" s="160"/>
-      <c r="U91" s="160"/>
+      <c r="G91" s="159"/>
+      <c r="H91" s="159"/>
+      <c r="I91" s="159"/>
+      <c r="J91" s="159"/>
+      <c r="K91" s="159"/>
+      <c r="L91" s="159"/>
+      <c r="M91" s="159"/>
+      <c r="N91" s="159"/>
+      <c r="O91" s="159"/>
+      <c r="P91" s="159"/>
+      <c r="Q91" s="159"/>
+      <c r="R91" s="159"/>
+      <c r="S91" s="159"/>
+      <c r="T91" s="159"/>
+      <c r="U91" s="159"/>
     </row>
     <row r="92" spans="1:21" s="19" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="76" t="s">
@@ -15371,24 +15392,24 @@
       <c r="E92" s="76" t="s">
         <v>1871</v>
       </c>
-      <c r="F92" s="160" t="s">
+      <c r="F92" s="159" t="s">
         <v>1872</v>
       </c>
-      <c r="G92" s="160"/>
-      <c r="H92" s="160"/>
-      <c r="I92" s="160"/>
-      <c r="J92" s="160"/>
-      <c r="K92" s="160"/>
-      <c r="L92" s="160"/>
-      <c r="M92" s="160"/>
-      <c r="N92" s="160"/>
-      <c r="O92" s="160"/>
-      <c r="P92" s="160"/>
-      <c r="Q92" s="160"/>
-      <c r="R92" s="160"/>
-      <c r="S92" s="160"/>
-      <c r="T92" s="160"/>
-      <c r="U92" s="160"/>
+      <c r="G92" s="159"/>
+      <c r="H92" s="159"/>
+      <c r="I92" s="159"/>
+      <c r="J92" s="159"/>
+      <c r="K92" s="159"/>
+      <c r="L92" s="159"/>
+      <c r="M92" s="159"/>
+      <c r="N92" s="159"/>
+      <c r="O92" s="159"/>
+      <c r="P92" s="159"/>
+      <c r="Q92" s="159"/>
+      <c r="R92" s="159"/>
+      <c r="S92" s="159"/>
+      <c r="T92" s="159"/>
+      <c r="U92" s="159"/>
     </row>
     <row r="93" spans="1:21" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="76" t="s">
@@ -15406,24 +15427,24 @@
       <c r="E93" s="76" t="s">
         <v>1874</v>
       </c>
-      <c r="F93" s="160" t="s">
+      <c r="F93" s="159" t="s">
         <v>1875</v>
       </c>
-      <c r="G93" s="160"/>
-      <c r="H93" s="160"/>
-      <c r="I93" s="160"/>
-      <c r="J93" s="160"/>
-      <c r="K93" s="160"/>
-      <c r="L93" s="160"/>
-      <c r="M93" s="160"/>
-      <c r="N93" s="160"/>
-      <c r="O93" s="160"/>
-      <c r="P93" s="160"/>
-      <c r="Q93" s="160"/>
-      <c r="R93" s="160"/>
-      <c r="S93" s="160"/>
-      <c r="T93" s="160"/>
-      <c r="U93" s="160"/>
+      <c r="G93" s="159"/>
+      <c r="H93" s="159"/>
+      <c r="I93" s="159"/>
+      <c r="J93" s="159"/>
+      <c r="K93" s="159"/>
+      <c r="L93" s="159"/>
+      <c r="M93" s="159"/>
+      <c r="N93" s="159"/>
+      <c r="O93" s="159"/>
+      <c r="P93" s="159"/>
+      <c r="Q93" s="159"/>
+      <c r="R93" s="159"/>
+      <c r="S93" s="159"/>
+      <c r="T93" s="159"/>
+      <c r="U93" s="159"/>
     </row>
     <row r="94" spans="1:21" s="19" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="76" t="s">
@@ -15441,24 +15462,24 @@
       <c r="E94" s="76" t="s">
         <v>1880</v>
       </c>
-      <c r="F94" s="160" t="s">
+      <c r="F94" s="159" t="s">
         <v>1881</v>
       </c>
-      <c r="G94" s="160"/>
-      <c r="H94" s="160"/>
-      <c r="I94" s="160"/>
-      <c r="J94" s="160"/>
-      <c r="K94" s="160"/>
-      <c r="L94" s="160"/>
-      <c r="M94" s="160"/>
-      <c r="N94" s="160"/>
-      <c r="O94" s="160"/>
-      <c r="P94" s="160"/>
-      <c r="Q94" s="160"/>
-      <c r="R94" s="160"/>
-      <c r="S94" s="160"/>
-      <c r="T94" s="160"/>
-      <c r="U94" s="160"/>
+      <c r="G94" s="159"/>
+      <c r="H94" s="159"/>
+      <c r="I94" s="159"/>
+      <c r="J94" s="159"/>
+      <c r="K94" s="159"/>
+      <c r="L94" s="159"/>
+      <c r="M94" s="159"/>
+      <c r="N94" s="159"/>
+      <c r="O94" s="159"/>
+      <c r="P94" s="159"/>
+      <c r="Q94" s="159"/>
+      <c r="R94" s="159"/>
+      <c r="S94" s="159"/>
+      <c r="T94" s="159"/>
+      <c r="U94" s="159"/>
     </row>
     <row r="95" spans="1:21" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="76" t="s">
@@ -15476,24 +15497,24 @@
       <c r="E95" s="76" t="s">
         <v>1886</v>
       </c>
-      <c r="F95" s="160" t="s">
+      <c r="F95" s="159" t="s">
         <v>1887</v>
       </c>
-      <c r="G95" s="160"/>
-      <c r="H95" s="160"/>
-      <c r="I95" s="160"/>
-      <c r="J95" s="160"/>
-      <c r="K95" s="160"/>
-      <c r="L95" s="160"/>
-      <c r="M95" s="160"/>
-      <c r="N95" s="160"/>
-      <c r="O95" s="160"/>
-      <c r="P95" s="160"/>
-      <c r="Q95" s="160"/>
-      <c r="R95" s="160"/>
-      <c r="S95" s="160"/>
-      <c r="T95" s="160"/>
-      <c r="U95" s="160"/>
+      <c r="G95" s="159"/>
+      <c r="H95" s="159"/>
+      <c r="I95" s="159"/>
+      <c r="J95" s="159"/>
+      <c r="K95" s="159"/>
+      <c r="L95" s="159"/>
+      <c r="M95" s="159"/>
+      <c r="N95" s="159"/>
+      <c r="O95" s="159"/>
+      <c r="P95" s="159"/>
+      <c r="Q95" s="159"/>
+      <c r="R95" s="159"/>
+      <c r="S95" s="159"/>
+      <c r="T95" s="159"/>
+      <c r="U95" s="159"/>
     </row>
     <row r="96" spans="1:21" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="76" t="s">
@@ -15511,24 +15532,24 @@
       <c r="E96" s="76" t="s">
         <v>1889</v>
       </c>
-      <c r="F96" s="160" t="s">
+      <c r="F96" s="159" t="s">
         <v>1890</v>
       </c>
-      <c r="G96" s="160"/>
-      <c r="H96" s="160"/>
-      <c r="I96" s="160"/>
-      <c r="J96" s="160"/>
-      <c r="K96" s="160"/>
-      <c r="L96" s="160"/>
-      <c r="M96" s="160"/>
-      <c r="N96" s="160"/>
-      <c r="O96" s="160"/>
-      <c r="P96" s="160"/>
-      <c r="Q96" s="160"/>
-      <c r="R96" s="160"/>
-      <c r="S96" s="160"/>
-      <c r="T96" s="160"/>
-      <c r="U96" s="160"/>
+      <c r="G96" s="159"/>
+      <c r="H96" s="159"/>
+      <c r="I96" s="159"/>
+      <c r="J96" s="159"/>
+      <c r="K96" s="159"/>
+      <c r="L96" s="159"/>
+      <c r="M96" s="159"/>
+      <c r="N96" s="159"/>
+      <c r="O96" s="159"/>
+      <c r="P96" s="159"/>
+      <c r="Q96" s="159"/>
+      <c r="R96" s="159"/>
+      <c r="S96" s="159"/>
+      <c r="T96" s="159"/>
+      <c r="U96" s="159"/>
     </row>
     <row r="97" spans="1:22" s="19" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="76" t="s">
@@ -15546,24 +15567,24 @@
       <c r="E97" s="76" t="s">
         <v>1892</v>
       </c>
-      <c r="F97" s="160" t="s">
+      <c r="F97" s="159" t="s">
         <v>1893</v>
       </c>
-      <c r="G97" s="160"/>
-      <c r="H97" s="160"/>
-      <c r="I97" s="160"/>
-      <c r="J97" s="160"/>
-      <c r="K97" s="160"/>
-      <c r="L97" s="160"/>
-      <c r="M97" s="160"/>
-      <c r="N97" s="160"/>
-      <c r="O97" s="160"/>
-      <c r="P97" s="160"/>
-      <c r="Q97" s="160"/>
-      <c r="R97" s="160"/>
-      <c r="S97" s="160"/>
-      <c r="T97" s="160"/>
-      <c r="U97" s="160"/>
+      <c r="G97" s="159"/>
+      <c r="H97" s="159"/>
+      <c r="I97" s="159"/>
+      <c r="J97" s="159"/>
+      <c r="K97" s="159"/>
+      <c r="L97" s="159"/>
+      <c r="M97" s="159"/>
+      <c r="N97" s="159"/>
+      <c r="O97" s="159"/>
+      <c r="P97" s="159"/>
+      <c r="Q97" s="159"/>
+      <c r="R97" s="159"/>
+      <c r="S97" s="159"/>
+      <c r="T97" s="159"/>
+      <c r="U97" s="159"/>
     </row>
     <row r="98" spans="1:22" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="76" t="s">
@@ -15581,24 +15602,24 @@
       <c r="E98" s="76" t="s">
         <v>1895</v>
       </c>
-      <c r="F98" s="160" t="s">
+      <c r="F98" s="159" t="s">
         <v>1896</v>
       </c>
-      <c r="G98" s="160"/>
-      <c r="H98" s="160"/>
-      <c r="I98" s="160"/>
-      <c r="J98" s="160"/>
-      <c r="K98" s="160"/>
-      <c r="L98" s="160"/>
-      <c r="M98" s="160"/>
-      <c r="N98" s="160"/>
-      <c r="O98" s="160"/>
-      <c r="P98" s="160"/>
-      <c r="Q98" s="160"/>
-      <c r="R98" s="160"/>
-      <c r="S98" s="160"/>
-      <c r="T98" s="160"/>
-      <c r="U98" s="160"/>
+      <c r="G98" s="159"/>
+      <c r="H98" s="159"/>
+      <c r="I98" s="159"/>
+      <c r="J98" s="159"/>
+      <c r="K98" s="159"/>
+      <c r="L98" s="159"/>
+      <c r="M98" s="159"/>
+      <c r="N98" s="159"/>
+      <c r="O98" s="159"/>
+      <c r="P98" s="159"/>
+      <c r="Q98" s="159"/>
+      <c r="R98" s="159"/>
+      <c r="S98" s="159"/>
+      <c r="T98" s="159"/>
+      <c r="U98" s="159"/>
     </row>
     <row r="99" spans="1:22" s="19" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="76" t="s">
@@ -15616,24 +15637,24 @@
       <c r="E99" s="76" t="s">
         <v>1898</v>
       </c>
-      <c r="F99" s="160" t="s">
+      <c r="F99" s="159" t="s">
         <v>1899</v>
       </c>
-      <c r="G99" s="160"/>
-      <c r="H99" s="160"/>
-      <c r="I99" s="160"/>
-      <c r="J99" s="160"/>
-      <c r="K99" s="160"/>
-      <c r="L99" s="160"/>
-      <c r="M99" s="160"/>
-      <c r="N99" s="160"/>
-      <c r="O99" s="160"/>
-      <c r="P99" s="160"/>
-      <c r="Q99" s="160"/>
-      <c r="R99" s="160"/>
-      <c r="S99" s="160"/>
-      <c r="T99" s="160"/>
-      <c r="U99" s="160"/>
+      <c r="G99" s="159"/>
+      <c r="H99" s="159"/>
+      <c r="I99" s="159"/>
+      <c r="J99" s="159"/>
+      <c r="K99" s="159"/>
+      <c r="L99" s="159"/>
+      <c r="M99" s="159"/>
+      <c r="N99" s="159"/>
+      <c r="O99" s="159"/>
+      <c r="P99" s="159"/>
+      <c r="Q99" s="159"/>
+      <c r="R99" s="159"/>
+      <c r="S99" s="159"/>
+      <c r="T99" s="159"/>
+      <c r="U99" s="159"/>
     </row>
     <row r="100" spans="1:22" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="76" t="s">
@@ -15651,24 +15672,24 @@
       <c r="E100" s="76" t="s">
         <v>1901</v>
       </c>
-      <c r="F100" s="160" t="s">
+      <c r="F100" s="159" t="s">
         <v>1902</v>
       </c>
-      <c r="G100" s="160"/>
-      <c r="H100" s="160"/>
-      <c r="I100" s="160"/>
-      <c r="J100" s="160"/>
-      <c r="K100" s="160"/>
-      <c r="L100" s="160"/>
-      <c r="M100" s="160"/>
-      <c r="N100" s="160"/>
-      <c r="O100" s="160"/>
-      <c r="P100" s="160"/>
-      <c r="Q100" s="160"/>
-      <c r="R100" s="160"/>
-      <c r="S100" s="160"/>
-      <c r="T100" s="160"/>
-      <c r="U100" s="160"/>
+      <c r="G100" s="159"/>
+      <c r="H100" s="159"/>
+      <c r="I100" s="159"/>
+      <c r="J100" s="159"/>
+      <c r="K100" s="159"/>
+      <c r="L100" s="159"/>
+      <c r="M100" s="159"/>
+      <c r="N100" s="159"/>
+      <c r="O100" s="159"/>
+      <c r="P100" s="159"/>
+      <c r="Q100" s="159"/>
+      <c r="R100" s="159"/>
+      <c r="S100" s="159"/>
+      <c r="T100" s="159"/>
+      <c r="U100" s="159"/>
     </row>
     <row r="101" spans="1:22" s="19" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="76" t="s">
@@ -15686,24 +15707,24 @@
       <c r="E101" s="76" t="s">
         <v>1904</v>
       </c>
-      <c r="F101" s="160" t="s">
+      <c r="F101" s="159" t="s">
         <v>1905</v>
       </c>
-      <c r="G101" s="160"/>
-      <c r="H101" s="160"/>
-      <c r="I101" s="160"/>
-      <c r="J101" s="160"/>
-      <c r="K101" s="160"/>
-      <c r="L101" s="160"/>
-      <c r="M101" s="160"/>
-      <c r="N101" s="160"/>
-      <c r="O101" s="160"/>
-      <c r="P101" s="160"/>
-      <c r="Q101" s="160"/>
-      <c r="R101" s="160"/>
-      <c r="S101" s="160"/>
-      <c r="T101" s="160"/>
-      <c r="U101" s="160"/>
+      <c r="G101" s="159"/>
+      <c r="H101" s="159"/>
+      <c r="I101" s="159"/>
+      <c r="J101" s="159"/>
+      <c r="K101" s="159"/>
+      <c r="L101" s="159"/>
+      <c r="M101" s="159"/>
+      <c r="N101" s="159"/>
+      <c r="O101" s="159"/>
+      <c r="P101" s="159"/>
+      <c r="Q101" s="159"/>
+      <c r="R101" s="159"/>
+      <c r="S101" s="159"/>
+      <c r="T101" s="159"/>
+      <c r="U101" s="159"/>
     </row>
     <row r="102" spans="1:22" s="19" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="76" t="s">
@@ -15721,24 +15742,24 @@
       <c r="E102" s="76" t="s">
         <v>1907</v>
       </c>
-      <c r="F102" s="160" t="s">
+      <c r="F102" s="159" t="s">
         <v>1908</v>
       </c>
-      <c r="G102" s="160"/>
-      <c r="H102" s="160"/>
-      <c r="I102" s="160"/>
-      <c r="J102" s="160"/>
-      <c r="K102" s="160"/>
-      <c r="L102" s="160"/>
-      <c r="M102" s="160"/>
-      <c r="N102" s="160"/>
-      <c r="O102" s="160"/>
-      <c r="P102" s="160"/>
-      <c r="Q102" s="160"/>
-      <c r="R102" s="160"/>
-      <c r="S102" s="160"/>
-      <c r="T102" s="160"/>
-      <c r="U102" s="160"/>
+      <c r="G102" s="159"/>
+      <c r="H102" s="159"/>
+      <c r="I102" s="159"/>
+      <c r="J102" s="159"/>
+      <c r="K102" s="159"/>
+      <c r="L102" s="159"/>
+      <c r="M102" s="159"/>
+      <c r="N102" s="159"/>
+      <c r="O102" s="159"/>
+      <c r="P102" s="159"/>
+      <c r="Q102" s="159"/>
+      <c r="R102" s="159"/>
+      <c r="S102" s="159"/>
+      <c r="T102" s="159"/>
+      <c r="U102" s="159"/>
     </row>
     <row r="103" spans="1:22" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="76" t="s">
@@ -15756,24 +15777,24 @@
       <c r="E103" s="76" t="s">
         <v>1912</v>
       </c>
-      <c r="F103" s="160" t="s">
+      <c r="F103" s="159" t="s">
         <v>1913</v>
       </c>
-      <c r="G103" s="160"/>
-      <c r="H103" s="160"/>
-      <c r="I103" s="160"/>
-      <c r="J103" s="160"/>
-      <c r="K103" s="160"/>
-      <c r="L103" s="160"/>
-      <c r="M103" s="160"/>
-      <c r="N103" s="160"/>
-      <c r="O103" s="160"/>
-      <c r="P103" s="160"/>
-      <c r="Q103" s="160"/>
-      <c r="R103" s="160"/>
-      <c r="S103" s="160"/>
-      <c r="T103" s="160"/>
-      <c r="U103" s="160"/>
+      <c r="G103" s="159"/>
+      <c r="H103" s="159"/>
+      <c r="I103" s="159"/>
+      <c r="J103" s="159"/>
+      <c r="K103" s="159"/>
+      <c r="L103" s="159"/>
+      <c r="M103" s="159"/>
+      <c r="N103" s="159"/>
+      <c r="O103" s="159"/>
+      <c r="P103" s="159"/>
+      <c r="Q103" s="159"/>
+      <c r="R103" s="159"/>
+      <c r="S103" s="159"/>
+      <c r="T103" s="159"/>
+      <c r="U103" s="159"/>
     </row>
     <row r="104" spans="1:22" s="19" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="76" t="s">
@@ -15791,24 +15812,24 @@
       <c r="E104" s="76" t="s">
         <v>1846</v>
       </c>
-      <c r="F104" s="160" t="s">
+      <c r="F104" s="159" t="s">
         <v>1916</v>
       </c>
-      <c r="G104" s="160"/>
-      <c r="H104" s="160"/>
-      <c r="I104" s="160"/>
-      <c r="J104" s="160"/>
-      <c r="K104" s="160"/>
-      <c r="L104" s="160"/>
-      <c r="M104" s="160"/>
-      <c r="N104" s="160"/>
-      <c r="O104" s="160"/>
-      <c r="P104" s="160"/>
-      <c r="Q104" s="160"/>
-      <c r="R104" s="160"/>
-      <c r="S104" s="160"/>
-      <c r="T104" s="160"/>
-      <c r="U104" s="160"/>
+      <c r="G104" s="159"/>
+      <c r="H104" s="159"/>
+      <c r="I104" s="159"/>
+      <c r="J104" s="159"/>
+      <c r="K104" s="159"/>
+      <c r="L104" s="159"/>
+      <c r="M104" s="159"/>
+      <c r="N104" s="159"/>
+      <c r="O104" s="159"/>
+      <c r="P104" s="159"/>
+      <c r="Q104" s="159"/>
+      <c r="R104" s="159"/>
+      <c r="S104" s="159"/>
+      <c r="T104" s="159"/>
+      <c r="U104" s="159"/>
     </row>
     <row r="105" spans="1:22" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="76" t="s">
@@ -15826,24 +15847,24 @@
       <c r="E105" s="76" t="s">
         <v>1918</v>
       </c>
-      <c r="F105" s="160" t="s">
+      <c r="F105" s="159" t="s">
         <v>1919</v>
       </c>
-      <c r="G105" s="160"/>
-      <c r="H105" s="160"/>
-      <c r="I105" s="160"/>
-      <c r="J105" s="160"/>
-      <c r="K105" s="160"/>
-      <c r="L105" s="160"/>
-      <c r="M105" s="160"/>
-      <c r="N105" s="160"/>
-      <c r="O105" s="160"/>
-      <c r="P105" s="160"/>
-      <c r="Q105" s="160"/>
-      <c r="R105" s="160"/>
-      <c r="S105" s="160"/>
-      <c r="T105" s="160"/>
-      <c r="U105" s="160"/>
+      <c r="G105" s="159"/>
+      <c r="H105" s="159"/>
+      <c r="I105" s="159"/>
+      <c r="J105" s="159"/>
+      <c r="K105" s="159"/>
+      <c r="L105" s="159"/>
+      <c r="M105" s="159"/>
+      <c r="N105" s="159"/>
+      <c r="O105" s="159"/>
+      <c r="P105" s="159"/>
+      <c r="Q105" s="159"/>
+      <c r="R105" s="159"/>
+      <c r="S105" s="159"/>
+      <c r="T105" s="159"/>
+      <c r="U105" s="159"/>
     </row>
     <row r="106" spans="1:22" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="76" t="s">
@@ -15861,24 +15882,24 @@
       <c r="E106" s="76" t="s">
         <v>1921</v>
       </c>
-      <c r="F106" s="160" t="s">
+      <c r="F106" s="159" t="s">
         <v>1922</v>
       </c>
-      <c r="G106" s="160"/>
-      <c r="H106" s="160"/>
-      <c r="I106" s="160"/>
-      <c r="J106" s="160"/>
-      <c r="K106" s="160"/>
-      <c r="L106" s="160"/>
-      <c r="M106" s="160"/>
-      <c r="N106" s="160"/>
-      <c r="O106" s="160"/>
-      <c r="P106" s="160"/>
-      <c r="Q106" s="160"/>
-      <c r="R106" s="160"/>
-      <c r="S106" s="160"/>
-      <c r="T106" s="160"/>
-      <c r="U106" s="160"/>
+      <c r="G106" s="159"/>
+      <c r="H106" s="159"/>
+      <c r="I106" s="159"/>
+      <c r="J106" s="159"/>
+      <c r="K106" s="159"/>
+      <c r="L106" s="159"/>
+      <c r="M106" s="159"/>
+      <c r="N106" s="159"/>
+      <c r="O106" s="159"/>
+      <c r="P106" s="159"/>
+      <c r="Q106" s="159"/>
+      <c r="R106" s="159"/>
+      <c r="S106" s="159"/>
+      <c r="T106" s="159"/>
+      <c r="U106" s="159"/>
     </row>
     <row r="107" spans="1:22" s="19" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="76" t="s">
@@ -15896,24 +15917,24 @@
       <c r="E107" s="76" t="s">
         <v>1925</v>
       </c>
-      <c r="F107" s="160" t="s">
+      <c r="F107" s="159" t="s">
         <v>1926</v>
       </c>
-      <c r="G107" s="160"/>
-      <c r="H107" s="160"/>
-      <c r="I107" s="160"/>
-      <c r="J107" s="160"/>
-      <c r="K107" s="160"/>
-      <c r="L107" s="160"/>
-      <c r="M107" s="160"/>
-      <c r="N107" s="160"/>
-      <c r="O107" s="160"/>
-      <c r="P107" s="160"/>
-      <c r="Q107" s="160"/>
-      <c r="R107" s="160"/>
-      <c r="S107" s="160"/>
-      <c r="T107" s="160"/>
-      <c r="U107" s="160"/>
+      <c r="G107" s="159"/>
+      <c r="H107" s="159"/>
+      <c r="I107" s="159"/>
+      <c r="J107" s="159"/>
+      <c r="K107" s="159"/>
+      <c r="L107" s="159"/>
+      <c r="M107" s="159"/>
+      <c r="N107" s="159"/>
+      <c r="O107" s="159"/>
+      <c r="P107" s="159"/>
+      <c r="Q107" s="159"/>
+      <c r="R107" s="159"/>
+      <c r="S107" s="159"/>
+      <c r="T107" s="159"/>
+      <c r="U107" s="159"/>
     </row>
     <row r="108" spans="1:22" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="76" t="s">
@@ -15931,24 +15952,24 @@
       <c r="E108" s="76" t="s">
         <v>1928</v>
       </c>
-      <c r="F108" s="161" t="s">
+      <c r="F108" s="163" t="s">
         <v>1929</v>
       </c>
-      <c r="G108" s="161"/>
-      <c r="H108" s="161"/>
-      <c r="I108" s="161"/>
-      <c r="J108" s="161"/>
-      <c r="K108" s="161"/>
-      <c r="L108" s="161"/>
-      <c r="M108" s="161"/>
-      <c r="N108" s="161"/>
-      <c r="O108" s="161"/>
-      <c r="P108" s="161"/>
-      <c r="Q108" s="161"/>
-      <c r="R108" s="161"/>
-      <c r="S108" s="161"/>
-      <c r="T108" s="161"/>
-      <c r="U108" s="161"/>
+      <c r="G108" s="163"/>
+      <c r="H108" s="163"/>
+      <c r="I108" s="163"/>
+      <c r="J108" s="163"/>
+      <c r="K108" s="163"/>
+      <c r="L108" s="163"/>
+      <c r="M108" s="163"/>
+      <c r="N108" s="163"/>
+      <c r="O108" s="163"/>
+      <c r="P108" s="163"/>
+      <c r="Q108" s="163"/>
+      <c r="R108" s="163"/>
+      <c r="S108" s="163"/>
+      <c r="T108" s="163"/>
+      <c r="U108" s="163"/>
     </row>
     <row r="109" spans="1:22" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="76" t="s">
@@ -15966,24 +15987,24 @@
       <c r="E109" s="76" t="s">
         <v>1932</v>
       </c>
-      <c r="F109" s="161" t="s">
+      <c r="F109" s="163" t="s">
         <v>1933</v>
       </c>
-      <c r="G109" s="161"/>
-      <c r="H109" s="161"/>
-      <c r="I109" s="161"/>
-      <c r="J109" s="161"/>
-      <c r="K109" s="161"/>
-      <c r="L109" s="161"/>
-      <c r="M109" s="161"/>
-      <c r="N109" s="161"/>
-      <c r="O109" s="161"/>
-      <c r="P109" s="161"/>
-      <c r="Q109" s="161"/>
-      <c r="R109" s="161"/>
-      <c r="S109" s="161"/>
-      <c r="T109" s="161"/>
-      <c r="U109" s="161"/>
+      <c r="G109" s="163"/>
+      <c r="H109" s="163"/>
+      <c r="I109" s="163"/>
+      <c r="J109" s="163"/>
+      <c r="K109" s="163"/>
+      <c r="L109" s="163"/>
+      <c r="M109" s="163"/>
+      <c r="N109" s="163"/>
+      <c r="O109" s="163"/>
+      <c r="P109" s="163"/>
+      <c r="Q109" s="163"/>
+      <c r="R109" s="163"/>
+      <c r="S109" s="163"/>
+      <c r="T109" s="163"/>
+      <c r="U109" s="163"/>
     </row>
     <row r="110" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A110" s="76" t="s">
@@ -16001,24 +16022,24 @@
       <c r="E110" s="76" t="s">
         <v>1936</v>
       </c>
-      <c r="F110" s="161" t="s">
+      <c r="F110" s="163" t="s">
         <v>1937</v>
       </c>
-      <c r="G110" s="161"/>
-      <c r="H110" s="161"/>
-      <c r="I110" s="161"/>
-      <c r="J110" s="161"/>
-      <c r="K110" s="161"/>
-      <c r="L110" s="161"/>
-      <c r="M110" s="161"/>
-      <c r="N110" s="161"/>
-      <c r="O110" s="161"/>
-      <c r="P110" s="161"/>
-      <c r="Q110" s="161"/>
-      <c r="R110" s="161"/>
-      <c r="S110" s="161"/>
-      <c r="T110" s="161"/>
-      <c r="U110" s="161"/>
+      <c r="G110" s="163"/>
+      <c r="H110" s="163"/>
+      <c r="I110" s="163"/>
+      <c r="J110" s="163"/>
+      <c r="K110" s="163"/>
+      <c r="L110" s="163"/>
+      <c r="M110" s="163"/>
+      <c r="N110" s="163"/>
+      <c r="O110" s="163"/>
+      <c r="P110" s="163"/>
+      <c r="Q110" s="163"/>
+      <c r="R110" s="163"/>
+      <c r="S110" s="163"/>
+      <c r="T110" s="163"/>
+      <c r="U110" s="163"/>
       <c r="V110" s="19"/>
     </row>
     <row r="111" spans="1:22" x14ac:dyDescent="0.25">
@@ -16037,24 +16058,24 @@
       <c r="E111" s="76" t="s">
         <v>1940</v>
       </c>
-      <c r="F111" s="161" t="s">
+      <c r="F111" s="163" t="s">
         <v>1941</v>
       </c>
-      <c r="G111" s="161"/>
-      <c r="H111" s="161"/>
-      <c r="I111" s="161"/>
-      <c r="J111" s="161"/>
-      <c r="K111" s="161"/>
-      <c r="L111" s="161"/>
-      <c r="M111" s="161"/>
-      <c r="N111" s="161"/>
-      <c r="O111" s="161"/>
-      <c r="P111" s="161"/>
-      <c r="Q111" s="161"/>
-      <c r="R111" s="161"/>
-      <c r="S111" s="161"/>
-      <c r="T111" s="161"/>
-      <c r="U111" s="161"/>
+      <c r="G111" s="163"/>
+      <c r="H111" s="163"/>
+      <c r="I111" s="163"/>
+      <c r="J111" s="163"/>
+      <c r="K111" s="163"/>
+      <c r="L111" s="163"/>
+      <c r="M111" s="163"/>
+      <c r="N111" s="163"/>
+      <c r="O111" s="163"/>
+      <c r="P111" s="163"/>
+      <c r="Q111" s="163"/>
+      <c r="R111" s="163"/>
+      <c r="S111" s="163"/>
+      <c r="T111" s="163"/>
+      <c r="U111" s="163"/>
       <c r="V111" s="19"/>
     </row>
     <row r="112" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16073,24 +16094,24 @@
       <c r="E112" s="76" t="s">
         <v>1944</v>
       </c>
-      <c r="F112" s="160" t="s">
+      <c r="F112" s="159" t="s">
         <v>1945</v>
       </c>
-      <c r="G112" s="160"/>
-      <c r="H112" s="160"/>
-      <c r="I112" s="160"/>
-      <c r="J112" s="160"/>
-      <c r="K112" s="160"/>
-      <c r="L112" s="160"/>
-      <c r="M112" s="160"/>
-      <c r="N112" s="160"/>
-      <c r="O112" s="160"/>
-      <c r="P112" s="160"/>
-      <c r="Q112" s="160"/>
-      <c r="R112" s="160"/>
-      <c r="S112" s="160"/>
-      <c r="T112" s="160"/>
-      <c r="U112" s="160"/>
+      <c r="G112" s="159"/>
+      <c r="H112" s="159"/>
+      <c r="I112" s="159"/>
+      <c r="J112" s="159"/>
+      <c r="K112" s="159"/>
+      <c r="L112" s="159"/>
+      <c r="M112" s="159"/>
+      <c r="N112" s="159"/>
+      <c r="O112" s="159"/>
+      <c r="P112" s="159"/>
+      <c r="Q112" s="159"/>
+      <c r="R112" s="159"/>
+      <c r="S112" s="159"/>
+      <c r="T112" s="159"/>
+      <c r="U112" s="159"/>
       <c r="V112" s="19"/>
     </row>
     <row r="113" spans="1:22" x14ac:dyDescent="0.25">
@@ -16109,24 +16130,24 @@
       <c r="E113" s="76" t="s">
         <v>1948</v>
       </c>
-      <c r="F113" s="161" t="s">
+      <c r="F113" s="163" t="s">
         <v>1949</v>
       </c>
-      <c r="G113" s="161"/>
-      <c r="H113" s="161"/>
-      <c r="I113" s="161"/>
-      <c r="J113" s="161"/>
-      <c r="K113" s="161"/>
-      <c r="L113" s="161"/>
-      <c r="M113" s="161"/>
-      <c r="N113" s="161"/>
-      <c r="O113" s="161"/>
-      <c r="P113" s="161"/>
-      <c r="Q113" s="161"/>
-      <c r="R113" s="161"/>
-      <c r="S113" s="161"/>
-      <c r="T113" s="161"/>
-      <c r="U113" s="161"/>
+      <c r="G113" s="163"/>
+      <c r="H113" s="163"/>
+      <c r="I113" s="163"/>
+      <c r="J113" s="163"/>
+      <c r="K113" s="163"/>
+      <c r="L113" s="163"/>
+      <c r="M113" s="163"/>
+      <c r="N113" s="163"/>
+      <c r="O113" s="163"/>
+      <c r="P113" s="163"/>
+      <c r="Q113" s="163"/>
+      <c r="R113" s="163"/>
+      <c r="S113" s="163"/>
+      <c r="T113" s="163"/>
+      <c r="U113" s="163"/>
       <c r="V113" s="19"/>
     </row>
     <row r="114" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16145,24 +16166,24 @@
       <c r="E114" s="76" t="s">
         <v>1952</v>
       </c>
-      <c r="F114" s="160" t="s">
+      <c r="F114" s="159" t="s">
         <v>1953</v>
       </c>
-      <c r="G114" s="160"/>
-      <c r="H114" s="160"/>
-      <c r="I114" s="160"/>
-      <c r="J114" s="160"/>
-      <c r="K114" s="160"/>
-      <c r="L114" s="160"/>
-      <c r="M114" s="160"/>
-      <c r="N114" s="160"/>
-      <c r="O114" s="160"/>
-      <c r="P114" s="160"/>
-      <c r="Q114" s="160"/>
-      <c r="R114" s="160"/>
-      <c r="S114" s="160"/>
-      <c r="T114" s="160"/>
-      <c r="U114" s="160"/>
+      <c r="G114" s="159"/>
+      <c r="H114" s="159"/>
+      <c r="I114" s="159"/>
+      <c r="J114" s="159"/>
+      <c r="K114" s="159"/>
+      <c r="L114" s="159"/>
+      <c r="M114" s="159"/>
+      <c r="N114" s="159"/>
+      <c r="O114" s="159"/>
+      <c r="P114" s="159"/>
+      <c r="Q114" s="159"/>
+      <c r="R114" s="159"/>
+      <c r="S114" s="159"/>
+      <c r="T114" s="159"/>
+      <c r="U114" s="159"/>
       <c r="V114" s="19"/>
     </row>
     <row r="115" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16181,24 +16202,24 @@
       <c r="E115" s="76" t="s">
         <v>1955</v>
       </c>
-      <c r="F115" s="160" t="s">
+      <c r="F115" s="159" t="s">
         <v>1956</v>
       </c>
-      <c r="G115" s="160"/>
-      <c r="H115" s="160"/>
-      <c r="I115" s="160"/>
-      <c r="J115" s="160"/>
-      <c r="K115" s="160"/>
-      <c r="L115" s="160"/>
-      <c r="M115" s="160"/>
-      <c r="N115" s="160"/>
-      <c r="O115" s="160"/>
-      <c r="P115" s="160"/>
-      <c r="Q115" s="160"/>
-      <c r="R115" s="160"/>
-      <c r="S115" s="160"/>
-      <c r="T115" s="160"/>
-      <c r="U115" s="160"/>
+      <c r="G115" s="159"/>
+      <c r="H115" s="159"/>
+      <c r="I115" s="159"/>
+      <c r="J115" s="159"/>
+      <c r="K115" s="159"/>
+      <c r="L115" s="159"/>
+      <c r="M115" s="159"/>
+      <c r="N115" s="159"/>
+      <c r="O115" s="159"/>
+      <c r="P115" s="159"/>
+      <c r="Q115" s="159"/>
+      <c r="R115" s="159"/>
+      <c r="S115" s="159"/>
+      <c r="T115" s="159"/>
+      <c r="U115" s="159"/>
       <c r="V115" s="19"/>
     </row>
     <row r="116" spans="1:22" x14ac:dyDescent="0.25">
@@ -16217,24 +16238,24 @@
       <c r="E116" s="76" t="s">
         <v>1960</v>
       </c>
-      <c r="F116" s="161" t="s">
+      <c r="F116" s="163" t="s">
         <v>1961</v>
       </c>
-      <c r="G116" s="161"/>
-      <c r="H116" s="161"/>
-      <c r="I116" s="161"/>
-      <c r="J116" s="161"/>
-      <c r="K116" s="161"/>
-      <c r="L116" s="161"/>
-      <c r="M116" s="161"/>
-      <c r="N116" s="161"/>
-      <c r="O116" s="161"/>
-      <c r="P116" s="161"/>
-      <c r="Q116" s="161"/>
-      <c r="R116" s="161"/>
-      <c r="S116" s="161"/>
-      <c r="T116" s="161"/>
-      <c r="U116" s="161"/>
+      <c r="G116" s="163"/>
+      <c r="H116" s="163"/>
+      <c r="I116" s="163"/>
+      <c r="J116" s="163"/>
+      <c r="K116" s="163"/>
+      <c r="L116" s="163"/>
+      <c r="M116" s="163"/>
+      <c r="N116" s="163"/>
+      <c r="O116" s="163"/>
+      <c r="P116" s="163"/>
+      <c r="Q116" s="163"/>
+      <c r="R116" s="163"/>
+      <c r="S116" s="163"/>
+      <c r="T116" s="163"/>
+      <c r="U116" s="163"/>
       <c r="V116" s="19"/>
     </row>
     <row r="117" spans="1:22" x14ac:dyDescent="0.25">
@@ -16253,24 +16274,24 @@
       <c r="E117" s="76" t="s">
         <v>1964</v>
       </c>
-      <c r="F117" s="161" t="s">
+      <c r="F117" s="163" t="s">
         <v>1965</v>
       </c>
-      <c r="G117" s="161"/>
-      <c r="H117" s="161"/>
-      <c r="I117" s="161"/>
-      <c r="J117" s="161"/>
-      <c r="K117" s="161"/>
-      <c r="L117" s="161"/>
-      <c r="M117" s="161"/>
-      <c r="N117" s="161"/>
-      <c r="O117" s="161"/>
-      <c r="P117" s="161"/>
-      <c r="Q117" s="161"/>
-      <c r="R117" s="161"/>
-      <c r="S117" s="161"/>
-      <c r="T117" s="161"/>
-      <c r="U117" s="161"/>
+      <c r="G117" s="163"/>
+      <c r="H117" s="163"/>
+      <c r="I117" s="163"/>
+      <c r="J117" s="163"/>
+      <c r="K117" s="163"/>
+      <c r="L117" s="163"/>
+      <c r="M117" s="163"/>
+      <c r="N117" s="163"/>
+      <c r="O117" s="163"/>
+      <c r="P117" s="163"/>
+      <c r="Q117" s="163"/>
+      <c r="R117" s="163"/>
+      <c r="S117" s="163"/>
+      <c r="T117" s="163"/>
+      <c r="U117" s="163"/>
       <c r="V117" s="19"/>
     </row>
     <row r="118" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16289,24 +16310,24 @@
       <c r="E118" s="76" t="s">
         <v>1968</v>
       </c>
-      <c r="F118" s="160" t="s">
+      <c r="F118" s="159" t="s">
         <v>1969</v>
       </c>
-      <c r="G118" s="160"/>
-      <c r="H118" s="160"/>
-      <c r="I118" s="160"/>
-      <c r="J118" s="160"/>
-      <c r="K118" s="160"/>
-      <c r="L118" s="160"/>
-      <c r="M118" s="160"/>
-      <c r="N118" s="160"/>
-      <c r="O118" s="160"/>
-      <c r="P118" s="160"/>
-      <c r="Q118" s="160"/>
-      <c r="R118" s="160"/>
-      <c r="S118" s="160"/>
-      <c r="T118" s="160"/>
-      <c r="U118" s="160"/>
+      <c r="G118" s="159"/>
+      <c r="H118" s="159"/>
+      <c r="I118" s="159"/>
+      <c r="J118" s="159"/>
+      <c r="K118" s="159"/>
+      <c r="L118" s="159"/>
+      <c r="M118" s="159"/>
+      <c r="N118" s="159"/>
+      <c r="O118" s="159"/>
+      <c r="P118" s="159"/>
+      <c r="Q118" s="159"/>
+      <c r="R118" s="159"/>
+      <c r="S118" s="159"/>
+      <c r="T118" s="159"/>
+      <c r="U118" s="159"/>
       <c r="V118" s="19"/>
     </row>
     <row r="119" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16325,24 +16346,24 @@
       <c r="E119" s="76" t="s">
         <v>1972</v>
       </c>
-      <c r="F119" s="160" t="s">
+      <c r="F119" s="159" t="s">
         <v>1973</v>
       </c>
-      <c r="G119" s="160"/>
-      <c r="H119" s="160"/>
-      <c r="I119" s="160"/>
-      <c r="J119" s="160"/>
-      <c r="K119" s="160"/>
-      <c r="L119" s="160"/>
-      <c r="M119" s="160"/>
-      <c r="N119" s="160"/>
-      <c r="O119" s="160"/>
-      <c r="P119" s="160"/>
-      <c r="Q119" s="160"/>
-      <c r="R119" s="160"/>
-      <c r="S119" s="160"/>
-      <c r="T119" s="160"/>
-      <c r="U119" s="160"/>
+      <c r="G119" s="159"/>
+      <c r="H119" s="159"/>
+      <c r="I119" s="159"/>
+      <c r="J119" s="159"/>
+      <c r="K119" s="159"/>
+      <c r="L119" s="159"/>
+      <c r="M119" s="159"/>
+      <c r="N119" s="159"/>
+      <c r="O119" s="159"/>
+      <c r="P119" s="159"/>
+      <c r="Q119" s="159"/>
+      <c r="R119" s="159"/>
+      <c r="S119" s="159"/>
+      <c r="T119" s="159"/>
+      <c r="U119" s="159"/>
       <c r="V119" s="19"/>
     </row>
     <row r="120" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16361,24 +16382,24 @@
       <c r="E120" s="76" t="s">
         <v>1976</v>
       </c>
-      <c r="F120" s="160" t="s">
+      <c r="F120" s="159" t="s">
         <v>1977</v>
       </c>
-      <c r="G120" s="160"/>
-      <c r="H120" s="160"/>
-      <c r="I120" s="160"/>
-      <c r="J120" s="160"/>
-      <c r="K120" s="160"/>
-      <c r="L120" s="160"/>
-      <c r="M120" s="160"/>
-      <c r="N120" s="160"/>
-      <c r="O120" s="160"/>
-      <c r="P120" s="160"/>
-      <c r="Q120" s="160"/>
-      <c r="R120" s="160"/>
-      <c r="S120" s="160"/>
-      <c r="T120" s="160"/>
-      <c r="U120" s="160"/>
+      <c r="G120" s="159"/>
+      <c r="H120" s="159"/>
+      <c r="I120" s="159"/>
+      <c r="J120" s="159"/>
+      <c r="K120" s="159"/>
+      <c r="L120" s="159"/>
+      <c r="M120" s="159"/>
+      <c r="N120" s="159"/>
+      <c r="O120" s="159"/>
+      <c r="P120" s="159"/>
+      <c r="Q120" s="159"/>
+      <c r="R120" s="159"/>
+      <c r="S120" s="159"/>
+      <c r="T120" s="159"/>
+      <c r="U120" s="159"/>
       <c r="V120" s="19"/>
     </row>
     <row r="121" spans="1:22" x14ac:dyDescent="0.25">
@@ -16397,24 +16418,24 @@
       <c r="E121" s="76" t="s">
         <v>1979</v>
       </c>
-      <c r="F121" s="161" t="s">
+      <c r="F121" s="163" t="s">
         <v>1980</v>
       </c>
-      <c r="G121" s="161"/>
-      <c r="H121" s="161"/>
-      <c r="I121" s="161"/>
-      <c r="J121" s="161"/>
-      <c r="K121" s="161"/>
-      <c r="L121" s="161"/>
-      <c r="M121" s="161"/>
-      <c r="N121" s="161"/>
-      <c r="O121" s="161"/>
-      <c r="P121" s="161"/>
-      <c r="Q121" s="161"/>
-      <c r="R121" s="161"/>
-      <c r="S121" s="161"/>
-      <c r="T121" s="161"/>
-      <c r="U121" s="161"/>
+      <c r="G121" s="163"/>
+      <c r="H121" s="163"/>
+      <c r="I121" s="163"/>
+      <c r="J121" s="163"/>
+      <c r="K121" s="163"/>
+      <c r="L121" s="163"/>
+      <c r="M121" s="163"/>
+      <c r="N121" s="163"/>
+      <c r="O121" s="163"/>
+      <c r="P121" s="163"/>
+      <c r="Q121" s="163"/>
+      <c r="R121" s="163"/>
+      <c r="S121" s="163"/>
+      <c r="T121" s="163"/>
+      <c r="U121" s="163"/>
       <c r="V121" s="19"/>
     </row>
     <row r="122" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16433,24 +16454,24 @@
       <c r="E122" s="94" t="s">
         <v>1039</v>
       </c>
-      <c r="F122" s="160" t="s">
+      <c r="F122" s="159" t="s">
         <v>1982</v>
       </c>
-      <c r="G122" s="160"/>
-      <c r="H122" s="160"/>
-      <c r="I122" s="160"/>
-      <c r="J122" s="160"/>
-      <c r="K122" s="160"/>
-      <c r="L122" s="160"/>
-      <c r="M122" s="160"/>
-      <c r="N122" s="160"/>
-      <c r="O122" s="160"/>
-      <c r="P122" s="160"/>
-      <c r="Q122" s="160"/>
-      <c r="R122" s="160"/>
-      <c r="S122" s="160"/>
-      <c r="T122" s="160"/>
-      <c r="U122" s="160"/>
+      <c r="G122" s="159"/>
+      <c r="H122" s="159"/>
+      <c r="I122" s="159"/>
+      <c r="J122" s="159"/>
+      <c r="K122" s="159"/>
+      <c r="L122" s="159"/>
+      <c r="M122" s="159"/>
+      <c r="N122" s="159"/>
+      <c r="O122" s="159"/>
+      <c r="P122" s="159"/>
+      <c r="Q122" s="159"/>
+      <c r="R122" s="159"/>
+      <c r="S122" s="159"/>
+      <c r="T122" s="159"/>
+      <c r="U122" s="159"/>
       <c r="V122" s="19"/>
     </row>
     <row r="123" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16469,24 +16490,24 @@
       <c r="E123" s="76" t="s">
         <v>1984</v>
       </c>
-      <c r="F123" s="160" t="s">
+      <c r="F123" s="159" t="s">
         <v>1985</v>
       </c>
-      <c r="G123" s="160"/>
-      <c r="H123" s="160"/>
-      <c r="I123" s="160"/>
-      <c r="J123" s="160"/>
-      <c r="K123" s="160"/>
-      <c r="L123" s="160"/>
-      <c r="M123" s="160"/>
-      <c r="N123" s="160"/>
-      <c r="O123" s="160"/>
-      <c r="P123" s="160"/>
-      <c r="Q123" s="160"/>
-      <c r="R123" s="160"/>
-      <c r="S123" s="160"/>
-      <c r="T123" s="160"/>
-      <c r="U123" s="160"/>
+      <c r="G123" s="159"/>
+      <c r="H123" s="159"/>
+      <c r="I123" s="159"/>
+      <c r="J123" s="159"/>
+      <c r="K123" s="159"/>
+      <c r="L123" s="159"/>
+      <c r="M123" s="159"/>
+      <c r="N123" s="159"/>
+      <c r="O123" s="159"/>
+      <c r="P123" s="159"/>
+      <c r="Q123" s="159"/>
+      <c r="R123" s="159"/>
+      <c r="S123" s="159"/>
+      <c r="T123" s="159"/>
+      <c r="U123" s="159"/>
       <c r="V123" s="19"/>
     </row>
     <row r="124" spans="1:22" x14ac:dyDescent="0.25">
@@ -16505,24 +16526,24 @@
       <c r="E124" s="76" t="s">
         <v>1988</v>
       </c>
-      <c r="F124" s="161" t="s">
+      <c r="F124" s="163" t="s">
         <v>1989</v>
       </c>
-      <c r="G124" s="161"/>
-      <c r="H124" s="161"/>
-      <c r="I124" s="161"/>
-      <c r="J124" s="161"/>
-      <c r="K124" s="161"/>
-      <c r="L124" s="161"/>
-      <c r="M124" s="161"/>
-      <c r="N124" s="161"/>
-      <c r="O124" s="161"/>
-      <c r="P124" s="161"/>
-      <c r="Q124" s="161"/>
-      <c r="R124" s="161"/>
-      <c r="S124" s="161"/>
-      <c r="T124" s="161"/>
-      <c r="U124" s="161"/>
+      <c r="G124" s="163"/>
+      <c r="H124" s="163"/>
+      <c r="I124" s="163"/>
+      <c r="J124" s="163"/>
+      <c r="K124" s="163"/>
+      <c r="L124" s="163"/>
+      <c r="M124" s="163"/>
+      <c r="N124" s="163"/>
+      <c r="O124" s="163"/>
+      <c r="P124" s="163"/>
+      <c r="Q124" s="163"/>
+      <c r="R124" s="163"/>
+      <c r="S124" s="163"/>
+      <c r="T124" s="163"/>
+      <c r="U124" s="163"/>
       <c r="V124" s="19"/>
     </row>
     <row r="125" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16541,24 +16562,24 @@
       <c r="E125" s="76" t="s">
         <v>1991</v>
       </c>
-      <c r="F125" s="160" t="s">
+      <c r="F125" s="159" t="s">
         <v>1992</v>
       </c>
-      <c r="G125" s="160"/>
-      <c r="H125" s="160"/>
-      <c r="I125" s="160"/>
-      <c r="J125" s="160"/>
-      <c r="K125" s="160"/>
-      <c r="L125" s="160"/>
-      <c r="M125" s="160"/>
-      <c r="N125" s="160"/>
-      <c r="O125" s="160"/>
-      <c r="P125" s="160"/>
-      <c r="Q125" s="160"/>
-      <c r="R125" s="160"/>
-      <c r="S125" s="160"/>
-      <c r="T125" s="160"/>
-      <c r="U125" s="160"/>
+      <c r="G125" s="159"/>
+      <c r="H125" s="159"/>
+      <c r="I125" s="159"/>
+      <c r="J125" s="159"/>
+      <c r="K125" s="159"/>
+      <c r="L125" s="159"/>
+      <c r="M125" s="159"/>
+      <c r="N125" s="159"/>
+      <c r="O125" s="159"/>
+      <c r="P125" s="159"/>
+      <c r="Q125" s="159"/>
+      <c r="R125" s="159"/>
+      <c r="S125" s="159"/>
+      <c r="T125" s="159"/>
+      <c r="U125" s="159"/>
       <c r="V125" s="19"/>
     </row>
     <row r="126" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16577,24 +16598,24 @@
       <c r="E126" s="94" t="s">
         <v>1995</v>
       </c>
-      <c r="F126" s="160" t="s">
+      <c r="F126" s="159" t="s">
         <v>1996</v>
       </c>
-      <c r="G126" s="160"/>
-      <c r="H126" s="160"/>
-      <c r="I126" s="160"/>
-      <c r="J126" s="160"/>
-      <c r="K126" s="160"/>
-      <c r="L126" s="160"/>
-      <c r="M126" s="160"/>
-      <c r="N126" s="160"/>
-      <c r="O126" s="160"/>
-      <c r="P126" s="160"/>
-      <c r="Q126" s="160"/>
-      <c r="R126" s="160"/>
-      <c r="S126" s="160"/>
-      <c r="T126" s="160"/>
-      <c r="U126" s="160"/>
+      <c r="G126" s="159"/>
+      <c r="H126" s="159"/>
+      <c r="I126" s="159"/>
+      <c r="J126" s="159"/>
+      <c r="K126" s="159"/>
+      <c r="L126" s="159"/>
+      <c r="M126" s="159"/>
+      <c r="N126" s="159"/>
+      <c r="O126" s="159"/>
+      <c r="P126" s="159"/>
+      <c r="Q126" s="159"/>
+      <c r="R126" s="159"/>
+      <c r="S126" s="159"/>
+      <c r="T126" s="159"/>
+      <c r="U126" s="159"/>
       <c r="V126" s="19"/>
     </row>
     <row r="127" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16613,24 +16634,24 @@
       <c r="E127" s="76" t="s">
         <v>1998</v>
       </c>
-      <c r="F127" s="160" t="s">
+      <c r="F127" s="159" t="s">
         <v>1999</v>
       </c>
-      <c r="G127" s="160"/>
-      <c r="H127" s="160"/>
-      <c r="I127" s="160"/>
-      <c r="J127" s="160"/>
-      <c r="K127" s="160"/>
-      <c r="L127" s="160"/>
-      <c r="M127" s="160"/>
-      <c r="N127" s="160"/>
-      <c r="O127" s="160"/>
-      <c r="P127" s="160"/>
-      <c r="Q127" s="160"/>
-      <c r="R127" s="160"/>
-      <c r="S127" s="160"/>
-      <c r="T127" s="160"/>
-      <c r="U127" s="160"/>
+      <c r="G127" s="159"/>
+      <c r="H127" s="159"/>
+      <c r="I127" s="159"/>
+      <c r="J127" s="159"/>
+      <c r="K127" s="159"/>
+      <c r="L127" s="159"/>
+      <c r="M127" s="159"/>
+      <c r="N127" s="159"/>
+      <c r="O127" s="159"/>
+      <c r="P127" s="159"/>
+      <c r="Q127" s="159"/>
+      <c r="R127" s="159"/>
+      <c r="S127" s="159"/>
+      <c r="T127" s="159"/>
+      <c r="U127" s="159"/>
       <c r="V127" s="19"/>
     </row>
     <row r="128" spans="1:22" x14ac:dyDescent="0.25">
@@ -16649,24 +16670,24 @@
       <c r="E128" s="76" t="s">
         <v>2001</v>
       </c>
-      <c r="F128" s="161" t="s">
+      <c r="F128" s="163" t="s">
         <v>2002</v>
       </c>
-      <c r="G128" s="161"/>
-      <c r="H128" s="161"/>
-      <c r="I128" s="161"/>
-      <c r="J128" s="161"/>
-      <c r="K128" s="161"/>
-      <c r="L128" s="161"/>
-      <c r="M128" s="161"/>
-      <c r="N128" s="161"/>
-      <c r="O128" s="161"/>
-      <c r="P128" s="161"/>
-      <c r="Q128" s="161"/>
-      <c r="R128" s="161"/>
-      <c r="S128" s="161"/>
-      <c r="T128" s="161"/>
-      <c r="U128" s="161"/>
+      <c r="G128" s="163"/>
+      <c r="H128" s="163"/>
+      <c r="I128" s="163"/>
+      <c r="J128" s="163"/>
+      <c r="K128" s="163"/>
+      <c r="L128" s="163"/>
+      <c r="M128" s="163"/>
+      <c r="N128" s="163"/>
+      <c r="O128" s="163"/>
+      <c r="P128" s="163"/>
+      <c r="Q128" s="163"/>
+      <c r="R128" s="163"/>
+      <c r="S128" s="163"/>
+      <c r="T128" s="163"/>
+      <c r="U128" s="163"/>
       <c r="V128" s="19"/>
     </row>
     <row r="129" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16685,24 +16706,24 @@
       <c r="E129" s="76" t="s">
         <v>2005</v>
       </c>
-      <c r="F129" s="160" t="s">
+      <c r="F129" s="159" t="s">
         <v>2006</v>
       </c>
-      <c r="G129" s="160"/>
-      <c r="H129" s="160"/>
-      <c r="I129" s="160"/>
-      <c r="J129" s="160"/>
-      <c r="K129" s="160"/>
-      <c r="L129" s="160"/>
-      <c r="M129" s="160"/>
-      <c r="N129" s="160"/>
-      <c r="O129" s="160"/>
-      <c r="P129" s="160"/>
-      <c r="Q129" s="160"/>
-      <c r="R129" s="160"/>
-      <c r="S129" s="160"/>
-      <c r="T129" s="160"/>
-      <c r="U129" s="160"/>
+      <c r="G129" s="159"/>
+      <c r="H129" s="159"/>
+      <c r="I129" s="159"/>
+      <c r="J129" s="159"/>
+      <c r="K129" s="159"/>
+      <c r="L129" s="159"/>
+      <c r="M129" s="159"/>
+      <c r="N129" s="159"/>
+      <c r="O129" s="159"/>
+      <c r="P129" s="159"/>
+      <c r="Q129" s="159"/>
+      <c r="R129" s="159"/>
+      <c r="S129" s="159"/>
+      <c r="T129" s="159"/>
+      <c r="U129" s="159"/>
       <c r="V129" s="19"/>
     </row>
     <row r="130" spans="1:22" x14ac:dyDescent="0.25">
@@ -16721,24 +16742,24 @@
       <c r="E130" s="76" t="s">
         <v>2009</v>
       </c>
-      <c r="F130" s="162" t="s">
+      <c r="F130" s="164" t="s">
         <v>2010</v>
       </c>
-      <c r="G130" s="162"/>
-      <c r="H130" s="162"/>
-      <c r="I130" s="162"/>
-      <c r="J130" s="162"/>
-      <c r="K130" s="162"/>
-      <c r="L130" s="162"/>
-      <c r="M130" s="162"/>
-      <c r="N130" s="162"/>
-      <c r="O130" s="162"/>
-      <c r="P130" s="162"/>
-      <c r="Q130" s="162"/>
-      <c r="R130" s="162"/>
-      <c r="S130" s="162"/>
-      <c r="T130" s="162"/>
-      <c r="U130" s="162"/>
+      <c r="G130" s="164"/>
+      <c r="H130" s="164"/>
+      <c r="I130" s="164"/>
+      <c r="J130" s="164"/>
+      <c r="K130" s="164"/>
+      <c r="L130" s="164"/>
+      <c r="M130" s="164"/>
+      <c r="N130" s="164"/>
+      <c r="O130" s="164"/>
+      <c r="P130" s="164"/>
+      <c r="Q130" s="164"/>
+      <c r="R130" s="164"/>
+      <c r="S130" s="164"/>
+      <c r="T130" s="164"/>
+      <c r="U130" s="164"/>
       <c r="V130" s="19"/>
     </row>
     <row r="131" spans="1:22" x14ac:dyDescent="0.25">
@@ -16757,24 +16778,24 @@
       <c r="E131" s="76" t="s">
         <v>2012</v>
       </c>
-      <c r="F131" s="162" t="s">
+      <c r="F131" s="164" t="s">
         <v>2013</v>
       </c>
-      <c r="G131" s="162"/>
-      <c r="H131" s="162"/>
-      <c r="I131" s="162"/>
-      <c r="J131" s="162"/>
-      <c r="K131" s="162"/>
-      <c r="L131" s="162"/>
-      <c r="M131" s="162"/>
-      <c r="N131" s="162"/>
-      <c r="O131" s="162"/>
-      <c r="P131" s="162"/>
-      <c r="Q131" s="162"/>
-      <c r="R131" s="162"/>
-      <c r="S131" s="162"/>
-      <c r="T131" s="162"/>
-      <c r="U131" s="162"/>
+      <c r="G131" s="164"/>
+      <c r="H131" s="164"/>
+      <c r="I131" s="164"/>
+      <c r="J131" s="164"/>
+      <c r="K131" s="164"/>
+      <c r="L131" s="164"/>
+      <c r="M131" s="164"/>
+      <c r="N131" s="164"/>
+      <c r="O131" s="164"/>
+      <c r="P131" s="164"/>
+      <c r="Q131" s="164"/>
+      <c r="R131" s="164"/>
+      <c r="S131" s="164"/>
+      <c r="T131" s="164"/>
+      <c r="U131" s="164"/>
       <c r="V131" s="19"/>
     </row>
     <row r="132" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16793,24 +16814,24 @@
       <c r="E132" s="76" t="s">
         <v>2017</v>
       </c>
-      <c r="F132" s="160" t="s">
+      <c r="F132" s="159" t="s">
         <v>2018</v>
       </c>
-      <c r="G132" s="160"/>
-      <c r="H132" s="160"/>
-      <c r="I132" s="160"/>
-      <c r="J132" s="160"/>
-      <c r="K132" s="160"/>
-      <c r="L132" s="160"/>
-      <c r="M132" s="160"/>
-      <c r="N132" s="160"/>
-      <c r="O132" s="160"/>
-      <c r="P132" s="160"/>
-      <c r="Q132" s="160"/>
-      <c r="R132" s="160"/>
-      <c r="S132" s="160"/>
-      <c r="T132" s="160"/>
-      <c r="U132" s="160"/>
+      <c r="G132" s="159"/>
+      <c r="H132" s="159"/>
+      <c r="I132" s="159"/>
+      <c r="J132" s="159"/>
+      <c r="K132" s="159"/>
+      <c r="L132" s="159"/>
+      <c r="M132" s="159"/>
+      <c r="N132" s="159"/>
+      <c r="O132" s="159"/>
+      <c r="P132" s="159"/>
+      <c r="Q132" s="159"/>
+      <c r="R132" s="159"/>
+      <c r="S132" s="159"/>
+      <c r="T132" s="159"/>
+      <c r="U132" s="159"/>
       <c r="V132" s="19"/>
     </row>
     <row r="133" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16829,24 +16850,24 @@
       <c r="E133" s="76" t="s">
         <v>2021</v>
       </c>
-      <c r="F133" s="160" t="s">
+      <c r="F133" s="159" t="s">
         <v>2022</v>
       </c>
-      <c r="G133" s="160"/>
-      <c r="H133" s="160"/>
-      <c r="I133" s="160"/>
-      <c r="J133" s="160"/>
-      <c r="K133" s="160"/>
-      <c r="L133" s="160"/>
-      <c r="M133" s="160"/>
-      <c r="N133" s="160"/>
-      <c r="O133" s="160"/>
-      <c r="P133" s="160"/>
-      <c r="Q133" s="160"/>
-      <c r="R133" s="160"/>
-      <c r="S133" s="160"/>
-      <c r="T133" s="160"/>
-      <c r="U133" s="160"/>
+      <c r="G133" s="159"/>
+      <c r="H133" s="159"/>
+      <c r="I133" s="159"/>
+      <c r="J133" s="159"/>
+      <c r="K133" s="159"/>
+      <c r="L133" s="159"/>
+      <c r="M133" s="159"/>
+      <c r="N133" s="159"/>
+      <c r="O133" s="159"/>
+      <c r="P133" s="159"/>
+      <c r="Q133" s="159"/>
+      <c r="R133" s="159"/>
+      <c r="S133" s="159"/>
+      <c r="T133" s="159"/>
+      <c r="U133" s="159"/>
       <c r="V133" s="19"/>
     </row>
     <row r="134" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16865,24 +16886,24 @@
       <c r="E134" s="76" t="s">
         <v>2025</v>
       </c>
-      <c r="F134" s="160" t="s">
+      <c r="F134" s="159" t="s">
         <v>2026</v>
       </c>
-      <c r="G134" s="160"/>
-      <c r="H134" s="160"/>
-      <c r="I134" s="160"/>
-      <c r="J134" s="160"/>
-      <c r="K134" s="160"/>
-      <c r="L134" s="160"/>
-      <c r="M134" s="160"/>
-      <c r="N134" s="160"/>
-      <c r="O134" s="160"/>
-      <c r="P134" s="160"/>
-      <c r="Q134" s="160"/>
-      <c r="R134" s="160"/>
-      <c r="S134" s="160"/>
-      <c r="T134" s="160"/>
-      <c r="U134" s="160"/>
+      <c r="G134" s="159"/>
+      <c r="H134" s="159"/>
+      <c r="I134" s="159"/>
+      <c r="J134" s="159"/>
+      <c r="K134" s="159"/>
+      <c r="L134" s="159"/>
+      <c r="M134" s="159"/>
+      <c r="N134" s="159"/>
+      <c r="O134" s="159"/>
+      <c r="P134" s="159"/>
+      <c r="Q134" s="159"/>
+      <c r="R134" s="159"/>
+      <c r="S134" s="159"/>
+      <c r="T134" s="159"/>
+      <c r="U134" s="159"/>
       <c r="V134" s="19"/>
     </row>
     <row r="135" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16901,24 +16922,24 @@
       <c r="E135" s="76" t="s">
         <v>2029</v>
       </c>
-      <c r="F135" s="160" t="s">
+      <c r="F135" s="159" t="s">
         <v>2030</v>
       </c>
-      <c r="G135" s="160"/>
-      <c r="H135" s="160"/>
-      <c r="I135" s="160"/>
-      <c r="J135" s="160"/>
-      <c r="K135" s="160"/>
-      <c r="L135" s="160"/>
-      <c r="M135" s="160"/>
-      <c r="N135" s="160"/>
-      <c r="O135" s="160"/>
-      <c r="P135" s="160"/>
-      <c r="Q135" s="160"/>
-      <c r="R135" s="160"/>
-      <c r="S135" s="160"/>
-      <c r="T135" s="160"/>
-      <c r="U135" s="160"/>
+      <c r="G135" s="159"/>
+      <c r="H135" s="159"/>
+      <c r="I135" s="159"/>
+      <c r="J135" s="159"/>
+      <c r="K135" s="159"/>
+      <c r="L135" s="159"/>
+      <c r="M135" s="159"/>
+      <c r="N135" s="159"/>
+      <c r="O135" s="159"/>
+      <c r="P135" s="159"/>
+      <c r="Q135" s="159"/>
+      <c r="R135" s="159"/>
+      <c r="S135" s="159"/>
+      <c r="T135" s="159"/>
+      <c r="U135" s="159"/>
       <c r="V135" s="19"/>
     </row>
     <row r="136" spans="1:22" x14ac:dyDescent="0.25">
@@ -16937,24 +16958,24 @@
       <c r="E136" s="76" t="s">
         <v>2035</v>
       </c>
-      <c r="F136" s="161" t="s">
+      <c r="F136" s="163" t="s">
         <v>2036</v>
       </c>
-      <c r="G136" s="161"/>
-      <c r="H136" s="161"/>
-      <c r="I136" s="161"/>
-      <c r="J136" s="161"/>
-      <c r="K136" s="161"/>
-      <c r="L136" s="161"/>
-      <c r="M136" s="161"/>
-      <c r="N136" s="161"/>
-      <c r="O136" s="161"/>
-      <c r="P136" s="161"/>
-      <c r="Q136" s="161"/>
-      <c r="R136" s="161"/>
-      <c r="S136" s="161"/>
-      <c r="T136" s="161"/>
-      <c r="U136" s="161"/>
+      <c r="G136" s="163"/>
+      <c r="H136" s="163"/>
+      <c r="I136" s="163"/>
+      <c r="J136" s="163"/>
+      <c r="K136" s="163"/>
+      <c r="L136" s="163"/>
+      <c r="M136" s="163"/>
+      <c r="N136" s="163"/>
+      <c r="O136" s="163"/>
+      <c r="P136" s="163"/>
+      <c r="Q136" s="163"/>
+      <c r="R136" s="163"/>
+      <c r="S136" s="163"/>
+      <c r="T136" s="163"/>
+      <c r="U136" s="163"/>
       <c r="V136" s="19"/>
     </row>
     <row r="137" spans="1:22" x14ac:dyDescent="0.25">
@@ -16973,24 +16994,24 @@
       <c r="E137" s="94" t="s">
         <v>1039</v>
       </c>
-      <c r="F137" s="161" t="s">
+      <c r="F137" s="163" t="s">
         <v>2038</v>
       </c>
-      <c r="G137" s="161"/>
-      <c r="H137" s="161"/>
-      <c r="I137" s="161"/>
-      <c r="J137" s="161"/>
-      <c r="K137" s="161"/>
-      <c r="L137" s="161"/>
-      <c r="M137" s="161"/>
-      <c r="N137" s="161"/>
-      <c r="O137" s="161"/>
-      <c r="P137" s="161"/>
-      <c r="Q137" s="161"/>
-      <c r="R137" s="161"/>
-      <c r="S137" s="161"/>
-      <c r="T137" s="161"/>
-      <c r="U137" s="161"/>
+      <c r="G137" s="163"/>
+      <c r="H137" s="163"/>
+      <c r="I137" s="163"/>
+      <c r="J137" s="163"/>
+      <c r="K137" s="163"/>
+      <c r="L137" s="163"/>
+      <c r="M137" s="163"/>
+      <c r="N137" s="163"/>
+      <c r="O137" s="163"/>
+      <c r="P137" s="163"/>
+      <c r="Q137" s="163"/>
+      <c r="R137" s="163"/>
+      <c r="S137" s="163"/>
+      <c r="T137" s="163"/>
+      <c r="U137" s="163"/>
       <c r="V137" s="19"/>
     </row>
     <row r="138" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17009,24 +17030,24 @@
       <c r="E138" s="76" t="s">
         <v>2041</v>
       </c>
-      <c r="F138" s="160" t="s">
+      <c r="F138" s="159" t="s">
         <v>2042</v>
       </c>
-      <c r="G138" s="160"/>
-      <c r="H138" s="160"/>
-      <c r="I138" s="160"/>
-      <c r="J138" s="160"/>
-      <c r="K138" s="160"/>
-      <c r="L138" s="160"/>
-      <c r="M138" s="160"/>
-      <c r="N138" s="160"/>
-      <c r="O138" s="160"/>
-      <c r="P138" s="160"/>
-      <c r="Q138" s="160"/>
-      <c r="R138" s="160"/>
-      <c r="S138" s="160"/>
-      <c r="T138" s="160"/>
-      <c r="U138" s="160"/>
+      <c r="G138" s="159"/>
+      <c r="H138" s="159"/>
+      <c r="I138" s="159"/>
+      <c r="J138" s="159"/>
+      <c r="K138" s="159"/>
+      <c r="L138" s="159"/>
+      <c r="M138" s="159"/>
+      <c r="N138" s="159"/>
+      <c r="O138" s="159"/>
+      <c r="P138" s="159"/>
+      <c r="Q138" s="159"/>
+      <c r="R138" s="159"/>
+      <c r="S138" s="159"/>
+      <c r="T138" s="159"/>
+      <c r="U138" s="159"/>
       <c r="V138" s="19"/>
     </row>
     <row r="139" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17045,24 +17066,24 @@
       <c r="E139" s="76" t="s">
         <v>2045</v>
       </c>
-      <c r="F139" s="160" t="s">
+      <c r="F139" s="159" t="s">
         <v>2046</v>
       </c>
-      <c r="G139" s="160"/>
-      <c r="H139" s="160"/>
-      <c r="I139" s="160"/>
-      <c r="J139" s="160"/>
-      <c r="K139" s="160"/>
-      <c r="L139" s="160"/>
-      <c r="M139" s="160"/>
-      <c r="N139" s="160"/>
-      <c r="O139" s="160"/>
-      <c r="P139" s="160"/>
-      <c r="Q139" s="160"/>
-      <c r="R139" s="160"/>
-      <c r="S139" s="160"/>
-      <c r="T139" s="160"/>
-      <c r="U139" s="160"/>
+      <c r="G139" s="159"/>
+      <c r="H139" s="159"/>
+      <c r="I139" s="159"/>
+      <c r="J139" s="159"/>
+      <c r="K139" s="159"/>
+      <c r="L139" s="159"/>
+      <c r="M139" s="159"/>
+      <c r="N139" s="159"/>
+      <c r="O139" s="159"/>
+      <c r="P139" s="159"/>
+      <c r="Q139" s="159"/>
+      <c r="R139" s="159"/>
+      <c r="S139" s="159"/>
+      <c r="T139" s="159"/>
+      <c r="U139" s="159"/>
       <c r="V139" s="19"/>
     </row>
     <row r="140" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17081,24 +17102,24 @@
       <c r="E140" s="76" t="s">
         <v>2048</v>
       </c>
-      <c r="F140" s="160" t="s">
+      <c r="F140" s="159" t="s">
         <v>2049</v>
       </c>
-      <c r="G140" s="160"/>
-      <c r="H140" s="160"/>
-      <c r="I140" s="160"/>
-      <c r="J140" s="160"/>
-      <c r="K140" s="160"/>
-      <c r="L140" s="160"/>
-      <c r="M140" s="160"/>
-      <c r="N140" s="160"/>
-      <c r="O140" s="160"/>
-      <c r="P140" s="160"/>
-      <c r="Q140" s="160"/>
-      <c r="R140" s="160"/>
-      <c r="S140" s="160"/>
-      <c r="T140" s="160"/>
-      <c r="U140" s="160"/>
+      <c r="G140" s="159"/>
+      <c r="H140" s="159"/>
+      <c r="I140" s="159"/>
+      <c r="J140" s="159"/>
+      <c r="K140" s="159"/>
+      <c r="L140" s="159"/>
+      <c r="M140" s="159"/>
+      <c r="N140" s="159"/>
+      <c r="O140" s="159"/>
+      <c r="P140" s="159"/>
+      <c r="Q140" s="159"/>
+      <c r="R140" s="159"/>
+      <c r="S140" s="159"/>
+      <c r="T140" s="159"/>
+      <c r="U140" s="159"/>
       <c r="V140" s="19"/>
     </row>
     <row r="141" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17117,24 +17138,24 @@
       <c r="E141" s="94" t="s">
         <v>1039</v>
       </c>
-      <c r="F141" s="160" t="s">
+      <c r="F141" s="159" t="s">
         <v>2052</v>
       </c>
-      <c r="G141" s="160"/>
-      <c r="H141" s="160"/>
-      <c r="I141" s="160"/>
-      <c r="J141" s="160"/>
-      <c r="K141" s="160"/>
-      <c r="L141" s="160"/>
-      <c r="M141" s="160"/>
-      <c r="N141" s="160"/>
-      <c r="O141" s="160"/>
-      <c r="P141" s="160"/>
-      <c r="Q141" s="160"/>
-      <c r="R141" s="160"/>
-      <c r="S141" s="160"/>
-      <c r="T141" s="160"/>
-      <c r="U141" s="160"/>
+      <c r="G141" s="159"/>
+      <c r="H141" s="159"/>
+      <c r="I141" s="159"/>
+      <c r="J141" s="159"/>
+      <c r="K141" s="159"/>
+      <c r="L141" s="159"/>
+      <c r="M141" s="159"/>
+      <c r="N141" s="159"/>
+      <c r="O141" s="159"/>
+      <c r="P141" s="159"/>
+      <c r="Q141" s="159"/>
+      <c r="R141" s="159"/>
+      <c r="S141" s="159"/>
+      <c r="T141" s="159"/>
+      <c r="U141" s="159"/>
       <c r="V141" s="19"/>
     </row>
     <row r="142" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17153,24 +17174,24 @@
       <c r="E142" s="76" t="s">
         <v>2054</v>
       </c>
-      <c r="F142" s="160" t="s">
+      <c r="F142" s="159" t="s">
         <v>2055</v>
       </c>
-      <c r="G142" s="160"/>
-      <c r="H142" s="160"/>
-      <c r="I142" s="160"/>
-      <c r="J142" s="160"/>
-      <c r="K142" s="160"/>
-      <c r="L142" s="160"/>
-      <c r="M142" s="160"/>
-      <c r="N142" s="160"/>
-      <c r="O142" s="160"/>
-      <c r="P142" s="160"/>
-      <c r="Q142" s="160"/>
-      <c r="R142" s="160"/>
-      <c r="S142" s="160"/>
-      <c r="T142" s="160"/>
-      <c r="U142" s="160"/>
+      <c r="G142" s="159"/>
+      <c r="H142" s="159"/>
+      <c r="I142" s="159"/>
+      <c r="J142" s="159"/>
+      <c r="K142" s="159"/>
+      <c r="L142" s="159"/>
+      <c r="M142" s="159"/>
+      <c r="N142" s="159"/>
+      <c r="O142" s="159"/>
+      <c r="P142" s="159"/>
+      <c r="Q142" s="159"/>
+      <c r="R142" s="159"/>
+      <c r="S142" s="159"/>
+      <c r="T142" s="159"/>
+      <c r="U142" s="159"/>
       <c r="V142" s="19"/>
     </row>
     <row r="143" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17189,24 +17210,24 @@
       <c r="E143" s="76" t="s">
         <v>2033</v>
       </c>
-      <c r="F143" s="160" t="s">
+      <c r="F143" s="159" t="s">
         <v>2058</v>
       </c>
-      <c r="G143" s="160"/>
-      <c r="H143" s="160"/>
-      <c r="I143" s="160"/>
-      <c r="J143" s="160"/>
-      <c r="K143" s="160"/>
-      <c r="L143" s="160"/>
-      <c r="M143" s="160"/>
-      <c r="N143" s="160"/>
-      <c r="O143" s="160"/>
-      <c r="P143" s="160"/>
-      <c r="Q143" s="160"/>
-      <c r="R143" s="160"/>
-      <c r="S143" s="160"/>
-      <c r="T143" s="160"/>
-      <c r="U143" s="160"/>
+      <c r="G143" s="159"/>
+      <c r="H143" s="159"/>
+      <c r="I143" s="159"/>
+      <c r="J143" s="159"/>
+      <c r="K143" s="159"/>
+      <c r="L143" s="159"/>
+      <c r="M143" s="159"/>
+      <c r="N143" s="159"/>
+      <c r="O143" s="159"/>
+      <c r="P143" s="159"/>
+      <c r="Q143" s="159"/>
+      <c r="R143" s="159"/>
+      <c r="S143" s="159"/>
+      <c r="T143" s="159"/>
+      <c r="U143" s="159"/>
       <c r="V143" s="19"/>
     </row>
     <row r="144" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17225,24 +17246,24 @@
       <c r="E144" s="76" t="s">
         <v>2060</v>
       </c>
-      <c r="F144" s="160" t="s">
+      <c r="F144" s="159" t="s">
         <v>2061</v>
       </c>
-      <c r="G144" s="160"/>
-      <c r="H144" s="160"/>
-      <c r="I144" s="160"/>
-      <c r="J144" s="160"/>
-      <c r="K144" s="160"/>
-      <c r="L144" s="160"/>
-      <c r="M144" s="160"/>
-      <c r="N144" s="160"/>
-      <c r="O144" s="160"/>
-      <c r="P144" s="160"/>
-      <c r="Q144" s="160"/>
-      <c r="R144" s="160"/>
-      <c r="S144" s="160"/>
-      <c r="T144" s="160"/>
-      <c r="U144" s="160"/>
+      <c r="G144" s="159"/>
+      <c r="H144" s="159"/>
+      <c r="I144" s="159"/>
+      <c r="J144" s="159"/>
+      <c r="K144" s="159"/>
+      <c r="L144" s="159"/>
+      <c r="M144" s="159"/>
+      <c r="N144" s="159"/>
+      <c r="O144" s="159"/>
+      <c r="P144" s="159"/>
+      <c r="Q144" s="159"/>
+      <c r="R144" s="159"/>
+      <c r="S144" s="159"/>
+      <c r="T144" s="159"/>
+      <c r="U144" s="159"/>
       <c r="V144" s="19"/>
     </row>
     <row r="145" spans="1:22" x14ac:dyDescent="0.25">
@@ -17261,24 +17282,24 @@
       <c r="E145" s="76" t="s">
         <v>2066</v>
       </c>
-      <c r="F145" s="161" t="s">
+      <c r="F145" s="163" t="s">
         <v>2064</v>
       </c>
-      <c r="G145" s="161"/>
-      <c r="H145" s="161"/>
-      <c r="I145" s="161"/>
-      <c r="J145" s="161"/>
-      <c r="K145" s="161"/>
-      <c r="L145" s="161"/>
-      <c r="M145" s="161"/>
-      <c r="N145" s="161"/>
-      <c r="O145" s="161"/>
-      <c r="P145" s="161"/>
-      <c r="Q145" s="161"/>
-      <c r="R145" s="161"/>
-      <c r="S145" s="161"/>
-      <c r="T145" s="161"/>
-      <c r="U145" s="161"/>
+      <c r="G145" s="163"/>
+      <c r="H145" s="163"/>
+      <c r="I145" s="163"/>
+      <c r="J145" s="163"/>
+      <c r="K145" s="163"/>
+      <c r="L145" s="163"/>
+      <c r="M145" s="163"/>
+      <c r="N145" s="163"/>
+      <c r="O145" s="163"/>
+      <c r="P145" s="163"/>
+      <c r="Q145" s="163"/>
+      <c r="R145" s="163"/>
+      <c r="S145" s="163"/>
+      <c r="T145" s="163"/>
+      <c r="U145" s="163"/>
       <c r="V145" s="19"/>
     </row>
     <row r="146" spans="1:22" x14ac:dyDescent="0.25">
@@ -17297,24 +17318,24 @@
       <c r="E146" s="94" t="s">
         <v>1039</v>
       </c>
-      <c r="F146" s="161" t="s">
+      <c r="F146" s="163" t="s">
         <v>2069</v>
       </c>
-      <c r="G146" s="161"/>
-      <c r="H146" s="161"/>
-      <c r="I146" s="161"/>
-      <c r="J146" s="161"/>
-      <c r="K146" s="161"/>
-      <c r="L146" s="161"/>
-      <c r="M146" s="161"/>
-      <c r="N146" s="161"/>
-      <c r="O146" s="161"/>
-      <c r="P146" s="161"/>
-      <c r="Q146" s="161"/>
-      <c r="R146" s="161"/>
-      <c r="S146" s="161"/>
-      <c r="T146" s="161"/>
-      <c r="U146" s="161"/>
+      <c r="G146" s="163"/>
+      <c r="H146" s="163"/>
+      <c r="I146" s="163"/>
+      <c r="J146" s="163"/>
+      <c r="K146" s="163"/>
+      <c r="L146" s="163"/>
+      <c r="M146" s="163"/>
+      <c r="N146" s="163"/>
+      <c r="O146" s="163"/>
+      <c r="P146" s="163"/>
+      <c r="Q146" s="163"/>
+      <c r="R146" s="163"/>
+      <c r="S146" s="163"/>
+      <c r="T146" s="163"/>
+      <c r="U146" s="163"/>
       <c r="V146" s="19"/>
     </row>
     <row r="147" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17333,24 +17354,24 @@
       <c r="E147" s="76" t="s">
         <v>2071</v>
       </c>
-      <c r="F147" s="160" t="s">
+      <c r="F147" s="159" t="s">
         <v>2072</v>
       </c>
-      <c r="G147" s="160"/>
-      <c r="H147" s="160"/>
-      <c r="I147" s="160"/>
-      <c r="J147" s="160"/>
-      <c r="K147" s="160"/>
-      <c r="L147" s="160"/>
-      <c r="M147" s="160"/>
-      <c r="N147" s="160"/>
-      <c r="O147" s="160"/>
-      <c r="P147" s="160"/>
-      <c r="Q147" s="160"/>
-      <c r="R147" s="160"/>
-      <c r="S147" s="160"/>
-      <c r="T147" s="160"/>
-      <c r="U147" s="160"/>
+      <c r="G147" s="159"/>
+      <c r="H147" s="159"/>
+      <c r="I147" s="159"/>
+      <c r="J147" s="159"/>
+      <c r="K147" s="159"/>
+      <c r="L147" s="159"/>
+      <c r="M147" s="159"/>
+      <c r="N147" s="159"/>
+      <c r="O147" s="159"/>
+      <c r="P147" s="159"/>
+      <c r="Q147" s="159"/>
+      <c r="R147" s="159"/>
+      <c r="S147" s="159"/>
+      <c r="T147" s="159"/>
+      <c r="U147" s="159"/>
       <c r="V147" s="19"/>
     </row>
     <row r="148" spans="1:22" x14ac:dyDescent="0.25">
@@ -17369,24 +17390,24 @@
       <c r="E148" s="76" t="s">
         <v>2079</v>
       </c>
-      <c r="F148" s="161" t="s">
+      <c r="F148" s="163" t="s">
         <v>2075</v>
       </c>
-      <c r="G148" s="161"/>
-      <c r="H148" s="161"/>
-      <c r="I148" s="161"/>
-      <c r="J148" s="161"/>
-      <c r="K148" s="161"/>
-      <c r="L148" s="161"/>
-      <c r="M148" s="161"/>
-      <c r="N148" s="161"/>
-      <c r="O148" s="161"/>
-      <c r="P148" s="161"/>
-      <c r="Q148" s="161"/>
-      <c r="R148" s="161"/>
-      <c r="S148" s="161"/>
-      <c r="T148" s="161"/>
-      <c r="U148" s="161"/>
+      <c r="G148" s="163"/>
+      <c r="H148" s="163"/>
+      <c r="I148" s="163"/>
+      <c r="J148" s="163"/>
+      <c r="K148" s="163"/>
+      <c r="L148" s="163"/>
+      <c r="M148" s="163"/>
+      <c r="N148" s="163"/>
+      <c r="O148" s="163"/>
+      <c r="P148" s="163"/>
+      <c r="Q148" s="163"/>
+      <c r="R148" s="163"/>
+      <c r="S148" s="163"/>
+      <c r="T148" s="163"/>
+      <c r="U148" s="163"/>
       <c r="V148" s="19"/>
     </row>
     <row r="149" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17405,24 +17426,24 @@
       <c r="E149" s="76" t="s">
         <v>2078</v>
       </c>
-      <c r="F149" s="160" t="s">
+      <c r="F149" s="159" t="s">
         <v>2080</v>
       </c>
-      <c r="G149" s="160"/>
-      <c r="H149" s="160"/>
-      <c r="I149" s="160"/>
-      <c r="J149" s="160"/>
-      <c r="K149" s="160"/>
-      <c r="L149" s="160"/>
-      <c r="M149" s="160"/>
-      <c r="N149" s="160"/>
-      <c r="O149" s="160"/>
-      <c r="P149" s="160"/>
-      <c r="Q149" s="160"/>
-      <c r="R149" s="160"/>
-      <c r="S149" s="160"/>
-      <c r="T149" s="160"/>
-      <c r="U149" s="160"/>
+      <c r="G149" s="159"/>
+      <c r="H149" s="159"/>
+      <c r="I149" s="159"/>
+      <c r="J149" s="159"/>
+      <c r="K149" s="159"/>
+      <c r="L149" s="159"/>
+      <c r="M149" s="159"/>
+      <c r="N149" s="159"/>
+      <c r="O149" s="159"/>
+      <c r="P149" s="159"/>
+      <c r="Q149" s="159"/>
+      <c r="R149" s="159"/>
+      <c r="S149" s="159"/>
+      <c r="T149" s="159"/>
+      <c r="U149" s="159"/>
       <c r="V149" s="19"/>
     </row>
     <row r="150" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17441,24 +17462,24 @@
       <c r="E150" s="76" t="s">
         <v>2083</v>
       </c>
-      <c r="F150" s="160" t="s">
+      <c r="F150" s="159" t="s">
         <v>2084</v>
       </c>
-      <c r="G150" s="160"/>
-      <c r="H150" s="160"/>
-      <c r="I150" s="160"/>
-      <c r="J150" s="160"/>
-      <c r="K150" s="160"/>
-      <c r="L150" s="160"/>
-      <c r="M150" s="160"/>
-      <c r="N150" s="160"/>
-      <c r="O150" s="160"/>
-      <c r="P150" s="160"/>
-      <c r="Q150" s="160"/>
-      <c r="R150" s="160"/>
-      <c r="S150" s="160"/>
-      <c r="T150" s="160"/>
-      <c r="U150" s="160"/>
+      <c r="G150" s="159"/>
+      <c r="H150" s="159"/>
+      <c r="I150" s="159"/>
+      <c r="J150" s="159"/>
+      <c r="K150" s="159"/>
+      <c r="L150" s="159"/>
+      <c r="M150" s="159"/>
+      <c r="N150" s="159"/>
+      <c r="O150" s="159"/>
+      <c r="P150" s="159"/>
+      <c r="Q150" s="159"/>
+      <c r="R150" s="159"/>
+      <c r="S150" s="159"/>
+      <c r="T150" s="159"/>
+      <c r="U150" s="159"/>
       <c r="V150" s="19"/>
     </row>
     <row r="151" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17477,24 +17498,24 @@
       <c r="E151" s="76" t="s">
         <v>2087</v>
       </c>
-      <c r="F151" s="160" t="s">
+      <c r="F151" s="159" t="s">
         <v>2088</v>
       </c>
-      <c r="G151" s="160"/>
-      <c r="H151" s="160"/>
-      <c r="I151" s="160"/>
-      <c r="J151" s="160"/>
-      <c r="K151" s="160"/>
-      <c r="L151" s="160"/>
-      <c r="M151" s="160"/>
-      <c r="N151" s="160"/>
-      <c r="O151" s="160"/>
-      <c r="P151" s="160"/>
-      <c r="Q151" s="160"/>
-      <c r="R151" s="160"/>
-      <c r="S151" s="160"/>
-      <c r="T151" s="160"/>
-      <c r="U151" s="160"/>
+      <c r="G151" s="159"/>
+      <c r="H151" s="159"/>
+      <c r="I151" s="159"/>
+      <c r="J151" s="159"/>
+      <c r="K151" s="159"/>
+      <c r="L151" s="159"/>
+      <c r="M151" s="159"/>
+      <c r="N151" s="159"/>
+      <c r="O151" s="159"/>
+      <c r="P151" s="159"/>
+      <c r="Q151" s="159"/>
+      <c r="R151" s="159"/>
+      <c r="S151" s="159"/>
+      <c r="T151" s="159"/>
+      <c r="U151" s="159"/>
       <c r="V151" s="19"/>
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.25">
@@ -17513,24 +17534,24 @@
       <c r="E152" s="76" t="s">
         <v>2090</v>
       </c>
-      <c r="F152" s="161" t="s">
+      <c r="F152" s="163" t="s">
         <v>2091</v>
       </c>
-      <c r="G152" s="161"/>
-      <c r="H152" s="161"/>
-      <c r="I152" s="161"/>
-      <c r="J152" s="161"/>
-      <c r="K152" s="161"/>
-      <c r="L152" s="161"/>
-      <c r="M152" s="161"/>
-      <c r="N152" s="161"/>
-      <c r="O152" s="161"/>
-      <c r="P152" s="161"/>
-      <c r="Q152" s="161"/>
-      <c r="R152" s="161"/>
-      <c r="S152" s="161"/>
-      <c r="T152" s="161"/>
-      <c r="U152" s="161"/>
+      <c r="G152" s="163"/>
+      <c r="H152" s="163"/>
+      <c r="I152" s="163"/>
+      <c r="J152" s="163"/>
+      <c r="K152" s="163"/>
+      <c r="L152" s="163"/>
+      <c r="M152" s="163"/>
+      <c r="N152" s="163"/>
+      <c r="O152" s="163"/>
+      <c r="P152" s="163"/>
+      <c r="Q152" s="163"/>
+      <c r="R152" s="163"/>
+      <c r="S152" s="163"/>
+      <c r="T152" s="163"/>
+      <c r="U152" s="163"/>
       <c r="V152" s="19"/>
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.25">
@@ -17549,24 +17570,24 @@
       <c r="E153" s="76" t="s">
         <v>2094</v>
       </c>
-      <c r="F153" s="161" t="s">
+      <c r="F153" s="163" t="s">
         <v>2095</v>
       </c>
-      <c r="G153" s="161"/>
-      <c r="H153" s="161"/>
-      <c r="I153" s="161"/>
-      <c r="J153" s="161"/>
-      <c r="K153" s="161"/>
-      <c r="L153" s="161"/>
-      <c r="M153" s="161"/>
-      <c r="N153" s="161"/>
-      <c r="O153" s="161"/>
-      <c r="P153" s="161"/>
-      <c r="Q153" s="161"/>
-      <c r="R153" s="161"/>
-      <c r="S153" s="161"/>
-      <c r="T153" s="161"/>
-      <c r="U153" s="161"/>
+      <c r="G153" s="163"/>
+      <c r="H153" s="163"/>
+      <c r="I153" s="163"/>
+      <c r="J153" s="163"/>
+      <c r="K153" s="163"/>
+      <c r="L153" s="163"/>
+      <c r="M153" s="163"/>
+      <c r="N153" s="163"/>
+      <c r="O153" s="163"/>
+      <c r="P153" s="163"/>
+      <c r="Q153" s="163"/>
+      <c r="R153" s="163"/>
+      <c r="S153" s="163"/>
+      <c r="T153" s="163"/>
+      <c r="U153" s="163"/>
       <c r="V153" s="19"/>
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.25">
@@ -17585,24 +17606,24 @@
       <c r="E154" s="94" t="s">
         <v>1039</v>
       </c>
-      <c r="F154" s="161" t="s">
+      <c r="F154" s="163" t="s">
         <v>2097</v>
       </c>
-      <c r="G154" s="161"/>
-      <c r="H154" s="161"/>
-      <c r="I154" s="161"/>
-      <c r="J154" s="161"/>
-      <c r="K154" s="161"/>
-      <c r="L154" s="161"/>
-      <c r="M154" s="161"/>
-      <c r="N154" s="161"/>
-      <c r="O154" s="161"/>
-      <c r="P154" s="161"/>
-      <c r="Q154" s="161"/>
-      <c r="R154" s="161"/>
-      <c r="S154" s="161"/>
-      <c r="T154" s="161"/>
-      <c r="U154" s="161"/>
+      <c r="G154" s="163"/>
+      <c r="H154" s="163"/>
+      <c r="I154" s="163"/>
+      <c r="J154" s="163"/>
+      <c r="K154" s="163"/>
+      <c r="L154" s="163"/>
+      <c r="M154" s="163"/>
+      <c r="N154" s="163"/>
+      <c r="O154" s="163"/>
+      <c r="P154" s="163"/>
+      <c r="Q154" s="163"/>
+      <c r="R154" s="163"/>
+      <c r="S154" s="163"/>
+      <c r="T154" s="163"/>
+      <c r="U154" s="163"/>
       <c r="V154" s="19"/>
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.25">
@@ -17621,24 +17642,24 @@
       <c r="E155" s="94" t="s">
         <v>1039</v>
       </c>
-      <c r="F155" s="161" t="s">
+      <c r="F155" s="163" t="s">
         <v>2099</v>
       </c>
-      <c r="G155" s="161"/>
-      <c r="H155" s="161"/>
-      <c r="I155" s="161"/>
-      <c r="J155" s="161"/>
-      <c r="K155" s="161"/>
-      <c r="L155" s="161"/>
-      <c r="M155" s="161"/>
-      <c r="N155" s="161"/>
-      <c r="O155" s="161"/>
-      <c r="P155" s="161"/>
-      <c r="Q155" s="161"/>
-      <c r="R155" s="161"/>
-      <c r="S155" s="161"/>
-      <c r="T155" s="161"/>
-      <c r="U155" s="161"/>
+      <c r="G155" s="163"/>
+      <c r="H155" s="163"/>
+      <c r="I155" s="163"/>
+      <c r="J155" s="163"/>
+      <c r="K155" s="163"/>
+      <c r="L155" s="163"/>
+      <c r="M155" s="163"/>
+      <c r="N155" s="163"/>
+      <c r="O155" s="163"/>
+      <c r="P155" s="163"/>
+      <c r="Q155" s="163"/>
+      <c r="R155" s="163"/>
+      <c r="S155" s="163"/>
+      <c r="T155" s="163"/>
+      <c r="U155" s="163"/>
       <c r="V155" s="19"/>
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.25">
@@ -17657,24 +17678,24 @@
       <c r="E156" s="76" t="s">
         <v>2103</v>
       </c>
-      <c r="F156" s="161" t="s">
+      <c r="F156" s="163" t="s">
         <v>2102</v>
       </c>
-      <c r="G156" s="161"/>
-      <c r="H156" s="161"/>
-      <c r="I156" s="161"/>
-      <c r="J156" s="161"/>
-      <c r="K156" s="161"/>
-      <c r="L156" s="161"/>
-      <c r="M156" s="161"/>
-      <c r="N156" s="161"/>
-      <c r="O156" s="161"/>
-      <c r="P156" s="161"/>
-      <c r="Q156" s="161"/>
-      <c r="R156" s="161"/>
-      <c r="S156" s="161"/>
-      <c r="T156" s="161"/>
-      <c r="U156" s="161"/>
+      <c r="G156" s="163"/>
+      <c r="H156" s="163"/>
+      <c r="I156" s="163"/>
+      <c r="J156" s="163"/>
+      <c r="K156" s="163"/>
+      <c r="L156" s="163"/>
+      <c r="M156" s="163"/>
+      <c r="N156" s="163"/>
+      <c r="O156" s="163"/>
+      <c r="P156" s="163"/>
+      <c r="Q156" s="163"/>
+      <c r="R156" s="163"/>
+      <c r="S156" s="163"/>
+      <c r="T156" s="163"/>
+      <c r="U156" s="163"/>
       <c r="V156" s="19"/>
     </row>
     <row r="157" spans="1:22" x14ac:dyDescent="0.25">
@@ -17693,24 +17714,24 @@
       <c r="E157" s="76" t="s">
         <v>2105</v>
       </c>
-      <c r="F157" s="162" t="s">
+      <c r="F157" s="164" t="s">
         <v>2106</v>
       </c>
-      <c r="G157" s="162"/>
-      <c r="H157" s="162"/>
-      <c r="I157" s="162"/>
-      <c r="J157" s="162"/>
-      <c r="K157" s="162"/>
-      <c r="L157" s="162"/>
-      <c r="M157" s="162"/>
-      <c r="N157" s="162"/>
-      <c r="O157" s="162"/>
-      <c r="P157" s="162"/>
-      <c r="Q157" s="162"/>
-      <c r="R157" s="162"/>
-      <c r="S157" s="162"/>
-      <c r="T157" s="162"/>
-      <c r="U157" s="162"/>
+      <c r="G157" s="164"/>
+      <c r="H157" s="164"/>
+      <c r="I157" s="164"/>
+      <c r="J157" s="164"/>
+      <c r="K157" s="164"/>
+      <c r="L157" s="164"/>
+      <c r="M157" s="164"/>
+      <c r="N157" s="164"/>
+      <c r="O157" s="164"/>
+      <c r="P157" s="164"/>
+      <c r="Q157" s="164"/>
+      <c r="R157" s="164"/>
+      <c r="S157" s="164"/>
+      <c r="T157" s="164"/>
+      <c r="U157" s="164"/>
       <c r="V157" s="19"/>
     </row>
     <row r="158" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17729,24 +17750,24 @@
       <c r="E158" s="76" t="s">
         <v>2109</v>
       </c>
-      <c r="F158" s="160" t="s">
+      <c r="F158" s="159" t="s">
         <v>2110</v>
       </c>
-      <c r="G158" s="160"/>
-      <c r="H158" s="160"/>
-      <c r="I158" s="160"/>
-      <c r="J158" s="160"/>
-      <c r="K158" s="160"/>
-      <c r="L158" s="160"/>
-      <c r="M158" s="160"/>
-      <c r="N158" s="160"/>
-      <c r="O158" s="160"/>
-      <c r="P158" s="160"/>
-      <c r="Q158" s="160"/>
-      <c r="R158" s="160"/>
-      <c r="S158" s="160"/>
-      <c r="T158" s="160"/>
-      <c r="U158" s="160"/>
+      <c r="G158" s="159"/>
+      <c r="H158" s="159"/>
+      <c r="I158" s="159"/>
+      <c r="J158" s="159"/>
+      <c r="K158" s="159"/>
+      <c r="L158" s="159"/>
+      <c r="M158" s="159"/>
+      <c r="N158" s="159"/>
+      <c r="O158" s="159"/>
+      <c r="P158" s="159"/>
+      <c r="Q158" s="159"/>
+      <c r="R158" s="159"/>
+      <c r="S158" s="159"/>
+      <c r="T158" s="159"/>
+      <c r="U158" s="159"/>
       <c r="V158" s="19"/>
     </row>
     <row r="159" spans="1:22" x14ac:dyDescent="0.25">
@@ -17755,22 +17776,22 @@
       <c r="C159" s="77"/>
       <c r="D159" s="76"/>
       <c r="E159" s="76"/>
-      <c r="F159" s="162"/>
-      <c r="G159" s="162"/>
-      <c r="H159" s="162"/>
-      <c r="I159" s="162"/>
-      <c r="J159" s="162"/>
-      <c r="K159" s="162"/>
-      <c r="L159" s="162"/>
-      <c r="M159" s="162"/>
-      <c r="N159" s="162"/>
-      <c r="O159" s="162"/>
-      <c r="P159" s="162"/>
-      <c r="Q159" s="162"/>
-      <c r="R159" s="162"/>
-      <c r="S159" s="162"/>
-      <c r="T159" s="162"/>
-      <c r="U159" s="162"/>
+      <c r="F159" s="164"/>
+      <c r="G159" s="164"/>
+      <c r="H159" s="164"/>
+      <c r="I159" s="164"/>
+      <c r="J159" s="164"/>
+      <c r="K159" s="164"/>
+      <c r="L159" s="164"/>
+      <c r="M159" s="164"/>
+      <c r="N159" s="164"/>
+      <c r="O159" s="164"/>
+      <c r="P159" s="164"/>
+      <c r="Q159" s="164"/>
+      <c r="R159" s="164"/>
+      <c r="S159" s="164"/>
+      <c r="T159" s="164"/>
+      <c r="U159" s="164"/>
       <c r="V159" s="19"/>
     </row>
     <row r="160" spans="1:22" x14ac:dyDescent="0.25">
@@ -17779,22 +17800,22 @@
       <c r="C160" s="77"/>
       <c r="D160" s="76"/>
       <c r="E160" s="76"/>
-      <c r="F160" s="162"/>
-      <c r="G160" s="162"/>
-      <c r="H160" s="162"/>
-      <c r="I160" s="162"/>
-      <c r="J160" s="162"/>
-      <c r="K160" s="162"/>
-      <c r="L160" s="162"/>
-      <c r="M160" s="162"/>
-      <c r="N160" s="162"/>
-      <c r="O160" s="162"/>
-      <c r="P160" s="162"/>
-      <c r="Q160" s="162"/>
-      <c r="R160" s="162"/>
-      <c r="S160" s="162"/>
-      <c r="T160" s="162"/>
-      <c r="U160" s="162"/>
+      <c r="F160" s="164"/>
+      <c r="G160" s="164"/>
+      <c r="H160" s="164"/>
+      <c r="I160" s="164"/>
+      <c r="J160" s="164"/>
+      <c r="K160" s="164"/>
+      <c r="L160" s="164"/>
+      <c r="M160" s="164"/>
+      <c r="N160" s="164"/>
+      <c r="O160" s="164"/>
+      <c r="P160" s="164"/>
+      <c r="Q160" s="164"/>
+      <c r="R160" s="164"/>
+      <c r="S160" s="164"/>
+      <c r="T160" s="164"/>
+      <c r="U160" s="164"/>
       <c r="V160" s="19"/>
     </row>
     <row r="161" spans="1:22" x14ac:dyDescent="0.25">
@@ -17803,22 +17824,22 @@
       <c r="C161" s="77"/>
       <c r="D161" s="76"/>
       <c r="E161" s="76"/>
-      <c r="F161" s="162"/>
-      <c r="G161" s="162"/>
-      <c r="H161" s="162"/>
-      <c r="I161" s="162"/>
-      <c r="J161" s="162"/>
-      <c r="K161" s="162"/>
-      <c r="L161" s="162"/>
-      <c r="M161" s="162"/>
-      <c r="N161" s="162"/>
-      <c r="O161" s="162"/>
-      <c r="P161" s="162"/>
-      <c r="Q161" s="162"/>
-      <c r="R161" s="162"/>
-      <c r="S161" s="162"/>
-      <c r="T161" s="162"/>
-      <c r="U161" s="162"/>
+      <c r="F161" s="164"/>
+      <c r="G161" s="164"/>
+      <c r="H161" s="164"/>
+      <c r="I161" s="164"/>
+      <c r="J161" s="164"/>
+      <c r="K161" s="164"/>
+      <c r="L161" s="164"/>
+      <c r="M161" s="164"/>
+      <c r="N161" s="164"/>
+      <c r="O161" s="164"/>
+      <c r="P161" s="164"/>
+      <c r="Q161" s="164"/>
+      <c r="R161" s="164"/>
+      <c r="S161" s="164"/>
+      <c r="T161" s="164"/>
+      <c r="U161" s="164"/>
       <c r="V161" s="19"/>
     </row>
     <row r="162" spans="1:22" x14ac:dyDescent="0.25">
@@ -17827,22 +17848,22 @@
       <c r="C162" s="77"/>
       <c r="D162" s="76"/>
       <c r="E162" s="76"/>
-      <c r="F162" s="162"/>
-      <c r="G162" s="162"/>
-      <c r="H162" s="162"/>
-      <c r="I162" s="162"/>
-      <c r="J162" s="162"/>
-      <c r="K162" s="162"/>
-      <c r="L162" s="162"/>
-      <c r="M162" s="162"/>
-      <c r="N162" s="162"/>
-      <c r="O162" s="162"/>
-      <c r="P162" s="162"/>
-      <c r="Q162" s="162"/>
-      <c r="R162" s="162"/>
-      <c r="S162" s="162"/>
-      <c r="T162" s="162"/>
-      <c r="U162" s="162"/>
+      <c r="F162" s="164"/>
+      <c r="G162" s="164"/>
+      <c r="H162" s="164"/>
+      <c r="I162" s="164"/>
+      <c r="J162" s="164"/>
+      <c r="K162" s="164"/>
+      <c r="L162" s="164"/>
+      <c r="M162" s="164"/>
+      <c r="N162" s="164"/>
+      <c r="O162" s="164"/>
+      <c r="P162" s="164"/>
+      <c r="Q162" s="164"/>
+      <c r="R162" s="164"/>
+      <c r="S162" s="164"/>
+      <c r="T162" s="164"/>
+      <c r="U162" s="164"/>
       <c r="V162" s="19"/>
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.25">
@@ -17851,22 +17872,22 @@
       <c r="C163" s="77"/>
       <c r="D163" s="76"/>
       <c r="E163" s="76"/>
-      <c r="F163" s="162"/>
-      <c r="G163" s="162"/>
-      <c r="H163" s="162"/>
-      <c r="I163" s="162"/>
-      <c r="J163" s="162"/>
-      <c r="K163" s="162"/>
-      <c r="L163" s="162"/>
-      <c r="M163" s="162"/>
-      <c r="N163" s="162"/>
-      <c r="O163" s="162"/>
-      <c r="P163" s="162"/>
-      <c r="Q163" s="162"/>
-      <c r="R163" s="162"/>
-      <c r="S163" s="162"/>
-      <c r="T163" s="162"/>
-      <c r="U163" s="162"/>
+      <c r="F163" s="164"/>
+      <c r="G163" s="164"/>
+      <c r="H163" s="164"/>
+      <c r="I163" s="164"/>
+      <c r="J163" s="164"/>
+      <c r="K163" s="164"/>
+      <c r="L163" s="164"/>
+      <c r="M163" s="164"/>
+      <c r="N163" s="164"/>
+      <c r="O163" s="164"/>
+      <c r="P163" s="164"/>
+      <c r="Q163" s="164"/>
+      <c r="R163" s="164"/>
+      <c r="S163" s="164"/>
+      <c r="T163" s="164"/>
+      <c r="U163" s="164"/>
       <c r="V163" s="19"/>
     </row>
     <row r="164" spans="1:22" x14ac:dyDescent="0.25">
@@ -17875,22 +17896,22 @@
       <c r="C164" s="77"/>
       <c r="D164" s="76"/>
       <c r="E164" s="76"/>
-      <c r="F164" s="162"/>
-      <c r="G164" s="162"/>
-      <c r="H164" s="162"/>
-      <c r="I164" s="162"/>
-      <c r="J164" s="162"/>
-      <c r="K164" s="162"/>
-      <c r="L164" s="162"/>
-      <c r="M164" s="162"/>
-      <c r="N164" s="162"/>
-      <c r="O164" s="162"/>
-      <c r="P164" s="162"/>
-      <c r="Q164" s="162"/>
-      <c r="R164" s="162"/>
-      <c r="S164" s="162"/>
-      <c r="T164" s="162"/>
-      <c r="U164" s="162"/>
+      <c r="F164" s="164"/>
+      <c r="G164" s="164"/>
+      <c r="H164" s="164"/>
+      <c r="I164" s="164"/>
+      <c r="J164" s="164"/>
+      <c r="K164" s="164"/>
+      <c r="L164" s="164"/>
+      <c r="M164" s="164"/>
+      <c r="N164" s="164"/>
+      <c r="O164" s="164"/>
+      <c r="P164" s="164"/>
+      <c r="Q164" s="164"/>
+      <c r="R164" s="164"/>
+      <c r="S164" s="164"/>
+      <c r="T164" s="164"/>
+      <c r="U164" s="164"/>
       <c r="V164" s="19"/>
     </row>
     <row r="165" spans="1:22" x14ac:dyDescent="0.25">
@@ -17899,22 +17920,22 @@
       <c r="C165" s="77"/>
       <c r="D165" s="76"/>
       <c r="E165" s="76"/>
-      <c r="F165" s="162"/>
-      <c r="G165" s="162"/>
-      <c r="H165" s="162"/>
-      <c r="I165" s="162"/>
-      <c r="J165" s="162"/>
-      <c r="K165" s="162"/>
-      <c r="L165" s="162"/>
-      <c r="M165" s="162"/>
-      <c r="N165" s="162"/>
-      <c r="O165" s="162"/>
-      <c r="P165" s="162"/>
-      <c r="Q165" s="162"/>
-      <c r="R165" s="162"/>
-      <c r="S165" s="162"/>
-      <c r="T165" s="162"/>
-      <c r="U165" s="162"/>
+      <c r="F165" s="164"/>
+      <c r="G165" s="164"/>
+      <c r="H165" s="164"/>
+      <c r="I165" s="164"/>
+      <c r="J165" s="164"/>
+      <c r="K165" s="164"/>
+      <c r="L165" s="164"/>
+      <c r="M165" s="164"/>
+      <c r="N165" s="164"/>
+      <c r="O165" s="164"/>
+      <c r="P165" s="164"/>
+      <c r="Q165" s="164"/>
+      <c r="R165" s="164"/>
+      <c r="S165" s="164"/>
+      <c r="T165" s="164"/>
+      <c r="U165" s="164"/>
       <c r="V165" s="19"/>
     </row>
     <row r="166" spans="1:22" x14ac:dyDescent="0.25">
@@ -17923,22 +17944,22 @@
       <c r="C166" s="77"/>
       <c r="D166" s="76"/>
       <c r="E166" s="76"/>
-      <c r="F166" s="162"/>
-      <c r="G166" s="162"/>
-      <c r="H166" s="162"/>
-      <c r="I166" s="162"/>
-      <c r="J166" s="162"/>
-      <c r="K166" s="162"/>
-      <c r="L166" s="162"/>
-      <c r="M166" s="162"/>
-      <c r="N166" s="162"/>
-      <c r="O166" s="162"/>
-      <c r="P166" s="162"/>
-      <c r="Q166" s="162"/>
-      <c r="R166" s="162"/>
-      <c r="S166" s="162"/>
-      <c r="T166" s="162"/>
-      <c r="U166" s="162"/>
+      <c r="F166" s="164"/>
+      <c r="G166" s="164"/>
+      <c r="H166" s="164"/>
+      <c r="I166" s="164"/>
+      <c r="J166" s="164"/>
+      <c r="K166" s="164"/>
+      <c r="L166" s="164"/>
+      <c r="M166" s="164"/>
+      <c r="N166" s="164"/>
+      <c r="O166" s="164"/>
+      <c r="P166" s="164"/>
+      <c r="Q166" s="164"/>
+      <c r="R166" s="164"/>
+      <c r="S166" s="164"/>
+      <c r="T166" s="164"/>
+      <c r="U166" s="164"/>
       <c r="V166" s="19"/>
     </row>
     <row r="167" spans="1:22" x14ac:dyDescent="0.25">
@@ -17947,22 +17968,22 @@
       <c r="C167" s="77"/>
       <c r="D167" s="76"/>
       <c r="E167" s="76"/>
-      <c r="F167" s="162"/>
-      <c r="G167" s="162"/>
-      <c r="H167" s="162"/>
-      <c r="I167" s="162"/>
-      <c r="J167" s="162"/>
-      <c r="K167" s="162"/>
-      <c r="L167" s="162"/>
-      <c r="M167" s="162"/>
-      <c r="N167" s="162"/>
-      <c r="O167" s="162"/>
-      <c r="P167" s="162"/>
-      <c r="Q167" s="162"/>
-      <c r="R167" s="162"/>
-      <c r="S167" s="162"/>
-      <c r="T167" s="162"/>
-      <c r="U167" s="162"/>
+      <c r="F167" s="164"/>
+      <c r="G167" s="164"/>
+      <c r="H167" s="164"/>
+      <c r="I167" s="164"/>
+      <c r="J167" s="164"/>
+      <c r="K167" s="164"/>
+      <c r="L167" s="164"/>
+      <c r="M167" s="164"/>
+      <c r="N167" s="164"/>
+      <c r="O167" s="164"/>
+      <c r="P167" s="164"/>
+      <c r="Q167" s="164"/>
+      <c r="R167" s="164"/>
+      <c r="S167" s="164"/>
+      <c r="T167" s="164"/>
+      <c r="U167" s="164"/>
       <c r="V167" s="19"/>
     </row>
     <row r="168" spans="1:22" x14ac:dyDescent="0.25">
@@ -17971,22 +17992,22 @@
       <c r="C168" s="77"/>
       <c r="D168" s="76"/>
       <c r="E168" s="76"/>
-      <c r="F168" s="162"/>
-      <c r="G168" s="162"/>
-      <c r="H168" s="162"/>
-      <c r="I168" s="162"/>
-      <c r="J168" s="162"/>
-      <c r="K168" s="162"/>
-      <c r="L168" s="162"/>
-      <c r="M168" s="162"/>
-      <c r="N168" s="162"/>
-      <c r="O168" s="162"/>
-      <c r="P168" s="162"/>
-      <c r="Q168" s="162"/>
-      <c r="R168" s="162"/>
-      <c r="S168" s="162"/>
-      <c r="T168" s="162"/>
-      <c r="U168" s="162"/>
+      <c r="F168" s="164"/>
+      <c r="G168" s="164"/>
+      <c r="H168" s="164"/>
+      <c r="I168" s="164"/>
+      <c r="J168" s="164"/>
+      <c r="K168" s="164"/>
+      <c r="L168" s="164"/>
+      <c r="M168" s="164"/>
+      <c r="N168" s="164"/>
+      <c r="O168" s="164"/>
+      <c r="P168" s="164"/>
+      <c r="Q168" s="164"/>
+      <c r="R168" s="164"/>
+      <c r="S168" s="164"/>
+      <c r="T168" s="164"/>
+      <c r="U168" s="164"/>
       <c r="V168" s="19"/>
     </row>
     <row r="169" spans="1:22" x14ac:dyDescent="0.25">
@@ -17995,22 +18016,22 @@
       <c r="C169" s="77"/>
       <c r="D169" s="76"/>
       <c r="E169" s="76"/>
-      <c r="F169" s="162"/>
-      <c r="G169" s="162"/>
-      <c r="H169" s="162"/>
-      <c r="I169" s="162"/>
-      <c r="J169" s="162"/>
-      <c r="K169" s="162"/>
-      <c r="L169" s="162"/>
-      <c r="M169" s="162"/>
-      <c r="N169" s="162"/>
-      <c r="O169" s="162"/>
-      <c r="P169" s="162"/>
-      <c r="Q169" s="162"/>
-      <c r="R169" s="162"/>
-      <c r="S169" s="162"/>
-      <c r="T169" s="162"/>
-      <c r="U169" s="162"/>
+      <c r="F169" s="164"/>
+      <c r="G169" s="164"/>
+      <c r="H169" s="164"/>
+      <c r="I169" s="164"/>
+      <c r="J169" s="164"/>
+      <c r="K169" s="164"/>
+      <c r="L169" s="164"/>
+      <c r="M169" s="164"/>
+      <c r="N169" s="164"/>
+      <c r="O169" s="164"/>
+      <c r="P169" s="164"/>
+      <c r="Q169" s="164"/>
+      <c r="R169" s="164"/>
+      <c r="S169" s="164"/>
+      <c r="T169" s="164"/>
+      <c r="U169" s="164"/>
       <c r="V169" s="19"/>
     </row>
     <row r="170" spans="1:22" x14ac:dyDescent="0.25">
@@ -18019,22 +18040,22 @@
       <c r="C170" s="77"/>
       <c r="D170" s="76"/>
       <c r="E170" s="76"/>
-      <c r="F170" s="162"/>
-      <c r="G170" s="162"/>
-      <c r="H170" s="162"/>
-      <c r="I170" s="162"/>
-      <c r="J170" s="162"/>
-      <c r="K170" s="162"/>
-      <c r="L170" s="162"/>
-      <c r="M170" s="162"/>
-      <c r="N170" s="162"/>
-      <c r="O170" s="162"/>
-      <c r="P170" s="162"/>
-      <c r="Q170" s="162"/>
-      <c r="R170" s="162"/>
-      <c r="S170" s="162"/>
-      <c r="T170" s="162"/>
-      <c r="U170" s="162"/>
+      <c r="F170" s="164"/>
+      <c r="G170" s="164"/>
+      <c r="H170" s="164"/>
+      <c r="I170" s="164"/>
+      <c r="J170" s="164"/>
+      <c r="K170" s="164"/>
+      <c r="L170" s="164"/>
+      <c r="M170" s="164"/>
+      <c r="N170" s="164"/>
+      <c r="O170" s="164"/>
+      <c r="P170" s="164"/>
+      <c r="Q170" s="164"/>
+      <c r="R170" s="164"/>
+      <c r="S170" s="164"/>
+      <c r="T170" s="164"/>
+      <c r="U170" s="164"/>
       <c r="V170" s="19"/>
     </row>
     <row r="171" spans="1:22" x14ac:dyDescent="0.25">
@@ -18043,22 +18064,22 @@
       <c r="C171" s="77"/>
       <c r="D171" s="76"/>
       <c r="E171" s="76"/>
-      <c r="F171" s="162"/>
-      <c r="G171" s="162"/>
-      <c r="H171" s="162"/>
-      <c r="I171" s="162"/>
-      <c r="J171" s="162"/>
-      <c r="K171" s="162"/>
-      <c r="L171" s="162"/>
-      <c r="M171" s="162"/>
-      <c r="N171" s="162"/>
-      <c r="O171" s="162"/>
-      <c r="P171" s="162"/>
-      <c r="Q171" s="162"/>
-      <c r="R171" s="162"/>
-      <c r="S171" s="162"/>
-      <c r="T171" s="162"/>
-      <c r="U171" s="162"/>
+      <c r="F171" s="164"/>
+      <c r="G171" s="164"/>
+      <c r="H171" s="164"/>
+      <c r="I171" s="164"/>
+      <c r="J171" s="164"/>
+      <c r="K171" s="164"/>
+      <c r="L171" s="164"/>
+      <c r="M171" s="164"/>
+      <c r="N171" s="164"/>
+      <c r="O171" s="164"/>
+      <c r="P171" s="164"/>
+      <c r="Q171" s="164"/>
+      <c r="R171" s="164"/>
+      <c r="S171" s="164"/>
+      <c r="T171" s="164"/>
+      <c r="U171" s="164"/>
       <c r="V171" s="19"/>
     </row>
     <row r="172" spans="1:22" x14ac:dyDescent="0.25">
@@ -18067,22 +18088,22 @@
       <c r="C172" s="77"/>
       <c r="D172" s="76"/>
       <c r="E172" s="76"/>
-      <c r="F172" s="162"/>
-      <c r="G172" s="162"/>
-      <c r="H172" s="162"/>
-      <c r="I172" s="162"/>
-      <c r="J172" s="162"/>
-      <c r="K172" s="162"/>
-      <c r="L172" s="162"/>
-      <c r="M172" s="162"/>
-      <c r="N172" s="162"/>
-      <c r="O172" s="162"/>
-      <c r="P172" s="162"/>
-      <c r="Q172" s="162"/>
-      <c r="R172" s="162"/>
-      <c r="S172" s="162"/>
-      <c r="T172" s="162"/>
-      <c r="U172" s="162"/>
+      <c r="F172" s="164"/>
+      <c r="G172" s="164"/>
+      <c r="H172" s="164"/>
+      <c r="I172" s="164"/>
+      <c r="J172" s="164"/>
+      <c r="K172" s="164"/>
+      <c r="L172" s="164"/>
+      <c r="M172" s="164"/>
+      <c r="N172" s="164"/>
+      <c r="O172" s="164"/>
+      <c r="P172" s="164"/>
+      <c r="Q172" s="164"/>
+      <c r="R172" s="164"/>
+      <c r="S172" s="164"/>
+      <c r="T172" s="164"/>
+      <c r="U172" s="164"/>
       <c r="V172" s="19"/>
     </row>
     <row r="173" spans="1:22" x14ac:dyDescent="0.25">
@@ -18091,22 +18112,22 @@
       <c r="C173" s="77"/>
       <c r="D173" s="76"/>
       <c r="E173" s="76"/>
-      <c r="F173" s="162"/>
-      <c r="G173" s="162"/>
-      <c r="H173" s="162"/>
-      <c r="I173" s="162"/>
-      <c r="J173" s="162"/>
-      <c r="K173" s="162"/>
-      <c r="L173" s="162"/>
-      <c r="M173" s="162"/>
-      <c r="N173" s="162"/>
-      <c r="O173" s="162"/>
-      <c r="P173" s="162"/>
-      <c r="Q173" s="162"/>
-      <c r="R173" s="162"/>
-      <c r="S173" s="162"/>
-      <c r="T173" s="162"/>
-      <c r="U173" s="162"/>
+      <c r="F173" s="164"/>
+      <c r="G173" s="164"/>
+      <c r="H173" s="164"/>
+      <c r="I173" s="164"/>
+      <c r="J173" s="164"/>
+      <c r="K173" s="164"/>
+      <c r="L173" s="164"/>
+      <c r="M173" s="164"/>
+      <c r="N173" s="164"/>
+      <c r="O173" s="164"/>
+      <c r="P173" s="164"/>
+      <c r="Q173" s="164"/>
+      <c r="R173" s="164"/>
+      <c r="S173" s="164"/>
+      <c r="T173" s="164"/>
+      <c r="U173" s="164"/>
       <c r="V173" s="19"/>
     </row>
     <row r="174" spans="1:22" x14ac:dyDescent="0.25">
@@ -18115,22 +18136,22 @@
       <c r="C174" s="77"/>
       <c r="D174" s="76"/>
       <c r="E174" s="76"/>
-      <c r="F174" s="162"/>
-      <c r="G174" s="162"/>
-      <c r="H174" s="162"/>
-      <c r="I174" s="162"/>
-      <c r="J174" s="162"/>
-      <c r="K174" s="162"/>
-      <c r="L174" s="162"/>
-      <c r="M174" s="162"/>
-      <c r="N174" s="162"/>
-      <c r="O174" s="162"/>
-      <c r="P174" s="162"/>
-      <c r="Q174" s="162"/>
-      <c r="R174" s="162"/>
-      <c r="S174" s="162"/>
-      <c r="T174" s="162"/>
-      <c r="U174" s="162"/>
+      <c r="F174" s="164"/>
+      <c r="G174" s="164"/>
+      <c r="H174" s="164"/>
+      <c r="I174" s="164"/>
+      <c r="J174" s="164"/>
+      <c r="K174" s="164"/>
+      <c r="L174" s="164"/>
+      <c r="M174" s="164"/>
+      <c r="N174" s="164"/>
+      <c r="O174" s="164"/>
+      <c r="P174" s="164"/>
+      <c r="Q174" s="164"/>
+      <c r="R174" s="164"/>
+      <c r="S174" s="164"/>
+      <c r="T174" s="164"/>
+      <c r="U174" s="164"/>
       <c r="V174" s="19"/>
     </row>
     <row r="175" spans="1:22" x14ac:dyDescent="0.25">
@@ -18139,22 +18160,22 @@
       <c r="C175" s="77"/>
       <c r="D175" s="76"/>
       <c r="E175" s="76"/>
-      <c r="F175" s="162"/>
-      <c r="G175" s="162"/>
-      <c r="H175" s="162"/>
-      <c r="I175" s="162"/>
-      <c r="J175" s="162"/>
-      <c r="K175" s="162"/>
-      <c r="L175" s="162"/>
-      <c r="M175" s="162"/>
-      <c r="N175" s="162"/>
-      <c r="O175" s="162"/>
-      <c r="P175" s="162"/>
-      <c r="Q175" s="162"/>
-      <c r="R175" s="162"/>
-      <c r="S175" s="162"/>
-      <c r="T175" s="162"/>
-      <c r="U175" s="162"/>
+      <c r="F175" s="164"/>
+      <c r="G175" s="164"/>
+      <c r="H175" s="164"/>
+      <c r="I175" s="164"/>
+      <c r="J175" s="164"/>
+      <c r="K175" s="164"/>
+      <c r="L175" s="164"/>
+      <c r="M175" s="164"/>
+      <c r="N175" s="164"/>
+      <c r="O175" s="164"/>
+      <c r="P175" s="164"/>
+      <c r="Q175" s="164"/>
+      <c r="R175" s="164"/>
+      <c r="S175" s="164"/>
+      <c r="T175" s="164"/>
+      <c r="U175" s="164"/>
       <c r="V175" s="19"/>
     </row>
     <row r="176" spans="1:22" x14ac:dyDescent="0.25">
@@ -18163,22 +18184,22 @@
       <c r="C176" s="77"/>
       <c r="D176" s="76"/>
       <c r="E176" s="76"/>
-      <c r="F176" s="162"/>
-      <c r="G176" s="162"/>
-      <c r="H176" s="162"/>
-      <c r="I176" s="162"/>
-      <c r="J176" s="162"/>
-      <c r="K176" s="162"/>
-      <c r="L176" s="162"/>
-      <c r="M176" s="162"/>
-      <c r="N176" s="162"/>
-      <c r="O176" s="162"/>
-      <c r="P176" s="162"/>
-      <c r="Q176" s="162"/>
-      <c r="R176" s="162"/>
-      <c r="S176" s="162"/>
-      <c r="T176" s="162"/>
-      <c r="U176" s="162"/>
+      <c r="F176" s="164"/>
+      <c r="G176" s="164"/>
+      <c r="H176" s="164"/>
+      <c r="I176" s="164"/>
+      <c r="J176" s="164"/>
+      <c r="K176" s="164"/>
+      <c r="L176" s="164"/>
+      <c r="M176" s="164"/>
+      <c r="N176" s="164"/>
+      <c r="O176" s="164"/>
+      <c r="P176" s="164"/>
+      <c r="Q176" s="164"/>
+      <c r="R176" s="164"/>
+      <c r="S176" s="164"/>
+      <c r="T176" s="164"/>
+      <c r="U176" s="164"/>
       <c r="V176" s="19"/>
     </row>
     <row r="177" spans="1:22" x14ac:dyDescent="0.25">
@@ -18187,22 +18208,22 @@
       <c r="C177" s="77"/>
       <c r="D177" s="76"/>
       <c r="E177" s="76"/>
-      <c r="F177" s="162"/>
-      <c r="G177" s="162"/>
-      <c r="H177" s="162"/>
-      <c r="I177" s="162"/>
-      <c r="J177" s="162"/>
-      <c r="K177" s="162"/>
-      <c r="L177" s="162"/>
-      <c r="M177" s="162"/>
-      <c r="N177" s="162"/>
-      <c r="O177" s="162"/>
-      <c r="P177" s="162"/>
-      <c r="Q177" s="162"/>
-      <c r="R177" s="162"/>
-      <c r="S177" s="162"/>
-      <c r="T177" s="162"/>
-      <c r="U177" s="162"/>
+      <c r="F177" s="164"/>
+      <c r="G177" s="164"/>
+      <c r="H177" s="164"/>
+      <c r="I177" s="164"/>
+      <c r="J177" s="164"/>
+      <c r="K177" s="164"/>
+      <c r="L177" s="164"/>
+      <c r="M177" s="164"/>
+      <c r="N177" s="164"/>
+      <c r="O177" s="164"/>
+      <c r="P177" s="164"/>
+      <c r="Q177" s="164"/>
+      <c r="R177" s="164"/>
+      <c r="S177" s="164"/>
+      <c r="T177" s="164"/>
+      <c r="U177" s="164"/>
       <c r="V177" s="19"/>
     </row>
     <row r="178" spans="1:22" x14ac:dyDescent="0.25">
@@ -18211,22 +18232,22 @@
       <c r="C178" s="77"/>
       <c r="D178" s="76"/>
       <c r="E178" s="76"/>
-      <c r="F178" s="162"/>
-      <c r="G178" s="162"/>
-      <c r="H178" s="162"/>
-      <c r="I178" s="162"/>
-      <c r="J178" s="162"/>
-      <c r="K178" s="162"/>
-      <c r="L178" s="162"/>
-      <c r="M178" s="162"/>
-      <c r="N178" s="162"/>
-      <c r="O178" s="162"/>
-      <c r="P178" s="162"/>
-      <c r="Q178" s="162"/>
-      <c r="R178" s="162"/>
-      <c r="S178" s="162"/>
-      <c r="T178" s="162"/>
-      <c r="U178" s="162"/>
+      <c r="F178" s="164"/>
+      <c r="G178" s="164"/>
+      <c r="H178" s="164"/>
+      <c r="I178" s="164"/>
+      <c r="J178" s="164"/>
+      <c r="K178" s="164"/>
+      <c r="L178" s="164"/>
+      <c r="M178" s="164"/>
+      <c r="N178" s="164"/>
+      <c r="O178" s="164"/>
+      <c r="P178" s="164"/>
+      <c r="Q178" s="164"/>
+      <c r="R178" s="164"/>
+      <c r="S178" s="164"/>
+      <c r="T178" s="164"/>
+      <c r="U178" s="164"/>
       <c r="V178" s="19"/>
     </row>
     <row r="179" spans="1:22" x14ac:dyDescent="0.25">
@@ -18235,22 +18256,22 @@
       <c r="C179" s="77"/>
       <c r="D179" s="76"/>
       <c r="E179" s="76"/>
-      <c r="F179" s="162"/>
-      <c r="G179" s="162"/>
-      <c r="H179" s="162"/>
-      <c r="I179" s="162"/>
-      <c r="J179" s="162"/>
-      <c r="K179" s="162"/>
-      <c r="L179" s="162"/>
-      <c r="M179" s="162"/>
-      <c r="N179" s="162"/>
-      <c r="O179" s="162"/>
-      <c r="P179" s="162"/>
-      <c r="Q179" s="162"/>
-      <c r="R179" s="162"/>
-      <c r="S179" s="162"/>
-      <c r="T179" s="162"/>
-      <c r="U179" s="162"/>
+      <c r="F179" s="164"/>
+      <c r="G179" s="164"/>
+      <c r="H179" s="164"/>
+      <c r="I179" s="164"/>
+      <c r="J179" s="164"/>
+      <c r="K179" s="164"/>
+      <c r="L179" s="164"/>
+      <c r="M179" s="164"/>
+      <c r="N179" s="164"/>
+      <c r="O179" s="164"/>
+      <c r="P179" s="164"/>
+      <c r="Q179" s="164"/>
+      <c r="R179" s="164"/>
+      <c r="S179" s="164"/>
+      <c r="T179" s="164"/>
+      <c r="U179" s="164"/>
       <c r="V179" s="19"/>
     </row>
     <row r="180" spans="1:22" x14ac:dyDescent="0.25">
@@ -18259,22 +18280,22 @@
       <c r="C180" s="77"/>
       <c r="D180" s="76"/>
       <c r="E180" s="76"/>
-      <c r="F180" s="162"/>
-      <c r="G180" s="162"/>
-      <c r="H180" s="162"/>
-      <c r="I180" s="162"/>
-      <c r="J180" s="162"/>
-      <c r="K180" s="162"/>
-      <c r="L180" s="162"/>
-      <c r="M180" s="162"/>
-      <c r="N180" s="162"/>
-      <c r="O180" s="162"/>
-      <c r="P180" s="162"/>
-      <c r="Q180" s="162"/>
-      <c r="R180" s="162"/>
-      <c r="S180" s="162"/>
-      <c r="T180" s="162"/>
-      <c r="U180" s="162"/>
+      <c r="F180" s="164"/>
+      <c r="G180" s="164"/>
+      <c r="H180" s="164"/>
+      <c r="I180" s="164"/>
+      <c r="J180" s="164"/>
+      <c r="K180" s="164"/>
+      <c r="L180" s="164"/>
+      <c r="M180" s="164"/>
+      <c r="N180" s="164"/>
+      <c r="O180" s="164"/>
+      <c r="P180" s="164"/>
+      <c r="Q180" s="164"/>
+      <c r="R180" s="164"/>
+      <c r="S180" s="164"/>
+      <c r="T180" s="164"/>
+      <c r="U180" s="164"/>
       <c r="V180" s="19"/>
     </row>
     <row r="181" spans="1:22" x14ac:dyDescent="0.25">
@@ -18283,22 +18304,22 @@
       <c r="C181" s="77"/>
       <c r="D181" s="76"/>
       <c r="E181" s="76"/>
-      <c r="F181" s="162"/>
-      <c r="G181" s="162"/>
-      <c r="H181" s="162"/>
-      <c r="I181" s="162"/>
-      <c r="J181" s="162"/>
-      <c r="K181" s="162"/>
-      <c r="L181" s="162"/>
-      <c r="M181" s="162"/>
-      <c r="N181" s="162"/>
-      <c r="O181" s="162"/>
-      <c r="P181" s="162"/>
-      <c r="Q181" s="162"/>
-      <c r="R181" s="162"/>
-      <c r="S181" s="162"/>
-      <c r="T181" s="162"/>
-      <c r="U181" s="162"/>
+      <c r="F181" s="164"/>
+      <c r="G181" s="164"/>
+      <c r="H181" s="164"/>
+      <c r="I181" s="164"/>
+      <c r="J181" s="164"/>
+      <c r="K181" s="164"/>
+      <c r="L181" s="164"/>
+      <c r="M181" s="164"/>
+      <c r="N181" s="164"/>
+      <c r="O181" s="164"/>
+      <c r="P181" s="164"/>
+      <c r="Q181" s="164"/>
+      <c r="R181" s="164"/>
+      <c r="S181" s="164"/>
+      <c r="T181" s="164"/>
+      <c r="U181" s="164"/>
       <c r="V181" s="19"/>
     </row>
     <row r="182" spans="1:22" x14ac:dyDescent="0.25">
@@ -18307,22 +18328,22 @@
       <c r="C182" s="77"/>
       <c r="D182" s="76"/>
       <c r="E182" s="76"/>
-      <c r="F182" s="162"/>
-      <c r="G182" s="162"/>
-      <c r="H182" s="162"/>
-      <c r="I182" s="162"/>
-      <c r="J182" s="162"/>
-      <c r="K182" s="162"/>
-      <c r="L182" s="162"/>
-      <c r="M182" s="162"/>
-      <c r="N182" s="162"/>
-      <c r="O182" s="162"/>
-      <c r="P182" s="162"/>
-      <c r="Q182" s="162"/>
-      <c r="R182" s="162"/>
-      <c r="S182" s="162"/>
-      <c r="T182" s="162"/>
-      <c r="U182" s="162"/>
+      <c r="F182" s="164"/>
+      <c r="G182" s="164"/>
+      <c r="H182" s="164"/>
+      <c r="I182" s="164"/>
+      <c r="J182" s="164"/>
+      <c r="K182" s="164"/>
+      <c r="L182" s="164"/>
+      <c r="M182" s="164"/>
+      <c r="N182" s="164"/>
+      <c r="O182" s="164"/>
+      <c r="P182" s="164"/>
+      <c r="Q182" s="164"/>
+      <c r="R182" s="164"/>
+      <c r="S182" s="164"/>
+      <c r="T182" s="164"/>
+      <c r="U182" s="164"/>
       <c r="V182" s="19"/>
     </row>
     <row r="183" spans="1:22" x14ac:dyDescent="0.25">
@@ -18331,22 +18352,22 @@
       <c r="C183" s="77"/>
       <c r="D183" s="76"/>
       <c r="E183" s="76"/>
-      <c r="F183" s="162"/>
-      <c r="G183" s="162"/>
-      <c r="H183" s="162"/>
-      <c r="I183" s="162"/>
-      <c r="J183" s="162"/>
-      <c r="K183" s="162"/>
-      <c r="L183" s="162"/>
-      <c r="M183" s="162"/>
-      <c r="N183" s="162"/>
-      <c r="O183" s="162"/>
-      <c r="P183" s="162"/>
-      <c r="Q183" s="162"/>
-      <c r="R183" s="162"/>
-      <c r="S183" s="162"/>
-      <c r="T183" s="162"/>
-      <c r="U183" s="162"/>
+      <c r="F183" s="164"/>
+      <c r="G183" s="164"/>
+      <c r="H183" s="164"/>
+      <c r="I183" s="164"/>
+      <c r="J183" s="164"/>
+      <c r="K183" s="164"/>
+      <c r="L183" s="164"/>
+      <c r="M183" s="164"/>
+      <c r="N183" s="164"/>
+      <c r="O183" s="164"/>
+      <c r="P183" s="164"/>
+      <c r="Q183" s="164"/>
+      <c r="R183" s="164"/>
+      <c r="S183" s="164"/>
+      <c r="T183" s="164"/>
+      <c r="U183" s="164"/>
       <c r="V183" s="19"/>
     </row>
     <row r="184" spans="1:22" x14ac:dyDescent="0.25">
@@ -18355,22 +18376,22 @@
       <c r="C184" s="77"/>
       <c r="D184" s="76"/>
       <c r="E184" s="76"/>
-      <c r="F184" s="162"/>
-      <c r="G184" s="162"/>
-      <c r="H184" s="162"/>
-      <c r="I184" s="162"/>
-      <c r="J184" s="162"/>
-      <c r="K184" s="162"/>
-      <c r="L184" s="162"/>
-      <c r="M184" s="162"/>
-      <c r="N184" s="162"/>
-      <c r="O184" s="162"/>
-      <c r="P184" s="162"/>
-      <c r="Q184" s="162"/>
-      <c r="R184" s="162"/>
-      <c r="S184" s="162"/>
-      <c r="T184" s="162"/>
-      <c r="U184" s="162"/>
+      <c r="F184" s="164"/>
+      <c r="G184" s="164"/>
+      <c r="H184" s="164"/>
+      <c r="I184" s="164"/>
+      <c r="J184" s="164"/>
+      <c r="K184" s="164"/>
+      <c r="L184" s="164"/>
+      <c r="M184" s="164"/>
+      <c r="N184" s="164"/>
+      <c r="O184" s="164"/>
+      <c r="P184" s="164"/>
+      <c r="Q184" s="164"/>
+      <c r="R184" s="164"/>
+      <c r="S184" s="164"/>
+      <c r="T184" s="164"/>
+      <c r="U184" s="164"/>
       <c r="V184" s="19"/>
     </row>
     <row r="185" spans="1:22" x14ac:dyDescent="0.25">
@@ -18379,22 +18400,22 @@
       <c r="C185" s="77"/>
       <c r="D185" s="76"/>
       <c r="E185" s="76"/>
-      <c r="F185" s="162"/>
-      <c r="G185" s="162"/>
-      <c r="H185" s="162"/>
-      <c r="I185" s="162"/>
-      <c r="J185" s="162"/>
-      <c r="K185" s="162"/>
-      <c r="L185" s="162"/>
-      <c r="M185" s="162"/>
-      <c r="N185" s="162"/>
-      <c r="O185" s="162"/>
-      <c r="P185" s="162"/>
-      <c r="Q185" s="162"/>
-      <c r="R185" s="162"/>
-      <c r="S185" s="162"/>
-      <c r="T185" s="162"/>
-      <c r="U185" s="162"/>
+      <c r="F185" s="164"/>
+      <c r="G185" s="164"/>
+      <c r="H185" s="164"/>
+      <c r="I185" s="164"/>
+      <c r="J185" s="164"/>
+      <c r="K185" s="164"/>
+      <c r="L185" s="164"/>
+      <c r="M185" s="164"/>
+      <c r="N185" s="164"/>
+      <c r="O185" s="164"/>
+      <c r="P185" s="164"/>
+      <c r="Q185" s="164"/>
+      <c r="R185" s="164"/>
+      <c r="S185" s="164"/>
+      <c r="T185" s="164"/>
+      <c r="U185" s="164"/>
       <c r="V185" s="19"/>
     </row>
     <row r="186" spans="1:22" x14ac:dyDescent="0.25">
@@ -18403,22 +18424,22 @@
       <c r="C186" s="77"/>
       <c r="D186" s="76"/>
       <c r="E186" s="76"/>
-      <c r="F186" s="162"/>
-      <c r="G186" s="162"/>
-      <c r="H186" s="162"/>
-      <c r="I186" s="162"/>
-      <c r="J186" s="162"/>
-      <c r="K186" s="162"/>
-      <c r="L186" s="162"/>
-      <c r="M186" s="162"/>
-      <c r="N186" s="162"/>
-      <c r="O186" s="162"/>
-      <c r="P186" s="162"/>
-      <c r="Q186" s="162"/>
-      <c r="R186" s="162"/>
-      <c r="S186" s="162"/>
-      <c r="T186" s="162"/>
-      <c r="U186" s="162"/>
+      <c r="F186" s="164"/>
+      <c r="G186" s="164"/>
+      <c r="H186" s="164"/>
+      <c r="I186" s="164"/>
+      <c r="J186" s="164"/>
+      <c r="K186" s="164"/>
+      <c r="L186" s="164"/>
+      <c r="M186" s="164"/>
+      <c r="N186" s="164"/>
+      <c r="O186" s="164"/>
+      <c r="P186" s="164"/>
+      <c r="Q186" s="164"/>
+      <c r="R186" s="164"/>
+      <c r="S186" s="164"/>
+      <c r="T186" s="164"/>
+      <c r="U186" s="164"/>
       <c r="V186" s="19"/>
     </row>
     <row r="187" spans="1:22" x14ac:dyDescent="0.25">
@@ -18427,22 +18448,22 @@
       <c r="C187" s="77"/>
       <c r="D187" s="76"/>
       <c r="E187" s="76"/>
-      <c r="F187" s="162"/>
-      <c r="G187" s="162"/>
-      <c r="H187" s="162"/>
-      <c r="I187" s="162"/>
-      <c r="J187" s="162"/>
-      <c r="K187" s="162"/>
-      <c r="L187" s="162"/>
-      <c r="M187" s="162"/>
-      <c r="N187" s="162"/>
-      <c r="O187" s="162"/>
-      <c r="P187" s="162"/>
-      <c r="Q187" s="162"/>
-      <c r="R187" s="162"/>
-      <c r="S187" s="162"/>
-      <c r="T187" s="162"/>
-      <c r="U187" s="162"/>
+      <c r="F187" s="164"/>
+      <c r="G187" s="164"/>
+      <c r="H187" s="164"/>
+      <c r="I187" s="164"/>
+      <c r="J187" s="164"/>
+      <c r="K187" s="164"/>
+      <c r="L187" s="164"/>
+      <c r="M187" s="164"/>
+      <c r="N187" s="164"/>
+      <c r="O187" s="164"/>
+      <c r="P187" s="164"/>
+      <c r="Q187" s="164"/>
+      <c r="R187" s="164"/>
+      <c r="S187" s="164"/>
+      <c r="T187" s="164"/>
+      <c r="U187" s="164"/>
       <c r="V187" s="19"/>
     </row>
     <row r="188" spans="1:22" x14ac:dyDescent="0.25">
@@ -18451,22 +18472,22 @@
       <c r="C188" s="77"/>
       <c r="D188" s="76"/>
       <c r="E188" s="76"/>
-      <c r="F188" s="162"/>
-      <c r="G188" s="162"/>
-      <c r="H188" s="162"/>
-      <c r="I188" s="162"/>
-      <c r="J188" s="162"/>
-      <c r="K188" s="162"/>
-      <c r="L188" s="162"/>
-      <c r="M188" s="162"/>
-      <c r="N188" s="162"/>
-      <c r="O188" s="162"/>
-      <c r="P188" s="162"/>
-      <c r="Q188" s="162"/>
-      <c r="R188" s="162"/>
-      <c r="S188" s="162"/>
-      <c r="T188" s="162"/>
-      <c r="U188" s="162"/>
+      <c r="F188" s="164"/>
+      <c r="G188" s="164"/>
+      <c r="H188" s="164"/>
+      <c r="I188" s="164"/>
+      <c r="J188" s="164"/>
+      <c r="K188" s="164"/>
+      <c r="L188" s="164"/>
+      <c r="M188" s="164"/>
+      <c r="N188" s="164"/>
+      <c r="O188" s="164"/>
+      <c r="P188" s="164"/>
+      <c r="Q188" s="164"/>
+      <c r="R188" s="164"/>
+      <c r="S188" s="164"/>
+      <c r="T188" s="164"/>
+      <c r="U188" s="164"/>
       <c r="V188" s="19"/>
     </row>
     <row r="189" spans="1:22" x14ac:dyDescent="0.25">
@@ -18475,22 +18496,22 @@
       <c r="C189" s="77"/>
       <c r="D189" s="76"/>
       <c r="E189" s="76"/>
-      <c r="F189" s="162"/>
-      <c r="G189" s="162"/>
-      <c r="H189" s="162"/>
-      <c r="I189" s="162"/>
-      <c r="J189" s="162"/>
-      <c r="K189" s="162"/>
-      <c r="L189" s="162"/>
-      <c r="M189" s="162"/>
-      <c r="N189" s="162"/>
-      <c r="O189" s="162"/>
-      <c r="P189" s="162"/>
-      <c r="Q189" s="162"/>
-      <c r="R189" s="162"/>
-      <c r="S189" s="162"/>
-      <c r="T189" s="162"/>
-      <c r="U189" s="162"/>
+      <c r="F189" s="164"/>
+      <c r="G189" s="164"/>
+      <c r="H189" s="164"/>
+      <c r="I189" s="164"/>
+      <c r="J189" s="164"/>
+      <c r="K189" s="164"/>
+      <c r="L189" s="164"/>
+      <c r="M189" s="164"/>
+      <c r="N189" s="164"/>
+      <c r="O189" s="164"/>
+      <c r="P189" s="164"/>
+      <c r="Q189" s="164"/>
+      <c r="R189" s="164"/>
+      <c r="S189" s="164"/>
+      <c r="T189" s="164"/>
+      <c r="U189" s="164"/>
       <c r="V189" s="19"/>
     </row>
     <row r="190" spans="1:22" x14ac:dyDescent="0.25">
@@ -18499,22 +18520,22 @@
       <c r="C190" s="77"/>
       <c r="D190" s="76"/>
       <c r="E190" s="76"/>
-      <c r="F190" s="162"/>
-      <c r="G190" s="162"/>
-      <c r="H190" s="162"/>
-      <c r="I190" s="162"/>
-      <c r="J190" s="162"/>
-      <c r="K190" s="162"/>
-      <c r="L190" s="162"/>
-      <c r="M190" s="162"/>
-      <c r="N190" s="162"/>
-      <c r="O190" s="162"/>
-      <c r="P190" s="162"/>
-      <c r="Q190" s="162"/>
-      <c r="R190" s="162"/>
-      <c r="S190" s="162"/>
-      <c r="T190" s="162"/>
-      <c r="U190" s="162"/>
+      <c r="F190" s="164"/>
+      <c r="G190" s="164"/>
+      <c r="H190" s="164"/>
+      <c r="I190" s="164"/>
+      <c r="J190" s="164"/>
+      <c r="K190" s="164"/>
+      <c r="L190" s="164"/>
+      <c r="M190" s="164"/>
+      <c r="N190" s="164"/>
+      <c r="O190" s="164"/>
+      <c r="P190" s="164"/>
+      <c r="Q190" s="164"/>
+      <c r="R190" s="164"/>
+      <c r="S190" s="164"/>
+      <c r="T190" s="164"/>
+      <c r="U190" s="164"/>
       <c r="V190" s="19"/>
     </row>
     <row r="191" spans="1:22" x14ac:dyDescent="0.25">
@@ -18523,22 +18544,22 @@
       <c r="C191" s="77"/>
       <c r="D191" s="76"/>
       <c r="E191" s="76"/>
-      <c r="F191" s="162"/>
-      <c r="G191" s="162"/>
-      <c r="H191" s="162"/>
-      <c r="I191" s="162"/>
-      <c r="J191" s="162"/>
-      <c r="K191" s="162"/>
-      <c r="L191" s="162"/>
-      <c r="M191" s="162"/>
-      <c r="N191" s="162"/>
-      <c r="O191" s="162"/>
-      <c r="P191" s="162"/>
-      <c r="Q191" s="162"/>
-      <c r="R191" s="162"/>
-      <c r="S191" s="162"/>
-      <c r="T191" s="162"/>
-      <c r="U191" s="162"/>
+      <c r="F191" s="164"/>
+      <c r="G191" s="164"/>
+      <c r="H191" s="164"/>
+      <c r="I191" s="164"/>
+      <c r="J191" s="164"/>
+      <c r="K191" s="164"/>
+      <c r="L191" s="164"/>
+      <c r="M191" s="164"/>
+      <c r="N191" s="164"/>
+      <c r="O191" s="164"/>
+      <c r="P191" s="164"/>
+      <c r="Q191" s="164"/>
+      <c r="R191" s="164"/>
+      <c r="S191" s="164"/>
+      <c r="T191" s="164"/>
+      <c r="U191" s="164"/>
       <c r="V191" s="19"/>
     </row>
     <row r="192" spans="1:22" x14ac:dyDescent="0.25">
@@ -18547,22 +18568,22 @@
       <c r="C192" s="77"/>
       <c r="D192" s="76"/>
       <c r="E192" s="76"/>
-      <c r="F192" s="162"/>
-      <c r="G192" s="162"/>
-      <c r="H192" s="162"/>
-      <c r="I192" s="162"/>
-      <c r="J192" s="162"/>
-      <c r="K192" s="162"/>
-      <c r="L192" s="162"/>
-      <c r="M192" s="162"/>
-      <c r="N192" s="162"/>
-      <c r="O192" s="162"/>
-      <c r="P192" s="162"/>
-      <c r="Q192" s="162"/>
-      <c r="R192" s="162"/>
-      <c r="S192" s="162"/>
-      <c r="T192" s="162"/>
-      <c r="U192" s="162"/>
+      <c r="F192" s="164"/>
+      <c r="G192" s="164"/>
+      <c r="H192" s="164"/>
+      <c r="I192" s="164"/>
+      <c r="J192" s="164"/>
+      <c r="K192" s="164"/>
+      <c r="L192" s="164"/>
+      <c r="M192" s="164"/>
+      <c r="N192" s="164"/>
+      <c r="O192" s="164"/>
+      <c r="P192" s="164"/>
+      <c r="Q192" s="164"/>
+      <c r="R192" s="164"/>
+      <c r="S192" s="164"/>
+      <c r="T192" s="164"/>
+      <c r="U192" s="164"/>
       <c r="V192" s="19"/>
     </row>
     <row r="193" spans="1:22" x14ac:dyDescent="0.25">
@@ -18571,22 +18592,22 @@
       <c r="C193" s="77"/>
       <c r="D193" s="76"/>
       <c r="E193" s="76"/>
-      <c r="F193" s="162"/>
-      <c r="G193" s="162"/>
-      <c r="H193" s="162"/>
-      <c r="I193" s="162"/>
-      <c r="J193" s="162"/>
-      <c r="K193" s="162"/>
-      <c r="L193" s="162"/>
-      <c r="M193" s="162"/>
-      <c r="N193" s="162"/>
-      <c r="O193" s="162"/>
-      <c r="P193" s="162"/>
-      <c r="Q193" s="162"/>
-      <c r="R193" s="162"/>
-      <c r="S193" s="162"/>
-      <c r="T193" s="162"/>
-      <c r="U193" s="162"/>
+      <c r="F193" s="164"/>
+      <c r="G193" s="164"/>
+      <c r="H193" s="164"/>
+      <c r="I193" s="164"/>
+      <c r="J193" s="164"/>
+      <c r="K193" s="164"/>
+      <c r="L193" s="164"/>
+      <c r="M193" s="164"/>
+      <c r="N193" s="164"/>
+      <c r="O193" s="164"/>
+      <c r="P193" s="164"/>
+      <c r="Q193" s="164"/>
+      <c r="R193" s="164"/>
+      <c r="S193" s="164"/>
+      <c r="T193" s="164"/>
+      <c r="U193" s="164"/>
       <c r="V193" s="19"/>
     </row>
     <row r="194" spans="1:22" x14ac:dyDescent="0.25">
@@ -18595,22 +18616,22 @@
       <c r="C194" s="77"/>
       <c r="D194" s="76"/>
       <c r="E194" s="76"/>
-      <c r="F194" s="162"/>
-      <c r="G194" s="162"/>
-      <c r="H194" s="162"/>
-      <c r="I194" s="162"/>
-      <c r="J194" s="162"/>
-      <c r="K194" s="162"/>
-      <c r="L194" s="162"/>
-      <c r="M194" s="162"/>
-      <c r="N194" s="162"/>
-      <c r="O194" s="162"/>
-      <c r="P194" s="162"/>
-      <c r="Q194" s="162"/>
-      <c r="R194" s="162"/>
-      <c r="S194" s="162"/>
-      <c r="T194" s="162"/>
-      <c r="U194" s="162"/>
+      <c r="F194" s="164"/>
+      <c r="G194" s="164"/>
+      <c r="H194" s="164"/>
+      <c r="I194" s="164"/>
+      <c r="J194" s="164"/>
+      <c r="K194" s="164"/>
+      <c r="L194" s="164"/>
+      <c r="M194" s="164"/>
+      <c r="N194" s="164"/>
+      <c r="O194" s="164"/>
+      <c r="P194" s="164"/>
+      <c r="Q194" s="164"/>
+      <c r="R194" s="164"/>
+      <c r="S194" s="164"/>
+      <c r="T194" s="164"/>
+      <c r="U194" s="164"/>
       <c r="V194" s="19"/>
     </row>
     <row r="195" spans="1:22" x14ac:dyDescent="0.25">
@@ -18619,22 +18640,22 @@
       <c r="C195" s="77"/>
       <c r="D195" s="76"/>
       <c r="E195" s="76"/>
-      <c r="F195" s="162"/>
-      <c r="G195" s="162"/>
-      <c r="H195" s="162"/>
-      <c r="I195" s="162"/>
-      <c r="J195" s="162"/>
-      <c r="K195" s="162"/>
-      <c r="L195" s="162"/>
-      <c r="M195" s="162"/>
-      <c r="N195" s="162"/>
-      <c r="O195" s="162"/>
-      <c r="P195" s="162"/>
-      <c r="Q195" s="162"/>
-      <c r="R195" s="162"/>
-      <c r="S195" s="162"/>
-      <c r="T195" s="162"/>
-      <c r="U195" s="162"/>
+      <c r="F195" s="164"/>
+      <c r="G195" s="164"/>
+      <c r="H195" s="164"/>
+      <c r="I195" s="164"/>
+      <c r="J195" s="164"/>
+      <c r="K195" s="164"/>
+      <c r="L195" s="164"/>
+      <c r="M195" s="164"/>
+      <c r="N195" s="164"/>
+      <c r="O195" s="164"/>
+      <c r="P195" s="164"/>
+      <c r="Q195" s="164"/>
+      <c r="R195" s="164"/>
+      <c r="S195" s="164"/>
+      <c r="T195" s="164"/>
+      <c r="U195" s="164"/>
       <c r="V195" s="19"/>
     </row>
     <row r="196" spans="1:22" x14ac:dyDescent="0.25">
@@ -18643,22 +18664,22 @@
       <c r="C196" s="77"/>
       <c r="D196" s="76"/>
       <c r="E196" s="76"/>
-      <c r="F196" s="162"/>
-      <c r="G196" s="162"/>
-      <c r="H196" s="162"/>
-      <c r="I196" s="162"/>
-      <c r="J196" s="162"/>
-      <c r="K196" s="162"/>
-      <c r="L196" s="162"/>
-      <c r="M196" s="162"/>
-      <c r="N196" s="162"/>
-      <c r="O196" s="162"/>
-      <c r="P196" s="162"/>
-      <c r="Q196" s="162"/>
-      <c r="R196" s="162"/>
-      <c r="S196" s="162"/>
-      <c r="T196" s="162"/>
-      <c r="U196" s="162"/>
+      <c r="F196" s="164"/>
+      <c r="G196" s="164"/>
+      <c r="H196" s="164"/>
+      <c r="I196" s="164"/>
+      <c r="J196" s="164"/>
+      <c r="K196" s="164"/>
+      <c r="L196" s="164"/>
+      <c r="M196" s="164"/>
+      <c r="N196" s="164"/>
+      <c r="O196" s="164"/>
+      <c r="P196" s="164"/>
+      <c r="Q196" s="164"/>
+      <c r="R196" s="164"/>
+      <c r="S196" s="164"/>
+      <c r="T196" s="164"/>
+      <c r="U196" s="164"/>
       <c r="V196" s="19"/>
     </row>
     <row r="197" spans="1:22" x14ac:dyDescent="0.25">
@@ -18667,22 +18688,22 @@
       <c r="C197" s="77"/>
       <c r="D197" s="76"/>
       <c r="E197" s="76"/>
-      <c r="F197" s="162"/>
-      <c r="G197" s="162"/>
-      <c r="H197" s="162"/>
-      <c r="I197" s="162"/>
-      <c r="J197" s="162"/>
-      <c r="K197" s="162"/>
-      <c r="L197" s="162"/>
-      <c r="M197" s="162"/>
-      <c r="N197" s="162"/>
-      <c r="O197" s="162"/>
-      <c r="P197" s="162"/>
-      <c r="Q197" s="162"/>
-      <c r="R197" s="162"/>
-      <c r="S197" s="162"/>
-      <c r="T197" s="162"/>
-      <c r="U197" s="162"/>
+      <c r="F197" s="164"/>
+      <c r="G197" s="164"/>
+      <c r="H197" s="164"/>
+      <c r="I197" s="164"/>
+      <c r="J197" s="164"/>
+      <c r="K197" s="164"/>
+      <c r="L197" s="164"/>
+      <c r="M197" s="164"/>
+      <c r="N197" s="164"/>
+      <c r="O197" s="164"/>
+      <c r="P197" s="164"/>
+      <c r="Q197" s="164"/>
+      <c r="R197" s="164"/>
+      <c r="S197" s="164"/>
+      <c r="T197" s="164"/>
+      <c r="U197" s="164"/>
       <c r="V197" s="19"/>
     </row>
     <row r="198" spans="1:22" x14ac:dyDescent="0.25">
@@ -18691,22 +18712,22 @@
       <c r="C198" s="77"/>
       <c r="D198" s="76"/>
       <c r="E198" s="76"/>
-      <c r="F198" s="162"/>
-      <c r="G198" s="162"/>
-      <c r="H198" s="162"/>
-      <c r="I198" s="162"/>
-      <c r="J198" s="162"/>
-      <c r="K198" s="162"/>
-      <c r="L198" s="162"/>
-      <c r="M198" s="162"/>
-      <c r="N198" s="162"/>
-      <c r="O198" s="162"/>
-      <c r="P198" s="162"/>
-      <c r="Q198" s="162"/>
-      <c r="R198" s="162"/>
-      <c r="S198" s="162"/>
-      <c r="T198" s="162"/>
-      <c r="U198" s="162"/>
+      <c r="F198" s="164"/>
+      <c r="G198" s="164"/>
+      <c r="H198" s="164"/>
+      <c r="I198" s="164"/>
+      <c r="J198" s="164"/>
+      <c r="K198" s="164"/>
+      <c r="L198" s="164"/>
+      <c r="M198" s="164"/>
+      <c r="N198" s="164"/>
+      <c r="O198" s="164"/>
+      <c r="P198" s="164"/>
+      <c r="Q198" s="164"/>
+      <c r="R198" s="164"/>
+      <c r="S198" s="164"/>
+      <c r="T198" s="164"/>
+      <c r="U198" s="164"/>
       <c r="V198" s="19"/>
     </row>
     <row r="199" spans="1:22" x14ac:dyDescent="0.25">
@@ -18715,22 +18736,22 @@
       <c r="C199" s="77"/>
       <c r="D199" s="76"/>
       <c r="E199" s="76"/>
-      <c r="F199" s="162"/>
-      <c r="G199" s="162"/>
-      <c r="H199" s="162"/>
-      <c r="I199" s="162"/>
-      <c r="J199" s="162"/>
-      <c r="K199" s="162"/>
-      <c r="L199" s="162"/>
-      <c r="M199" s="162"/>
-      <c r="N199" s="162"/>
-      <c r="O199" s="162"/>
-      <c r="P199" s="162"/>
-      <c r="Q199" s="162"/>
-      <c r="R199" s="162"/>
-      <c r="S199" s="162"/>
-      <c r="T199" s="162"/>
-      <c r="U199" s="162"/>
+      <c r="F199" s="164"/>
+      <c r="G199" s="164"/>
+      <c r="H199" s="164"/>
+      <c r="I199" s="164"/>
+      <c r="J199" s="164"/>
+      <c r="K199" s="164"/>
+      <c r="L199" s="164"/>
+      <c r="M199" s="164"/>
+      <c r="N199" s="164"/>
+      <c r="O199" s="164"/>
+      <c r="P199" s="164"/>
+      <c r="Q199" s="164"/>
+      <c r="R199" s="164"/>
+      <c r="S199" s="164"/>
+      <c r="T199" s="164"/>
+      <c r="U199" s="164"/>
       <c r="V199" s="19"/>
     </row>
     <row r="200" spans="1:22" x14ac:dyDescent="0.25">
@@ -18739,22 +18760,22 @@
       <c r="C200" s="77"/>
       <c r="D200" s="76"/>
       <c r="E200" s="76"/>
-      <c r="F200" s="162"/>
-      <c r="G200" s="162"/>
-      <c r="H200" s="162"/>
-      <c r="I200" s="162"/>
-      <c r="J200" s="162"/>
-      <c r="K200" s="162"/>
-      <c r="L200" s="162"/>
-      <c r="M200" s="162"/>
-      <c r="N200" s="162"/>
-      <c r="O200" s="162"/>
-      <c r="P200" s="162"/>
-      <c r="Q200" s="162"/>
-      <c r="R200" s="162"/>
-      <c r="S200" s="162"/>
-      <c r="T200" s="162"/>
-      <c r="U200" s="162"/>
+      <c r="F200" s="164"/>
+      <c r="G200" s="164"/>
+      <c r="H200" s="164"/>
+      <c r="I200" s="164"/>
+      <c r="J200" s="164"/>
+      <c r="K200" s="164"/>
+      <c r="L200" s="164"/>
+      <c r="M200" s="164"/>
+      <c r="N200" s="164"/>
+      <c r="O200" s="164"/>
+      <c r="P200" s="164"/>
+      <c r="Q200" s="164"/>
+      <c r="R200" s="164"/>
+      <c r="S200" s="164"/>
+      <c r="T200" s="164"/>
+      <c r="U200" s="164"/>
       <c r="V200" s="19"/>
     </row>
     <row r="201" spans="1:22" x14ac:dyDescent="0.25">
@@ -18763,22 +18784,22 @@
       <c r="C201" s="77"/>
       <c r="D201" s="76"/>
       <c r="E201" s="76"/>
-      <c r="F201" s="162"/>
-      <c r="G201" s="162"/>
-      <c r="H201" s="162"/>
-      <c r="I201" s="162"/>
-      <c r="J201" s="162"/>
-      <c r="K201" s="162"/>
-      <c r="L201" s="162"/>
-      <c r="M201" s="162"/>
-      <c r="N201" s="162"/>
-      <c r="O201" s="162"/>
-      <c r="P201" s="162"/>
-      <c r="Q201" s="162"/>
-      <c r="R201" s="162"/>
-      <c r="S201" s="162"/>
-      <c r="T201" s="162"/>
-      <c r="U201" s="162"/>
+      <c r="F201" s="164"/>
+      <c r="G201" s="164"/>
+      <c r="H201" s="164"/>
+      <c r="I201" s="164"/>
+      <c r="J201" s="164"/>
+      <c r="K201" s="164"/>
+      <c r="L201" s="164"/>
+      <c r="M201" s="164"/>
+      <c r="N201" s="164"/>
+      <c r="O201" s="164"/>
+      <c r="P201" s="164"/>
+      <c r="Q201" s="164"/>
+      <c r="R201" s="164"/>
+      <c r="S201" s="164"/>
+      <c r="T201" s="164"/>
+      <c r="U201" s="164"/>
       <c r="V201" s="19"/>
     </row>
     <row r="202" spans="1:22" x14ac:dyDescent="0.25">
@@ -18787,22 +18808,22 @@
       <c r="C202" s="77"/>
       <c r="D202" s="76"/>
       <c r="E202" s="76"/>
-      <c r="F202" s="162"/>
-      <c r="G202" s="162"/>
-      <c r="H202" s="162"/>
-      <c r="I202" s="162"/>
-      <c r="J202" s="162"/>
-      <c r="K202" s="162"/>
-      <c r="L202" s="162"/>
-      <c r="M202" s="162"/>
-      <c r="N202" s="162"/>
-      <c r="O202" s="162"/>
-      <c r="P202" s="162"/>
-      <c r="Q202" s="162"/>
-      <c r="R202" s="162"/>
-      <c r="S202" s="162"/>
-      <c r="T202" s="162"/>
-      <c r="U202" s="162"/>
+      <c r="F202" s="164"/>
+      <c r="G202" s="164"/>
+      <c r="H202" s="164"/>
+      <c r="I202" s="164"/>
+      <c r="J202" s="164"/>
+      <c r="K202" s="164"/>
+      <c r="L202" s="164"/>
+      <c r="M202" s="164"/>
+      <c r="N202" s="164"/>
+      <c r="O202" s="164"/>
+      <c r="P202" s="164"/>
+      <c r="Q202" s="164"/>
+      <c r="R202" s="164"/>
+      <c r="S202" s="164"/>
+      <c r="T202" s="164"/>
+      <c r="U202" s="164"/>
       <c r="V202" s="19"/>
     </row>
     <row r="203" spans="1:22" x14ac:dyDescent="0.25">
@@ -21549,21 +21570,92 @@
     </row>
   </sheetData>
   <mergeCells count="125">
-    <mergeCell ref="F85:U85"/>
-    <mergeCell ref="F84:U84"/>
-    <mergeCell ref="F83:U83"/>
-    <mergeCell ref="F99:U99"/>
-    <mergeCell ref="F98:U98"/>
-    <mergeCell ref="F97:U97"/>
-    <mergeCell ref="F96:U96"/>
-    <mergeCell ref="F95:U95"/>
-    <mergeCell ref="F91:U91"/>
-    <mergeCell ref="F90:U90"/>
-    <mergeCell ref="F89:U89"/>
-    <mergeCell ref="F88:U88"/>
-    <mergeCell ref="F92:U92"/>
-    <mergeCell ref="F93:U93"/>
-    <mergeCell ref="F94:U94"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:U3"/>
+    <mergeCell ref="F134:U134"/>
+    <mergeCell ref="F135:U135"/>
+    <mergeCell ref="F136:U136"/>
+    <mergeCell ref="F137:U137"/>
+    <mergeCell ref="F132:U132"/>
+    <mergeCell ref="F133:U133"/>
+    <mergeCell ref="F122:U122"/>
+    <mergeCell ref="F123:U123"/>
+    <mergeCell ref="F124:U124"/>
+    <mergeCell ref="F125:U125"/>
+    <mergeCell ref="F113:U113"/>
+    <mergeCell ref="F112:U112"/>
+    <mergeCell ref="F111:U111"/>
+    <mergeCell ref="F110:U110"/>
+    <mergeCell ref="F108:U108"/>
+    <mergeCell ref="F107:U107"/>
+    <mergeCell ref="F100:U100"/>
+    <mergeCell ref="F101:U101"/>
+    <mergeCell ref="F102:U102"/>
+    <mergeCell ref="F103:U103"/>
+    <mergeCell ref="F104:U104"/>
+    <mergeCell ref="F197:U197"/>
+    <mergeCell ref="F192:U192"/>
+    <mergeCell ref="F193:U193"/>
+    <mergeCell ref="F182:U182"/>
+    <mergeCell ref="F183:U183"/>
+    <mergeCell ref="F184:U184"/>
+    <mergeCell ref="F185:U185"/>
+    <mergeCell ref="F180:U180"/>
+    <mergeCell ref="F181:U181"/>
+    <mergeCell ref="F194:U194"/>
+    <mergeCell ref="F195:U195"/>
+    <mergeCell ref="F196:U196"/>
+    <mergeCell ref="F172:U172"/>
+    <mergeCell ref="F173:U173"/>
+    <mergeCell ref="F168:U168"/>
+    <mergeCell ref="F169:U169"/>
+    <mergeCell ref="F158:U158"/>
+    <mergeCell ref="F159:U159"/>
+    <mergeCell ref="F160:U160"/>
+    <mergeCell ref="F161:U161"/>
+    <mergeCell ref="F166:U166"/>
+    <mergeCell ref="F167:U167"/>
+    <mergeCell ref="F164:U164"/>
+    <mergeCell ref="F165:U165"/>
+    <mergeCell ref="F138:U138"/>
+    <mergeCell ref="F139:U139"/>
+    <mergeCell ref="F140:U140"/>
+    <mergeCell ref="F141:U141"/>
+    <mergeCell ref="F142:U142"/>
+    <mergeCell ref="F143:U143"/>
+    <mergeCell ref="F149:U149"/>
+    <mergeCell ref="F170:U170"/>
+    <mergeCell ref="F171:U171"/>
+    <mergeCell ref="F156:U156"/>
+    <mergeCell ref="F157:U157"/>
+    <mergeCell ref="F146:U146"/>
+    <mergeCell ref="F147:U147"/>
+    <mergeCell ref="F148:U148"/>
+    <mergeCell ref="F105:U105"/>
+    <mergeCell ref="F106:U106"/>
+    <mergeCell ref="F150:U150"/>
+    <mergeCell ref="F151:U151"/>
+    <mergeCell ref="F152:U152"/>
+    <mergeCell ref="F153:U153"/>
+    <mergeCell ref="F154:U154"/>
+    <mergeCell ref="F155:U155"/>
+    <mergeCell ref="F126:U126"/>
+    <mergeCell ref="F127:U127"/>
+    <mergeCell ref="F128:U128"/>
+    <mergeCell ref="F129:U129"/>
+    <mergeCell ref="F130:U130"/>
+    <mergeCell ref="F131:U131"/>
+    <mergeCell ref="F114:U114"/>
+    <mergeCell ref="F115:U115"/>
+    <mergeCell ref="F116:U116"/>
+    <mergeCell ref="F117:U117"/>
+    <mergeCell ref="F118:U118"/>
+    <mergeCell ref="F119:U119"/>
+    <mergeCell ref="F120:U120"/>
+    <mergeCell ref="F121:U121"/>
+    <mergeCell ref="F144:U144"/>
+    <mergeCell ref="F145:U145"/>
     <mergeCell ref="A81:U81"/>
     <mergeCell ref="F109:U109"/>
     <mergeCell ref="F198:U198"/>
@@ -21588,92 +21680,21 @@
     <mergeCell ref="F163:U163"/>
     <mergeCell ref="F87:U87"/>
     <mergeCell ref="F86:U86"/>
-    <mergeCell ref="F105:U105"/>
-    <mergeCell ref="F106:U106"/>
-    <mergeCell ref="F150:U150"/>
-    <mergeCell ref="F151:U151"/>
-    <mergeCell ref="F152:U152"/>
-    <mergeCell ref="F153:U153"/>
-    <mergeCell ref="F154:U154"/>
-    <mergeCell ref="F155:U155"/>
-    <mergeCell ref="F126:U126"/>
-    <mergeCell ref="F127:U127"/>
-    <mergeCell ref="F128:U128"/>
-    <mergeCell ref="F129:U129"/>
-    <mergeCell ref="F130:U130"/>
-    <mergeCell ref="F131:U131"/>
-    <mergeCell ref="F114:U114"/>
-    <mergeCell ref="F115:U115"/>
-    <mergeCell ref="F116:U116"/>
-    <mergeCell ref="F117:U117"/>
-    <mergeCell ref="F118:U118"/>
-    <mergeCell ref="F119:U119"/>
-    <mergeCell ref="F120:U120"/>
-    <mergeCell ref="F121:U121"/>
-    <mergeCell ref="F144:U144"/>
-    <mergeCell ref="F145:U145"/>
-    <mergeCell ref="F138:U138"/>
-    <mergeCell ref="F139:U139"/>
-    <mergeCell ref="F140:U140"/>
-    <mergeCell ref="F141:U141"/>
-    <mergeCell ref="F142:U142"/>
-    <mergeCell ref="F143:U143"/>
-    <mergeCell ref="F149:U149"/>
-    <mergeCell ref="F170:U170"/>
-    <mergeCell ref="F171:U171"/>
-    <mergeCell ref="F156:U156"/>
-    <mergeCell ref="F157:U157"/>
-    <mergeCell ref="F146:U146"/>
-    <mergeCell ref="F147:U147"/>
-    <mergeCell ref="F148:U148"/>
-    <mergeCell ref="F172:U172"/>
-    <mergeCell ref="F173:U173"/>
-    <mergeCell ref="F168:U168"/>
-    <mergeCell ref="F169:U169"/>
-    <mergeCell ref="F158:U158"/>
-    <mergeCell ref="F159:U159"/>
-    <mergeCell ref="F160:U160"/>
-    <mergeCell ref="F161:U161"/>
-    <mergeCell ref="F166:U166"/>
-    <mergeCell ref="F167:U167"/>
-    <mergeCell ref="F164:U164"/>
-    <mergeCell ref="F165:U165"/>
-    <mergeCell ref="F197:U197"/>
-    <mergeCell ref="F192:U192"/>
-    <mergeCell ref="F193:U193"/>
-    <mergeCell ref="F182:U182"/>
-    <mergeCell ref="F183:U183"/>
-    <mergeCell ref="F184:U184"/>
-    <mergeCell ref="F185:U185"/>
-    <mergeCell ref="F180:U180"/>
-    <mergeCell ref="F181:U181"/>
-    <mergeCell ref="F194:U194"/>
-    <mergeCell ref="F195:U195"/>
-    <mergeCell ref="F196:U196"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:U3"/>
-    <mergeCell ref="F134:U134"/>
-    <mergeCell ref="F135:U135"/>
-    <mergeCell ref="F136:U136"/>
-    <mergeCell ref="F137:U137"/>
-    <mergeCell ref="F132:U132"/>
-    <mergeCell ref="F133:U133"/>
-    <mergeCell ref="F122:U122"/>
-    <mergeCell ref="F123:U123"/>
-    <mergeCell ref="F124:U124"/>
-    <mergeCell ref="F125:U125"/>
-    <mergeCell ref="F113:U113"/>
-    <mergeCell ref="F112:U112"/>
-    <mergeCell ref="F111:U111"/>
-    <mergeCell ref="F110:U110"/>
-    <mergeCell ref="F108:U108"/>
-    <mergeCell ref="F107:U107"/>
-    <mergeCell ref="F100:U100"/>
-    <mergeCell ref="F101:U101"/>
-    <mergeCell ref="F102:U102"/>
-    <mergeCell ref="F103:U103"/>
-    <mergeCell ref="F104:U104"/>
+    <mergeCell ref="F85:U85"/>
+    <mergeCell ref="F84:U84"/>
+    <mergeCell ref="F83:U83"/>
+    <mergeCell ref="F99:U99"/>
+    <mergeCell ref="F98:U98"/>
+    <mergeCell ref="F97:U97"/>
+    <mergeCell ref="F96:U96"/>
+    <mergeCell ref="F95:U95"/>
+    <mergeCell ref="F91:U91"/>
+    <mergeCell ref="F90:U90"/>
+    <mergeCell ref="F89:U89"/>
+    <mergeCell ref="F88:U88"/>
+    <mergeCell ref="F92:U92"/>
+    <mergeCell ref="F93:U93"/>
+    <mergeCell ref="F94:U94"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -21961,17 +21982,17 @@
       <c r="H13" s="11"/>
     </row>
     <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="123" t="s">
         <v>320</v>
       </c>
-      <c r="B14" s="104"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
+      <c r="B14" s="123"/>
+      <c r="C14" s="123"/>
+      <c r="D14" s="123"/>
+      <c r="E14" s="123"/>
+      <c r="F14" s="123"/>
+      <c r="G14" s="123"/>
+      <c r="H14" s="123"/>
+      <c r="I14" s="123"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="s">
@@ -22024,17 +22045,17 @@
       </c>
     </row>
     <row r="16" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="104" t="s">
+      <c r="A16" s="123" t="s">
         <v>322</v>
       </c>
-      <c r="B16" s="104"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="104"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="104"/>
-      <c r="I16" s="104"/>
+      <c r="B16" s="123"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="123"/>
+      <c r="F16" s="123"/>
+      <c r="G16" s="123"/>
+      <c r="H16" s="123"/>
+      <c r="I16" s="123"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
@@ -22060,17 +22081,17 @@
       <c r="I17" s="11"/>
     </row>
     <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="104" t="s">
+      <c r="A18" s="123" t="s">
         <v>370</v>
       </c>
-      <c r="B18" s="104"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="104"/>
-      <c r="I18" s="104"/>
+      <c r="B18" s="123"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="123"/>
+      <c r="F18" s="123"/>
+      <c r="G18" s="123"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="123"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
@@ -22096,17 +22117,17 @@
       <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="104" t="s">
+      <c r="A20" s="123" t="s">
         <v>371</v>
       </c>
-      <c r="B20" s="104"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="104"/>
+      <c r="B20" s="123"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="123"/>
+      <c r="I20" s="123"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
@@ -22168,17 +22189,17 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="104" t="s">
+      <c r="A22" s="123" t="s">
         <v>326</v>
       </c>
-      <c r="B22" s="104"/>
-      <c r="C22" s="104"/>
-      <c r="D22" s="104"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="104"/>
-      <c r="I22" s="104"/>
+      <c r="B22" s="123"/>
+      <c r="C22" s="123"/>
+      <c r="D22" s="123"/>
+      <c r="E22" s="123"/>
+      <c r="F22" s="123"/>
+      <c r="G22" s="123"/>
+      <c r="H22" s="123"/>
+      <c r="I22" s="123"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
@@ -22830,16 +22851,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A6:I6"/>
     <mergeCell ref="A18:I18"/>
     <mergeCell ref="A22:I22"/>
     <mergeCell ref="A10:I10"/>
@@ -22847,6 +22858,16 @@
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A26:I26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22869,60 +22890,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="131" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
     </row>
     <row r="2" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="132" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
     </row>
     <row r="3" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131" t="s">
+      <c r="A3" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="131"/>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="131"/>
+      <c r="B3" s="133"/>
+      <c r="C3" s="133"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="133"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="133"/>
+      <c r="H3" s="133"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
     </row>
     <row r="4" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="132" t="s">
+      <c r="A4" s="129" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="132"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="132"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="132"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="132"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="129"/>
     </row>
     <row r="5" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -23149,15 +23170,15 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="132" t="s">
+      <c r="A13" s="129" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="132"/>
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
+      <c r="B13" s="129"/>
+      <c r="C13" s="129"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="129"/>
     </row>
     <row r="14" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -23275,87 +23296,87 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="132" t="s">
+      <c r="A20" s="129" t="s">
         <v>99</v>
       </c>
-      <c r="B20" s="132"/>
-      <c r="C20" s="132"/>
-      <c r="D20" s="132"/>
-      <c r="E20" s="132"/>
-      <c r="F20" s="132"/>
-      <c r="G20" s="132"/>
-      <c r="H20" s="132"/>
-      <c r="I20" s="132"/>
-      <c r="J20" s="132"/>
+      <c r="B20" s="129"/>
+      <c r="C20" s="129"/>
+      <c r="D20" s="129"/>
+      <c r="E20" s="129"/>
+      <c r="F20" s="129"/>
+      <c r="G20" s="129"/>
+      <c r="H20" s="129"/>
+      <c r="I20" s="129"/>
+      <c r="J20" s="129"/>
     </row>
     <row r="21" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="133" t="s">
+      <c r="A21" s="130" t="s">
         <v>100</v>
       </c>
-      <c r="B21" s="133"/>
-      <c r="C21" s="133"/>
-      <c r="D21" s="133"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="133"/>
-      <c r="I21" s="133"/>
-      <c r="J21" s="133"/>
+      <c r="B21" s="130"/>
+      <c r="C21" s="130"/>
+      <c r="D21" s="130"/>
+      <c r="E21" s="130"/>
+      <c r="F21" s="130"/>
+      <c r="G21" s="130"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="130"/>
+      <c r="J21" s="130"/>
     </row>
     <row r="22" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="133" t="s">
+      <c r="A22" s="130" t="s">
         <v>101</v>
       </c>
-      <c r="B22" s="133"/>
-      <c r="C22" s="133"/>
-      <c r="D22" s="133"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="133"/>
-      <c r="H22" s="133"/>
-      <c r="I22" s="133"/>
-      <c r="J22" s="133"/>
+      <c r="B22" s="130"/>
+      <c r="C22" s="130"/>
+      <c r="D22" s="130"/>
+      <c r="E22" s="130"/>
+      <c r="F22" s="130"/>
+      <c r="G22" s="130"/>
+      <c r="H22" s="130"/>
+      <c r="I22" s="130"/>
+      <c r="J22" s="130"/>
     </row>
     <row r="23" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="133" t="s">
+      <c r="A23" s="130" t="s">
         <v>102</v>
       </c>
-      <c r="B23" s="133"/>
-      <c r="C23" s="133"/>
-      <c r="D23" s="133"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="133"/>
-      <c r="I23" s="133"/>
-      <c r="J23" s="133"/>
+      <c r="B23" s="130"/>
+      <c r="C23" s="130"/>
+      <c r="D23" s="130"/>
+      <c r="E23" s="130"/>
+      <c r="F23" s="130"/>
+      <c r="G23" s="130"/>
+      <c r="H23" s="130"/>
+      <c r="I23" s="130"/>
+      <c r="J23" s="130"/>
     </row>
     <row r="24" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="133" t="s">
+      <c r="A24" s="130" t="s">
         <v>103</v>
       </c>
-      <c r="B24" s="133"/>
-      <c r="C24" s="133"/>
-      <c r="D24" s="133"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="133"/>
-      <c r="I24" s="133"/>
-      <c r="J24" s="133"/>
+      <c r="B24" s="130"/>
+      <c r="C24" s="130"/>
+      <c r="D24" s="130"/>
+      <c r="E24" s="130"/>
+      <c r="F24" s="130"/>
+      <c r="G24" s="130"/>
+      <c r="H24" s="130"/>
+      <c r="I24" s="130"/>
+      <c r="J24" s="130"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A13:G13"/>
   </mergeCells>
   <conditionalFormatting sqref="F15:F18">
     <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="Agreed"/>
@@ -23434,588 +23455,588 @@
       <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="139" t="s">
+      <c r="A5" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="139"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="139"/>
-      <c r="E5" s="139"/>
-      <c r="F5" s="139"/>
+      <c r="B5" s="143"/>
+      <c r="C5" s="143"/>
+      <c r="D5" s="143"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
     </row>
     <row r="6" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="140" t="s">
+      <c r="A6" s="142" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="140"/>
-      <c r="C6" s="140"/>
-      <c r="D6" s="142" t="s">
+      <c r="B6" s="142"/>
+      <c r="C6" s="142"/>
+      <c r="D6" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="140" t="s">
+      <c r="E6" s="142" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="140"/>
+      <c r="F6" s="142"/>
     </row>
     <row r="7" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="141" t="s">
+      <c r="A7" s="139" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="141"/>
-      <c r="C7" s="141"/>
-      <c r="D7" s="143"/>
-      <c r="E7" s="141"/>
-      <c r="F7" s="141"/>
+      <c r="B7" s="139"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="141"/>
+      <c r="E7" s="139"/>
+      <c r="F7" s="139"/>
     </row>
     <row r="8" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="139" t="s">
+      <c r="A8" s="143" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="139"/>
-      <c r="C8" s="139"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="139"/>
-      <c r="F8" s="139"/>
+      <c r="B8" s="143"/>
+      <c r="C8" s="143"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143"/>
     </row>
     <row r="9" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="140" t="s">
+      <c r="A9" s="142" t="s">
         <v>108</v>
       </c>
-      <c r="B9" s="140"/>
-      <c r="C9" s="140"/>
-      <c r="D9" s="142" t="s">
+      <c r="B9" s="142"/>
+      <c r="C9" s="142"/>
+      <c r="D9" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E9" s="140" t="s">
+      <c r="E9" s="142" t="s">
         <v>109</v>
       </c>
-      <c r="F9" s="140"/>
+      <c r="F9" s="142"/>
     </row>
     <row r="10" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="141" t="s">
+      <c r="A10" s="139" t="s">
         <v>110</v>
       </c>
-      <c r="B10" s="141"/>
-      <c r="C10" s="141"/>
-      <c r="D10" s="143"/>
-      <c r="E10" s="141"/>
-      <c r="F10" s="141"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="141"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
     </row>
     <row r="11" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="139" t="s">
+      <c r="A11" s="143" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="139"/>
-      <c r="C11" s="139"/>
-      <c r="D11" s="139"/>
-      <c r="E11" s="139"/>
-      <c r="F11" s="139"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="143"/>
+      <c r="F11" s="143"/>
     </row>
     <row r="12" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="140" t="s">
+      <c r="A12" s="142" t="s">
         <v>112</v>
       </c>
-      <c r="B12" s="140"/>
-      <c r="C12" s="140"/>
-      <c r="D12" s="142" t="s">
+      <c r="B12" s="142"/>
+      <c r="C12" s="142"/>
+      <c r="D12" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="140" t="s">
+      <c r="E12" s="142" t="s">
         <v>113</v>
       </c>
-      <c r="F12" s="140"/>
+      <c r="F12" s="142"/>
     </row>
     <row r="13" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="144" t="s">
+      <c r="A13" s="147" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="144"/>
-      <c r="C13" s="144"/>
-      <c r="D13" s="143"/>
-      <c r="E13" s="141"/>
-      <c r="F13" s="141"/>
+      <c r="B13" s="147"/>
+      <c r="C13" s="147"/>
+      <c r="D13" s="141"/>
+      <c r="E13" s="139"/>
+      <c r="F13" s="139"/>
     </row>
     <row r="14" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="139" t="s">
+      <c r="A14" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="139"/>
-      <c r="C14" s="139"/>
-      <c r="D14" s="139"/>
-      <c r="E14" s="139"/>
-      <c r="F14" s="139"/>
+      <c r="B14" s="143"/>
+      <c r="C14" s="143"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="143"/>
+      <c r="F14" s="143"/>
     </row>
     <row r="15" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="140" t="s">
+      <c r="A15" s="142" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="140"/>
-      <c r="C15" s="140"/>
-      <c r="D15" s="142" t="s">
+      <c r="B15" s="142"/>
+      <c r="C15" s="142"/>
+      <c r="D15" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E15" s="140" t="s">
+      <c r="E15" s="142" t="s">
         <v>115</v>
       </c>
-      <c r="F15" s="140"/>
+      <c r="F15" s="142"/>
     </row>
     <row r="16" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="139" t="s">
         <v>116</v>
       </c>
-      <c r="B16" s="141"/>
-      <c r="C16" s="141"/>
-      <c r="D16" s="143"/>
-      <c r="E16" s="141"/>
-      <c r="F16" s="141"/>
+      <c r="B16" s="139"/>
+      <c r="C16" s="139"/>
+      <c r="D16" s="141"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="139"/>
     </row>
     <row r="17" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="139" t="s">
+      <c r="A17" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="139"/>
-      <c r="C17" s="139"/>
-      <c r="D17" s="139"/>
-      <c r="E17" s="139"/>
-      <c r="F17" s="139"/>
+      <c r="B17" s="143"/>
+      <c r="C17" s="143"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="143"/>
+      <c r="F17" s="143"/>
     </row>
     <row r="18" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="140" t="s">
+      <c r="A18" s="142" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="140"/>
-      <c r="C18" s="140"/>
-      <c r="D18" s="142" t="s">
+      <c r="B18" s="142"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E18" s="140" t="s">
+      <c r="E18" s="142" t="s">
         <v>118</v>
       </c>
-      <c r="F18" s="140"/>
+      <c r="F18" s="142"/>
     </row>
     <row r="19" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="141" t="s">
+      <c r="A19" s="139" t="s">
         <v>109</v>
       </c>
-      <c r="B19" s="141"/>
-      <c r="C19" s="141"/>
-      <c r="D19" s="143"/>
-      <c r="E19" s="141"/>
-      <c r="F19" s="141"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="141"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
     </row>
     <row r="20" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="139" t="s">
+      <c r="A20" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="139"/>
-      <c r="C20" s="139"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="139"/>
-      <c r="F20" s="139"/>
+      <c r="B20" s="143"/>
+      <c r="C20" s="143"/>
+      <c r="D20" s="143"/>
+      <c r="E20" s="143"/>
+      <c r="F20" s="143"/>
     </row>
     <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="140" t="s">
+      <c r="A21" s="142" t="s">
         <v>119</v>
       </c>
-      <c r="B21" s="140"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="142" t="s">
+      <c r="B21" s="142"/>
+      <c r="C21" s="142"/>
+      <c r="D21" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E21" s="140" t="s">
+      <c r="E21" s="142" t="s">
         <v>120</v>
       </c>
-      <c r="F21" s="140"/>
+      <c r="F21" s="142"/>
     </row>
     <row r="22" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="141" t="s">
+      <c r="A22" s="139" t="s">
         <v>121</v>
       </c>
-      <c r="B22" s="141"/>
-      <c r="C22" s="141"/>
-      <c r="D22" s="143"/>
-      <c r="E22" s="141"/>
-      <c r="F22" s="141"/>
+      <c r="B22" s="139"/>
+      <c r="C22" s="139"/>
+      <c r="D22" s="141"/>
+      <c r="E22" s="139"/>
+      <c r="F22" s="139"/>
     </row>
     <row r="23" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="139" t="s">
+      <c r="A23" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="139"/>
-      <c r="C23" s="139"/>
-      <c r="D23" s="139"/>
-      <c r="E23" s="139"/>
-      <c r="F23" s="139"/>
+      <c r="B23" s="143"/>
+      <c r="C23" s="143"/>
+      <c r="D23" s="143"/>
+      <c r="E23" s="143"/>
+      <c r="F23" s="143"/>
     </row>
     <row r="24" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="140" t="s">
+      <c r="A24" s="142" t="s">
         <v>118</v>
       </c>
-      <c r="B24" s="140"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="142" t="s">
+      <c r="B24" s="142"/>
+      <c r="C24" s="142"/>
+      <c r="D24" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E24" s="140" t="s">
+      <c r="E24" s="142" t="s">
         <v>122</v>
       </c>
-      <c r="F24" s="140"/>
+      <c r="F24" s="142"/>
     </row>
     <row r="25" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="141" t="s">
+      <c r="A25" s="139" t="s">
         <v>123</v>
       </c>
-      <c r="B25" s="141"/>
-      <c r="C25" s="141"/>
-      <c r="D25" s="143"/>
-      <c r="E25" s="141"/>
-      <c r="F25" s="141"/>
+      <c r="B25" s="139"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
     </row>
     <row r="26" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="139" t="s">
+      <c r="A26" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="139"/>
-      <c r="C26" s="139"/>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="139"/>
+      <c r="B26" s="143"/>
+      <c r="C26" s="143"/>
+      <c r="D26" s="143"/>
+      <c r="E26" s="143"/>
+      <c r="F26" s="143"/>
     </row>
     <row r="27" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="140" t="s">
+      <c r="A27" s="142" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="140"/>
-      <c r="C27" s="140"/>
-      <c r="D27" s="142" t="s">
+      <c r="B27" s="142"/>
+      <c r="C27" s="142"/>
+      <c r="D27" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E27" s="140" t="s">
+      <c r="E27" s="142" t="s">
         <v>124</v>
       </c>
-      <c r="F27" s="140"/>
+      <c r="F27" s="142"/>
     </row>
     <row r="28" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="141" t="s">
+      <c r="A28" s="139" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="141"/>
-      <c r="C28" s="141"/>
-      <c r="D28" s="143"/>
-      <c r="E28" s="141"/>
-      <c r="F28" s="141"/>
+      <c r="B28" s="139"/>
+      <c r="C28" s="139"/>
+      <c r="D28" s="141"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="139"/>
     </row>
     <row r="29" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="139" t="s">
+      <c r="A29" s="143" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="139"/>
-      <c r="C29" s="139"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
+      <c r="B29" s="143"/>
+      <c r="C29" s="143"/>
+      <c r="D29" s="143"/>
+      <c r="E29" s="143"/>
+      <c r="F29" s="143"/>
     </row>
     <row r="30" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="140" t="s">
+      <c r="A30" s="142" t="s">
         <v>118</v>
       </c>
-      <c r="B30" s="140"/>
-      <c r="C30" s="140"/>
-      <c r="D30" s="142" t="s">
+      <c r="B30" s="142"/>
+      <c r="C30" s="142"/>
+      <c r="D30" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E30" s="140" t="s">
+      <c r="E30" s="142" t="s">
         <v>125</v>
       </c>
-      <c r="F30" s="140"/>
+      <c r="F30" s="142"/>
     </row>
     <row r="31" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="141" t="s">
+      <c r="A31" s="139" t="s">
         <v>126</v>
       </c>
-      <c r="B31" s="141"/>
-      <c r="C31" s="141"/>
-      <c r="D31" s="143"/>
-      <c r="E31" s="141"/>
-      <c r="F31" s="141"/>
+      <c r="B31" s="139"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="141"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="139"/>
     </row>
     <row r="32" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="139" t="s">
+      <c r="A32" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="139"/>
-      <c r="C32" s="139"/>
-      <c r="D32" s="139"/>
-      <c r="E32" s="139"/>
-      <c r="F32" s="139"/>
+      <c r="B32" s="143"/>
+      <c r="C32" s="143"/>
+      <c r="D32" s="143"/>
+      <c r="E32" s="143"/>
+      <c r="F32" s="143"/>
     </row>
     <row r="33" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="140" t="s">
+      <c r="A33" s="142" t="s">
         <v>120</v>
       </c>
-      <c r="B33" s="140"/>
-      <c r="C33" s="140"/>
-      <c r="D33" s="142" t="s">
+      <c r="B33" s="142"/>
+      <c r="C33" s="142"/>
+      <c r="D33" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E33" s="140" t="s">
+      <c r="E33" s="142" t="s">
         <v>127</v>
       </c>
-      <c r="F33" s="140"/>
+      <c r="F33" s="142"/>
     </row>
     <row r="34" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="141" t="s">
+      <c r="A34" s="139" t="s">
         <v>126</v>
       </c>
-      <c r="B34" s="141"/>
-      <c r="C34" s="141"/>
-      <c r="D34" s="143"/>
-      <c r="E34" s="141"/>
-      <c r="F34" s="141"/>
+      <c r="B34" s="139"/>
+      <c r="C34" s="139"/>
+      <c r="D34" s="141"/>
+      <c r="E34" s="139"/>
+      <c r="F34" s="139"/>
     </row>
     <row r="35" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="139" t="s">
+      <c r="A35" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="139"/>
-      <c r="C35" s="139"/>
-      <c r="D35" s="139"/>
-      <c r="E35" s="139"/>
-      <c r="F35" s="139"/>
+      <c r="B35" s="143"/>
+      <c r="C35" s="143"/>
+      <c r="D35" s="143"/>
+      <c r="E35" s="143"/>
+      <c r="F35" s="143"/>
     </row>
     <row r="36" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="140" t="s">
+      <c r="A36" s="142" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="140"/>
-      <c r="C36" s="140"/>
-      <c r="D36" s="142" t="s">
+      <c r="B36" s="142"/>
+      <c r="C36" s="142"/>
+      <c r="D36" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E36" s="140" t="s">
+      <c r="E36" s="142" t="s">
         <v>128</v>
       </c>
-      <c r="F36" s="140"/>
+      <c r="F36" s="142"/>
     </row>
     <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="141" t="s">
+      <c r="A37" s="139" t="s">
         <v>129</v>
       </c>
-      <c r="B37" s="141"/>
-      <c r="C37" s="141"/>
-      <c r="D37" s="143"/>
-      <c r="E37" s="141"/>
-      <c r="F37" s="141"/>
+      <c r="B37" s="139"/>
+      <c r="C37" s="139"/>
+      <c r="D37" s="141"/>
+      <c r="E37" s="139"/>
+      <c r="F37" s="139"/>
     </row>
     <row r="38" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="139" t="s">
+      <c r="A38" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="139"/>
-      <c r="C38" s="139"/>
-      <c r="D38" s="139"/>
-      <c r="E38" s="139"/>
-      <c r="F38" s="139"/>
+      <c r="B38" s="143"/>
+      <c r="C38" s="143"/>
+      <c r="D38" s="143"/>
+      <c r="E38" s="143"/>
+      <c r="F38" s="143"/>
     </row>
     <row r="39" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="140" t="s">
+      <c r="A39" s="142" t="s">
         <v>120</v>
       </c>
-      <c r="B39" s="140"/>
-      <c r="C39" s="140"/>
-      <c r="D39" s="142" t="s">
+      <c r="B39" s="142"/>
+      <c r="C39" s="142"/>
+      <c r="D39" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E39" s="140" t="s">
+      <c r="E39" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="F39" s="140"/>
+      <c r="F39" s="142"/>
     </row>
     <row r="40" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="141" t="s">
+      <c r="A40" s="139" t="s">
         <v>129</v>
       </c>
-      <c r="B40" s="141"/>
-      <c r="C40" s="141"/>
-      <c r="D40" s="143"/>
-      <c r="E40" s="141"/>
-      <c r="F40" s="141"/>
+      <c r="B40" s="139"/>
+      <c r="C40" s="139"/>
+      <c r="D40" s="141"/>
+      <c r="E40" s="139"/>
+      <c r="F40" s="139"/>
     </row>
     <row r="41" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="139" t="s">
+      <c r="A41" s="143" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="139"/>
-      <c r="C41" s="139"/>
-      <c r="D41" s="139"/>
-      <c r="E41" s="139"/>
-      <c r="F41" s="139"/>
+      <c r="B41" s="143"/>
+      <c r="C41" s="143"/>
+      <c r="D41" s="143"/>
+      <c r="E41" s="143"/>
+      <c r="F41" s="143"/>
     </row>
     <row r="42" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="140" t="s">
+      <c r="A42" s="142" t="s">
         <v>131</v>
       </c>
-      <c r="B42" s="140"/>
-      <c r="C42" s="140"/>
-      <c r="D42" s="142" t="s">
+      <c r="B42" s="142"/>
+      <c r="C42" s="142"/>
+      <c r="D42" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E42" s="140" t="s">
+      <c r="E42" s="142" t="s">
         <v>132</v>
       </c>
-      <c r="F42" s="140"/>
+      <c r="F42" s="142"/>
     </row>
     <row r="43" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="141" t="s">
+      <c r="A43" s="139" t="s">
         <v>133</v>
       </c>
-      <c r="B43" s="141"/>
-      <c r="C43" s="141"/>
-      <c r="D43" s="143"/>
-      <c r="E43" s="141"/>
-      <c r="F43" s="141"/>
+      <c r="B43" s="139"/>
+      <c r="C43" s="139"/>
+      <c r="D43" s="141"/>
+      <c r="E43" s="139"/>
+      <c r="F43" s="139"/>
     </row>
     <row r="44" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="139" t="s">
+      <c r="A44" s="143" t="s">
         <v>134</v>
       </c>
-      <c r="B44" s="139"/>
-      <c r="C44" s="139"/>
-      <c r="D44" s="139"/>
-      <c r="E44" s="139"/>
-      <c r="F44" s="139"/>
+      <c r="B44" s="143"/>
+      <c r="C44" s="143"/>
+      <c r="D44" s="143"/>
+      <c r="E44" s="143"/>
+      <c r="F44" s="143"/>
     </row>
     <row r="45" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="140" t="s">
+      <c r="A45" s="142" t="s">
         <v>135</v>
       </c>
-      <c r="B45" s="140"/>
-      <c r="C45" s="140"/>
-      <c r="D45" s="142" t="s">
+      <c r="B45" s="142"/>
+      <c r="C45" s="142"/>
+      <c r="D45" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E45" s="140" t="s">
+      <c r="E45" s="142" t="s">
         <v>136</v>
       </c>
-      <c r="F45" s="140"/>
+      <c r="F45" s="142"/>
     </row>
     <row r="46" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="140" t="s">
+      <c r="A46" s="142" t="s">
         <v>110</v>
       </c>
-      <c r="B46" s="140"/>
-      <c r="C46" s="140"/>
-      <c r="D46" s="142"/>
-      <c r="E46" s="140"/>
-      <c r="F46" s="140"/>
+      <c r="B46" s="142"/>
+      <c r="C46" s="142"/>
+      <c r="D46" s="140"/>
+      <c r="E46" s="142"/>
+      <c r="F46" s="142"/>
     </row>
     <row r="47" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="141" t="s">
+      <c r="A47" s="139" t="s">
         <v>137</v>
       </c>
-      <c r="B47" s="141"/>
-      <c r="C47" s="141"/>
-      <c r="D47" s="143"/>
-      <c r="E47" s="141"/>
-      <c r="F47" s="141"/>
+      <c r="B47" s="139"/>
+      <c r="C47" s="139"/>
+      <c r="D47" s="141"/>
+      <c r="E47" s="139"/>
+      <c r="F47" s="139"/>
     </row>
     <row r="48" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="139" t="s">
+      <c r="A48" s="143" t="s">
         <v>138</v>
       </c>
-      <c r="B48" s="139"/>
-      <c r="C48" s="139"/>
-      <c r="D48" s="139"/>
-      <c r="E48" s="139"/>
-      <c r="F48" s="139"/>
+      <c r="B48" s="143"/>
+      <c r="C48" s="143"/>
+      <c r="D48" s="143"/>
+      <c r="E48" s="143"/>
+      <c r="F48" s="143"/>
     </row>
     <row r="49" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="140" t="s">
+      <c r="A49" s="142" t="s">
         <v>135</v>
       </c>
-      <c r="B49" s="140"/>
-      <c r="C49" s="140"/>
-      <c r="D49" s="142" t="s">
+      <c r="B49" s="142"/>
+      <c r="C49" s="142"/>
+      <c r="D49" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E49" s="140" t="s">
+      <c r="E49" s="142" t="s">
         <v>139</v>
       </c>
-      <c r="F49" s="140"/>
+      <c r="F49" s="142"/>
     </row>
     <row r="50" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="140" t="s">
+      <c r="A50" s="142" t="s">
         <v>110</v>
       </c>
-      <c r="B50" s="140"/>
-      <c r="C50" s="140"/>
-      <c r="D50" s="142"/>
-      <c r="E50" s="140"/>
-      <c r="F50" s="140"/>
+      <c r="B50" s="142"/>
+      <c r="C50" s="142"/>
+      <c r="D50" s="140"/>
+      <c r="E50" s="142"/>
+      <c r="F50" s="142"/>
     </row>
     <row r="51" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="141" t="s">
+      <c r="A51" s="139" t="s">
         <v>140</v>
       </c>
-      <c r="B51" s="141"/>
-      <c r="C51" s="141"/>
-      <c r="D51" s="143"/>
-      <c r="E51" s="141"/>
-      <c r="F51" s="141"/>
+      <c r="B51" s="139"/>
+      <c r="C51" s="139"/>
+      <c r="D51" s="141"/>
+      <c r="E51" s="139"/>
+      <c r="F51" s="139"/>
     </row>
     <row r="52" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="139" t="s">
+      <c r="A52" s="143" t="s">
         <v>141</v>
       </c>
-      <c r="B52" s="139"/>
-      <c r="C52" s="139"/>
-      <c r="D52" s="139"/>
-      <c r="E52" s="139"/>
-      <c r="F52" s="139"/>
+      <c r="B52" s="143"/>
+      <c r="C52" s="143"/>
+      <c r="D52" s="143"/>
+      <c r="E52" s="143"/>
+      <c r="F52" s="143"/>
     </row>
     <row r="53" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="140" t="s">
+      <c r="A53" s="142" t="s">
         <v>135</v>
       </c>
-      <c r="B53" s="140"/>
-      <c r="C53" s="140"/>
-      <c r="D53" s="142" t="s">
+      <c r="B53" s="142"/>
+      <c r="C53" s="142"/>
+      <c r="D53" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="E53" s="140" t="s">
+      <c r="E53" s="142" t="s">
         <v>142</v>
       </c>
-      <c r="F53" s="140"/>
+      <c r="F53" s="142"/>
     </row>
     <row r="54" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="140" t="s">
+      <c r="A54" s="142" t="s">
         <v>110</v>
       </c>
-      <c r="B54" s="140"/>
-      <c r="C54" s="140"/>
-      <c r="D54" s="142"/>
-      <c r="E54" s="140"/>
-      <c r="F54" s="140"/>
+      <c r="B54" s="142"/>
+      <c r="C54" s="142"/>
+      <c r="D54" s="140"/>
+      <c r="E54" s="142"/>
+      <c r="F54" s="142"/>
     </row>
     <row r="55" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="141" t="s">
+      <c r="A55" s="139" t="s">
         <v>143</v>
       </c>
-      <c r="B55" s="141"/>
-      <c r="C55" s="141"/>
-      <c r="D55" s="143"/>
-      <c r="E55" s="141"/>
-      <c r="F55" s="141"/>
+      <c r="B55" s="139"/>
+      <c r="C55" s="139"/>
+      <c r="D55" s="141"/>
+      <c r="E55" s="139"/>
+      <c r="F55" s="139"/>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="104" t="s">
+      <c r="A56" s="123" t="s">
         <v>176</v>
       </c>
-      <c r="B56" s="104"/>
-      <c r="C56" s="104"/>
-      <c r="D56" s="104"/>
-      <c r="E56" s="104"/>
-      <c r="F56" s="104"/>
+      <c r="B56" s="123"/>
+      <c r="C56" s="123"/>
+      <c r="D56" s="123"/>
+      <c r="E56" s="123"/>
+      <c r="F56" s="123"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="138" t="s">
@@ -24023,7 +24044,7 @@
       </c>
       <c r="B57" s="138"/>
       <c r="C57" s="138"/>
-      <c r="D57" s="146" t="s">
+      <c r="D57" s="145" t="s">
         <v>105</v>
       </c>
       <c r="E57" s="138" t="s">
@@ -24032,22 +24053,22 @@
       <c r="F57" s="138"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="145"/>
-      <c r="B58" s="145"/>
-      <c r="C58" s="145"/>
-      <c r="D58" s="147"/>
-      <c r="E58" s="145"/>
-      <c r="F58" s="145"/>
+      <c r="A58" s="144"/>
+      <c r="B58" s="144"/>
+      <c r="C58" s="144"/>
+      <c r="D58" s="146"/>
+      <c r="E58" s="144"/>
+      <c r="F58" s="144"/>
     </row>
     <row r="59" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="104" t="s">
+      <c r="A59" s="123" t="s">
         <v>180</v>
       </c>
-      <c r="B59" s="104"/>
-      <c r="C59" s="104"/>
-      <c r="D59" s="104"/>
-      <c r="E59" s="104"/>
-      <c r="F59" s="104"/>
+      <c r="B59" s="123"/>
+      <c r="C59" s="123"/>
+      <c r="D59" s="123"/>
+      <c r="E59" s="123"/>
+      <c r="F59" s="123"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="134" t="s">
@@ -24072,14 +24093,14 @@
       <c r="F61" s="135"/>
     </row>
     <row r="62" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="104" t="s">
+      <c r="A62" s="123" t="s">
         <v>251</v>
       </c>
-      <c r="B62" s="104"/>
-      <c r="C62" s="104"/>
-      <c r="D62" s="104"/>
-      <c r="E62" s="104"/>
-      <c r="F62" s="104"/>
+      <c r="B62" s="123"/>
+      <c r="C62" s="123"/>
+      <c r="D62" s="123"/>
+      <c r="E62" s="123"/>
+      <c r="F62" s="123"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="134" t="s">
@@ -24104,14 +24125,14 @@
       <c r="F64" s="135"/>
     </row>
     <row r="65" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="104" t="s">
+      <c r="A65" s="123" t="s">
         <v>944</v>
       </c>
-      <c r="B65" s="104"/>
-      <c r="C65" s="104"/>
-      <c r="D65" s="104"/>
-      <c r="E65" s="104"/>
-      <c r="F65" s="104"/>
+      <c r="B65" s="123"/>
+      <c r="C65" s="123"/>
+      <c r="D65" s="123"/>
+      <c r="E65" s="123"/>
+      <c r="F65" s="123"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="134"/>
@@ -24132,14 +24153,14 @@
       <c r="F67" s="135"/>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="104" t="s">
+      <c r="A68" s="123" t="s">
         <v>945</v>
       </c>
-      <c r="B68" s="104"/>
-      <c r="C68" s="104"/>
-      <c r="D68" s="104"/>
-      <c r="E68" s="104"/>
-      <c r="F68" s="104"/>
+      <c r="B68" s="123"/>
+      <c r="C68" s="123"/>
+      <c r="D68" s="123"/>
+      <c r="E68" s="123"/>
+      <c r="F68" s="123"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="134"/>
@@ -24160,14 +24181,14 @@
       <c r="F70" s="135"/>
     </row>
     <row r="71" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="104" t="s">
+      <c r="A71" s="123" t="s">
         <v>1264</v>
       </c>
-      <c r="B71" s="104"/>
-      <c r="C71" s="104"/>
-      <c r="D71" s="104"/>
-      <c r="E71" s="104"/>
-      <c r="F71" s="104"/>
+      <c r="B71" s="123"/>
+      <c r="C71" s="123"/>
+      <c r="D71" s="123"/>
+      <c r="E71" s="123"/>
+      <c r="F71" s="123"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="134"/>
@@ -24189,92 +24210,6 @@
     </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E69:F70"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="D49:D51"/>
-    <mergeCell ref="E49:F51"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="D53:D55"/>
-    <mergeCell ref="E53:F55"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="E57:F58"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D45:D47"/>
-    <mergeCell ref="E45:F47"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:F40"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:F43"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:F34"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:F37"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:F28"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:F31"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:F22"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:F25"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:F19"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:F13"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A72:C73"/>
     <mergeCell ref="D72:D73"/>
@@ -24299,6 +24234,92 @@
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:F19"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:F10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:F22"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:F25"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:F28"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:F31"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:F34"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:F37"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:F40"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:F43"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D45:D47"/>
+    <mergeCell ref="E45:F47"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E69:F70"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="D49:D51"/>
+    <mergeCell ref="E49:F51"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="D53:D55"/>
+    <mergeCell ref="E53:F55"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E57:F58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -35109,7 +35130,7 @@
         <v>1498</v>
       </c>
       <c r="T22" s="18" t="s">
-        <v>1347</v>
+        <v>164</v>
       </c>
       <c r="U22" s="20" t="s">
         <v>1499</v>
@@ -35239,7 +35260,7 @@
         <v>732</v>
       </c>
       <c r="T24" s="18" t="s">
-        <v>161</v>
+        <v>1347</v>
       </c>
       <c r="U24" s="20" t="s">
         <v>1514</v>
@@ -37417,82 +37438,127 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>144</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="D52" s="14" t="s">
         <v>234</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="F52" s="14" t="s">
         <v>191</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>2748</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
-        <v>2749</v>
+        <v>2748</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>144</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>2750</v>
+        <v>2749</v>
       </c>
       <c r="D53" s="14" t="s">
         <v>234</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="F53" s="14" t="s">
         <v>191</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H53" s="14" t="s">
-        <v>2748</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="14"/>
+      <c r="A54" s="14" t="s">
+        <v>2752</v>
+      </c>
       <c r="B54" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
+      <c r="C54" s="14" t="s">
+        <v>2755</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="14"/>
+      <c r="A55" s="14" t="s">
+        <v>2753</v>
+      </c>
       <c r="B55" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
+      <c r="C55" s="14" t="s">
+        <v>2756</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G55" s="14" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="14"/>
+      <c r="A56" s="14" t="s">
+        <v>2754</v>
+      </c>
       <c r="B56" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
+      <c r="C56" s="14" t="s">
+        <v>2757</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="F56" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="H56" s="14" t="s">
+        <v>1244</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="14"/>
@@ -39156,7 +39222,7 @@
         <v>164</v>
       </c>
       <c r="H14" s="70" t="s">
-        <v>247</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -39594,7 +39660,7 @@
         <v>164</v>
       </c>
       <c r="H32" s="70" t="s">
-        <v>247</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -40032,7 +40098,7 @@
         <v>164</v>
       </c>
       <c r="H50" s="70" t="s">
-        <v>247</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -40470,7 +40536,7 @@
         <v>164</v>
       </c>
       <c r="H68" s="70" t="s">
-        <v>247</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -40934,7 +41000,7 @@
         <v>164</v>
       </c>
       <c r="H87" s="70" t="s">
-        <v>247</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -41384,7 +41450,7 @@
         <v>164</v>
       </c>
       <c r="H105" s="70" t="s">
-        <v>247</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -41822,7 +41888,7 @@
         <v>164</v>
       </c>
       <c r="H123" s="70" t="s">
-        <v>247</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -42113,7 +42179,7 @@
         <v>200</v>
       </c>
       <c r="G135" s="70" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H135" s="70"/>
     </row>
@@ -42137,7 +42203,7 @@
         <v>200</v>
       </c>
       <c r="G136" s="70" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H136" s="70"/>
     </row>
@@ -42161,7 +42227,7 @@
         <v>200</v>
       </c>
       <c r="G137" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H137" s="70"/>
     </row>
@@ -42185,7 +42251,7 @@
         <v>191</v>
       </c>
       <c r="G138" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H138" s="70"/>
     </row>
@@ -42209,7 +42275,7 @@
         <v>218</v>
       </c>
       <c r="G139" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H139" s="70"/>
     </row>
@@ -42233,7 +42299,7 @@
         <v>218</v>
       </c>
       <c r="G140" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H140" s="70"/>
     </row>
@@ -42257,7 +42323,7 @@
         <v>191</v>
       </c>
       <c r="G141" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H141" s="70"/>
     </row>
@@ -42281,10 +42347,10 @@
         <v>191</v>
       </c>
       <c r="G142" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H142" s="70" t="s">
-        <v>247</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -42307,7 +42373,7 @@
         <v>191</v>
       </c>
       <c r="G143" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H143" s="70"/>
     </row>
@@ -42331,7 +42397,7 @@
         <v>191</v>
       </c>
       <c r="G144" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H144" s="70"/>
     </row>
@@ -42355,7 +42421,7 @@
         <v>191</v>
       </c>
       <c r="G145" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H145" s="70"/>
     </row>
@@ -42379,7 +42445,7 @@
         <v>191</v>
       </c>
       <c r="G146" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H146" s="70"/>
     </row>
@@ -42403,7 +42469,7 @@
         <v>191</v>
       </c>
       <c r="G147" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H147" s="70"/>
     </row>
@@ -42427,7 +42493,7 @@
         <v>191</v>
       </c>
       <c r="G148" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H148" s="70"/>
     </row>
@@ -42451,7 +42517,7 @@
         <v>191</v>
       </c>
       <c r="G149" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H149" s="70"/>
     </row>
@@ -42475,7 +42541,7 @@
         <v>191</v>
       </c>
       <c r="G150" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H150" s="70"/>
     </row>
@@ -42499,7 +42565,7 @@
         <v>200</v>
       </c>
       <c r="G151" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H151" s="70"/>
     </row>
@@ -42511,7 +42577,7 @@
         <v>157</v>
       </c>
       <c r="C152" s="70" t="s">
-        <v>2744</v>
+        <v>2751</v>
       </c>
       <c r="D152" s="71" t="s">
         <v>233</v>
@@ -42523,7 +42589,7 @@
         <v>1039</v>
       </c>
       <c r="G152" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H152" s="70" t="s">
         <v>283</v>
@@ -42549,7 +42615,7 @@
         <v>199</v>
       </c>
       <c r="G153" s="70" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H153" s="70" t="s">
         <v>1073</v>
